--- a/research/traditional_assets/database/data/greece/greece_paper_forest_products.xlsx
+++ b/research/traditional_assets/database/data/greece/greece_paper_forest_products.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="atse_akrit" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,25 +590,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.04389999999999999</v>
+        <v>0.081</v>
       </c>
       <c r="G2">
-        <v>0.008194444444444443</v>
+        <v>0.07068181818181818</v>
       </c>
       <c r="H2">
-        <v>0.008194444444444443</v>
+        <v>0.07068181818181818</v>
       </c>
       <c r="I2">
-        <v>-0.04</v>
+        <v>0.02081818181818182</v>
       </c>
       <c r="J2">
-        <v>-0.04</v>
+        <v>0.02081818181818182</v>
       </c>
       <c r="K2">
-        <v>-0.6899999999999999</v>
+        <v>0.217</v>
       </c>
       <c r="L2">
-        <v>-0.01916666666666667</v>
+        <v>0.004931818181818182</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -615,7 +617,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,79 +626,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.778</v>
+        <v>1.08</v>
       </c>
       <c r="V2">
-        <v>0.08810872027180068</v>
+        <v>0.1317073170731708</v>
       </c>
       <c r="W2">
-        <v>0.1408163265306122</v>
+        <v>-0.03760831889081456</v>
       </c>
       <c r="X2">
-        <v>0.3686534160155576</v>
+        <v>0.4725898274345979</v>
       </c>
       <c r="Y2">
-        <v>-0.2278370894849454</v>
+        <v>-0.5101981463254124</v>
       </c>
       <c r="Z2">
-        <v>0.9203630320848779</v>
+        <v>1.034028952810679</v>
       </c>
       <c r="AA2">
-        <v>-0.03681452128339512</v>
+        <v>0.02152660274487686</v>
       </c>
       <c r="AB2">
-        <v>0.09393437278702221</v>
+        <v>0.1480718073319095</v>
       </c>
       <c r="AC2">
-        <v>-0.1307488940704173</v>
+        <v>-0.1265452045870326</v>
       </c>
       <c r="AD2">
-        <v>49.1</v>
+        <v>39.2</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>49.1</v>
+        <v>39.2</v>
       </c>
       <c r="AG2">
-        <v>48.322</v>
+        <v>38.12</v>
       </c>
       <c r="AH2">
-        <v>0.8475746590712929</v>
+        <v>0.8270042194092827</v>
       </c>
       <c r="AI2">
-        <v>1.13316408954535</v>
+        <v>1.119360365505425</v>
       </c>
       <c r="AJ2">
-        <v>0.8454997200447929</v>
+        <v>0.8229706390328152</v>
       </c>
       <c r="AK2">
-        <v>1.135598796766309</v>
+        <v>1.123158515026517</v>
       </c>
       <c r="AL2">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AM2">
-        <v>1.903</v>
+        <v>1.6</v>
       </c>
       <c r="AN2">
-        <v>26.97802197802198</v>
+        <v>10.23498694516971</v>
       </c>
       <c r="AO2">
-        <v>-0.7539267015706806</v>
+        <v>0.5725</v>
       </c>
       <c r="AP2">
-        <v>26.55054945054945</v>
+        <v>9.953002610966058</v>
       </c>
       <c r="AQ2">
-        <v>-0.7566999474513925</v>
+        <v>0.5725</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +718,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.04389999999999999</v>
+        <v>0.081</v>
       </c>
       <c r="G3">
-        <v>0.008194444444444443</v>
+        <v>0.07068181818181818</v>
       </c>
       <c r="H3">
-        <v>0.008194444444444443</v>
+        <v>0.07068181818181818</v>
       </c>
       <c r="I3">
-        <v>-0.04</v>
+        <v>0.02081818181818182</v>
       </c>
       <c r="J3">
-        <v>-0.04</v>
+        <v>0.02081818181818182</v>
       </c>
       <c r="K3">
-        <v>-0.6899999999999999</v>
+        <v>0.217</v>
       </c>
       <c r="L3">
-        <v>-0.01916666666666667</v>
+        <v>0.004931818181818182</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -743,7 +745,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,79 +754,8788 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.778</v>
+        <v>1.08</v>
       </c>
       <c r="V3">
-        <v>0.08810872027180068</v>
+        <v>0.1317073170731708</v>
       </c>
       <c r="W3">
-        <v>0.1408163265306122</v>
+        <v>-0.03760831889081456</v>
       </c>
       <c r="X3">
-        <v>0.3686534160155576</v>
+        <v>0.4725898274345979</v>
       </c>
       <c r="Y3">
-        <v>-0.2278370894849454</v>
+        <v>-0.5101981463254124</v>
       </c>
       <c r="Z3">
-        <v>0.9203630320848779</v>
+        <v>1.034028952810679</v>
       </c>
       <c r="AA3">
-        <v>-0.03681452128339512</v>
+        <v>0.02152660274487686</v>
       </c>
       <c r="AB3">
-        <v>0.09393437278702221</v>
+        <v>0.1480718073319095</v>
       </c>
       <c r="AC3">
-        <v>-0.1307488940704173</v>
+        <v>-0.1265452045870326</v>
       </c>
       <c r="AD3">
-        <v>49.1</v>
+        <v>39.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>49.1</v>
+        <v>39.2</v>
       </c>
       <c r="AG3">
-        <v>48.322</v>
+        <v>38.12</v>
       </c>
       <c r="AH3">
-        <v>0.8475746590712929</v>
+        <v>0.8270042194092827</v>
       </c>
       <c r="AI3">
-        <v>1.13316408954535</v>
+        <v>1.119360365505425</v>
       </c>
       <c r="AJ3">
-        <v>0.8454997200447929</v>
+        <v>0.8229706390328152</v>
       </c>
       <c r="AK3">
-        <v>1.135598796766309</v>
+        <v>1.123158515026517</v>
       </c>
       <c r="AL3">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AM3">
-        <v>1.903</v>
+        <v>1.6</v>
       </c>
       <c r="AN3">
-        <v>26.97802197802198</v>
+        <v>10.23498694516971</v>
       </c>
       <c r="AO3">
-        <v>-0.7539267015706806</v>
+        <v>0.5725</v>
       </c>
       <c r="AP3">
-        <v>26.55054945054945</v>
+        <v>9.953002610966058</v>
       </c>
       <c r="AQ3">
-        <v>-0.7566999474513925</v>
+        <v>0.5725</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Akritas S.A. (ATSE:AKRIT)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ATSE:AKRIT</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Paper/Forest Products</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.827004219409283</v>
+      </c>
+      <c r="F2">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H2">
+        <v>53.6230164164809</v>
+      </c>
+      <c r="I2">
+        <v>46.32</v>
+      </c>
+      <c r="J2">
+        <v>55.8610164164809</v>
+      </c>
+      <c r="K2">
+        <v>39.2</v>
+      </c>
+      <c r="L2">
+        <v>3.318</v>
+      </c>
+      <c r="M2">
+        <v>0.148071807331909</v>
+      </c>
+      <c r="N2">
+        <v>0.129408271032475</v>
+      </c>
+      <c r="O2">
+        <v>0.0801879357798165</v>
+      </c>
+      <c r="P2">
+        <v>0.0429</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.472589827434598</v>
+      </c>
+      <c r="T2">
+        <v>0.135919646271479</v>
+      </c>
+      <c r="U2">
+        <v>3.57862193925151</v>
+      </c>
+      <c r="V2">
+        <v>0.801204811405728</v>
+      </c>
+      <c r="W2">
+        <v>5.019453120718942</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AB2">
+        <v>0.1212170033041622</v>
+      </c>
+      <c r="AC2">
+        <v>0.1028050458715596</v>
+      </c>
+      <c r="AD2">
+        <v>0.22</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>3.83</v>
+      </c>
+      <c r="AH2">
+        <v>2.914</v>
+      </c>
+      <c r="AI2">
+        <v>3.366</v>
+      </c>
+      <c r="AJ2">
+        <v>39.2</v>
+      </c>
+      <c r="AK2">
+        <v>39.2</v>
+      </c>
+      <c r="AL2">
+        <v>1.6</v>
+      </c>
+      <c r="AN2">
+        <v>1.08</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1305339742357051</v>
+      </c>
+      <c r="C2">
+        <v>56.25552420228623</v>
+      </c>
+      <c r="D2">
+        <v>55.17552420228623</v>
+      </c>
+      <c r="E2">
+        <v>-39.2</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>1.08</v>
+      </c>
+      <c r="H2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>3.83</v>
+      </c>
+      <c r="K2">
+        <v>2.914</v>
+      </c>
+      <c r="L2">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="O2">
+        <v>0.2015199999999999</v>
+      </c>
+      <c r="P2">
+        <v>0.71448</v>
+      </c>
+      <c r="Q2">
+        <v>3.62848</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1305339742357051</v>
+      </c>
+      <c r="T2">
+        <v>0.7567748066294202</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.22</v>
+      </c>
+      <c r="W2">
+        <v>0.035646</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1303006194923866</v>
+      </c>
+      <c r="C3">
+        <v>55.92223877186094</v>
+      </c>
+      <c r="D3">
+        <v>55.31623877186094</v>
+      </c>
+      <c r="E3">
+        <v>-38.72600000000001</v>
+      </c>
+      <c r="F3">
+        <v>0.4740000000000001</v>
+      </c>
+      <c r="G3">
+        <v>1.08</v>
+      </c>
+      <c r="H3">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>3.83</v>
+      </c>
+      <c r="K3">
+        <v>2.914</v>
+      </c>
+      <c r="L3">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M3">
+        <v>0.02166180000000001</v>
+      </c>
+      <c r="N3">
+        <v>0.8943382</v>
+      </c>
+      <c r="O3">
+        <v>0.196754404</v>
+      </c>
+      <c r="P3">
+        <v>0.697583796</v>
+      </c>
+      <c r="Q3">
+        <v>3.611583796</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1312567267599865</v>
+      </c>
+      <c r="T3">
+        <v>0.7627372748028641</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.22</v>
+      </c>
+      <c r="W3">
+        <v>0.035646</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>42.28642125769787</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.130067264749068</v>
+      </c>
+      <c r="C4">
+        <v>55.58967290747841</v>
+      </c>
+      <c r="D4">
+        <v>55.45767290747841</v>
+      </c>
+      <c r="E4">
+        <v>-38.252</v>
+      </c>
+      <c r="F4">
+        <v>0.9480000000000002</v>
+      </c>
+      <c r="G4">
+        <v>1.08</v>
+      </c>
+      <c r="H4">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>3.83</v>
+      </c>
+      <c r="K4">
+        <v>2.914</v>
+      </c>
+      <c r="L4">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M4">
+        <v>0.04332360000000001</v>
+      </c>
+      <c r="N4">
+        <v>0.8726763999999999</v>
+      </c>
+      <c r="O4">
+        <v>0.191988808</v>
+      </c>
+      <c r="P4">
+        <v>0.680687592</v>
+      </c>
+      <c r="Q4">
+        <v>3.594687592</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1319942293357837</v>
+      </c>
+      <c r="T4">
+        <v>0.7688214260002558</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.22</v>
+      </c>
+      <c r="W4">
+        <v>0.035646</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>21.14321062884893</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1298339100057495</v>
+      </c>
+      <c r="C5">
+        <v>55.25783214270792</v>
+      </c>
+      <c r="D5">
+        <v>55.59983214270792</v>
+      </c>
+      <c r="E5">
+        <v>-37.77800000000001</v>
+      </c>
+      <c r="F5">
+        <v>1.422</v>
+      </c>
+      <c r="G5">
+        <v>1.08</v>
+      </c>
+      <c r="H5">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>3.83</v>
+      </c>
+      <c r="K5">
+        <v>2.914</v>
+      </c>
+      <c r="L5">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M5">
+        <v>0.06498540000000001</v>
+      </c>
+      <c r="N5">
+        <v>0.8510146</v>
+      </c>
+      <c r="O5">
+        <v>0.187223212</v>
+      </c>
+      <c r="P5">
+        <v>0.6637913879999999</v>
+      </c>
+      <c r="Q5">
+        <v>3.577791388</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1327469381502572</v>
+      </c>
+      <c r="T5">
+        <v>0.7750310236140887</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.22</v>
+      </c>
+      <c r="W5">
+        <v>0.035646</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>14.09547375256596</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1297690352624309</v>
+      </c>
+      <c r="C6">
+        <v>54.8234832704615</v>
+      </c>
+      <c r="D6">
+        <v>55.6394832704615</v>
+      </c>
+      <c r="E6">
+        <v>-37.304</v>
+      </c>
+      <c r="F6">
+        <v>1.896</v>
+      </c>
+      <c r="G6">
+        <v>1.08</v>
+      </c>
+      <c r="H6">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>3.83</v>
+      </c>
+      <c r="K6">
+        <v>2.914</v>
+      </c>
+      <c r="L6">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M6">
+        <v>0.09688560000000002</v>
+      </c>
+      <c r="N6">
+        <v>0.8191143999999999</v>
+      </c>
+      <c r="O6">
+        <v>0.180205168</v>
+      </c>
+      <c r="P6">
+        <v>0.6389092319999999</v>
+      </c>
+      <c r="Q6">
+        <v>3.552909232</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1335153283983656</v>
+      </c>
+      <c r="T6">
+        <v>0.7813699878448763</v>
+      </c>
+      <c r="U6">
+        <v>0.0511</v>
+      </c>
+      <c r="V6">
+        <v>0.22</v>
+      </c>
+      <c r="W6">
+        <v>0.039858</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>9.454449371217185</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1296519005191124</v>
+      </c>
+      <c r="C7">
+        <v>54.42121888142863</v>
+      </c>
+      <c r="D7">
+        <v>55.71121888142863</v>
+      </c>
+      <c r="E7">
+        <v>-36.83000000000001</v>
+      </c>
+      <c r="F7">
+        <v>2.370000000000001</v>
+      </c>
+      <c r="G7">
+        <v>1.08</v>
+      </c>
+      <c r="H7">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>3.83</v>
+      </c>
+      <c r="K7">
+        <v>2.914</v>
+      </c>
+      <c r="L7">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M7">
+        <v>0.1256100000000001</v>
+      </c>
+      <c r="N7">
+        <v>0.7903899999999999</v>
+      </c>
+      <c r="O7">
+        <v>0.1738858</v>
+      </c>
+      <c r="P7">
+        <v>0.6165041999999999</v>
+      </c>
+      <c r="Q7">
+        <v>3.5305042</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1342998952832762</v>
+      </c>
+      <c r="T7">
+        <v>0.787842403954207</v>
+      </c>
+      <c r="U7">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V7">
+        <v>0.22</v>
+      </c>
+      <c r="W7">
+        <v>0.04134000000000001</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>7.292413024440726</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1295690857757938</v>
+      </c>
+      <c r="C8">
+        <v>53.99804797430973</v>
+      </c>
+      <c r="D8">
+        <v>55.76204797430973</v>
+      </c>
+      <c r="E8">
+        <v>-36.356</v>
+      </c>
+      <c r="F8">
+        <v>2.844</v>
+      </c>
+      <c r="G8">
+        <v>1.08</v>
+      </c>
+      <c r="H8">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>3.83</v>
+      </c>
+      <c r="K8">
+        <v>2.914</v>
+      </c>
+      <c r="L8">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M8">
+        <v>0.15642</v>
+      </c>
+      <c r="N8">
+        <v>0.7595799999999999</v>
+      </c>
+      <c r="O8">
+        <v>0.1671076</v>
+      </c>
+      <c r="P8">
+        <v>0.5924723999999999</v>
+      </c>
+      <c r="Q8">
+        <v>3.5064724</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1351011550806317</v>
+      </c>
+      <c r="T8">
+        <v>0.794452531044587</v>
+      </c>
+      <c r="U8">
+        <v>0.055</v>
+      </c>
+      <c r="V8">
+        <v>0.22</v>
+      </c>
+      <c r="W8">
+        <v>0.0429</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>5.856028640838766</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1294082710324753</v>
+      </c>
+      <c r="C9">
+        <v>53.62301641648087</v>
+      </c>
+      <c r="D9">
+        <v>55.86101641648087</v>
+      </c>
+      <c r="E9">
+        <v>-35.88200000000001</v>
+      </c>
+      <c r="F9">
+        <v>3.318000000000001</v>
+      </c>
+      <c r="G9">
+        <v>1.08</v>
+      </c>
+      <c r="H9">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>3.83</v>
+      </c>
+      <c r="K9">
+        <v>2.914</v>
+      </c>
+      <c r="L9">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M9">
+        <v>0.18249</v>
+      </c>
+      <c r="N9">
+        <v>0.7335099999999999</v>
+      </c>
+      <c r="O9">
+        <v>0.1613722</v>
+      </c>
+      <c r="P9">
+        <v>0.5721377999999999</v>
+      </c>
+      <c r="Q9">
+        <v>3.4861378</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1359196462714788</v>
+      </c>
+      <c r="T9">
+        <v>0.8012048114057282</v>
+      </c>
+      <c r="U9">
+        <v>0.055</v>
+      </c>
+      <c r="V9">
+        <v>0.22</v>
+      </c>
+      <c r="W9">
+        <v>0.0429</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>5.019453120718942</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1294845762891567</v>
+      </c>
+      <c r="C10">
+        <v>53.10201295271042</v>
+      </c>
+      <c r="D10">
+        <v>55.81401295271042</v>
+      </c>
+      <c r="E10">
+        <v>-35.408</v>
+      </c>
+      <c r="F10">
+        <v>3.792000000000001</v>
+      </c>
+      <c r="G10">
+        <v>1.08</v>
+      </c>
+      <c r="H10">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>3.83</v>
+      </c>
+      <c r="K10">
+        <v>2.914</v>
+      </c>
+      <c r="L10">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M10">
+        <v>0.2229696000000001</v>
+      </c>
+      <c r="N10">
+        <v>0.6930303999999998</v>
+      </c>
+      <c r="O10">
+        <v>0.1524666879999999</v>
+      </c>
+      <c r="P10">
+        <v>0.5405637119999999</v>
+      </c>
+      <c r="Q10">
+        <v>3.454563712</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1367559307490834</v>
+      </c>
+      <c r="T10">
+        <v>0.8081038804703722</v>
+      </c>
+      <c r="U10">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V10">
+        <v>0.22</v>
+      </c>
+      <c r="W10">
+        <v>0.04586400000000001</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>4.108183357731276</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1301466615458382</v>
+      </c>
+      <c r="C11">
+        <v>52.2234701432978</v>
+      </c>
+      <c r="D11">
+        <v>55.4094701432978</v>
+      </c>
+      <c r="E11">
+        <v>-34.934</v>
+      </c>
+      <c r="F11">
+        <v>4.266</v>
+      </c>
+      <c r="G11">
+        <v>1.08</v>
+      </c>
+      <c r="H11">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>3.83</v>
+      </c>
+      <c r="K11">
+        <v>2.914</v>
+      </c>
+      <c r="L11">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M11">
+        <v>0.2990466</v>
+      </c>
+      <c r="N11">
+        <v>0.6169533999999999</v>
+      </c>
+      <c r="O11">
+        <v>0.135729748</v>
+      </c>
+      <c r="P11">
+        <v>0.4812236519999999</v>
+      </c>
+      <c r="Q11">
+        <v>3.395223652</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1376105951053167</v>
+      </c>
+      <c r="T11">
+        <v>0.815154577426547</v>
+      </c>
+      <c r="U11">
+        <v>0.0701</v>
+      </c>
+      <c r="V11">
+        <v>0.22</v>
+      </c>
+      <c r="W11">
+        <v>0.054678</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>3.06306776268314</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1317650268025196</v>
+      </c>
+      <c r="C12">
+        <v>50.78488416451323</v>
+      </c>
+      <c r="D12">
+        <v>54.44488416451323</v>
+      </c>
+      <c r="E12">
+        <v>-34.46</v>
+      </c>
+      <c r="F12">
+        <v>4.740000000000001</v>
+      </c>
+      <c r="G12">
+        <v>1.08</v>
+      </c>
+      <c r="H12">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>3.83</v>
+      </c>
+      <c r="K12">
+        <v>2.914</v>
+      </c>
+      <c r="L12">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M12">
+        <v>0.4332360000000001</v>
+      </c>
+      <c r="N12">
+        <v>0.4827639999999998</v>
+      </c>
+      <c r="O12">
+        <v>0.1062080799999999</v>
+      </c>
+      <c r="P12">
+        <v>0.3765559199999999</v>
+      </c>
+      <c r="Q12">
+        <v>3.29055592</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1384842520027996</v>
+      </c>
+      <c r="T12">
+        <v>0.8223619565373033</v>
+      </c>
+      <c r="U12">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V12">
+        <v>0.22</v>
+      </c>
+      <c r="W12">
+        <v>0.07129200000000001</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>2.114321062884893</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1336985120592011</v>
+      </c>
+      <c r="C13">
+        <v>49.20161091512713</v>
+      </c>
+      <c r="D13">
+        <v>53.33561091512713</v>
+      </c>
+      <c r="E13">
+        <v>-33.986</v>
+      </c>
+      <c r="F13">
+        <v>5.214</v>
+      </c>
+      <c r="G13">
+        <v>1.08</v>
+      </c>
+      <c r="H13">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>3.83</v>
+      </c>
+      <c r="K13">
+        <v>2.914</v>
+      </c>
+      <c r="L13">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M13">
+        <v>0.5865750000000001</v>
+      </c>
+      <c r="N13">
+        <v>0.3294249999999999</v>
+      </c>
+      <c r="O13">
+        <v>0.07247349999999995</v>
+      </c>
+      <c r="P13">
+        <v>0.2569514999999999</v>
+      </c>
+      <c r="Q13">
+        <v>3.1709515</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1393775416395518</v>
+      </c>
+      <c r="T13">
+        <v>0.8297312992235824</v>
+      </c>
+      <c r="U13">
+        <v>0.1125</v>
+      </c>
+      <c r="V13">
+        <v>0.22</v>
+      </c>
+      <c r="W13">
+        <v>0.08775000000000001</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>1.561607637557004</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1432347494128753</v>
+      </c>
+      <c r="C14">
+        <v>43.85738287370126</v>
+      </c>
+      <c r="D14">
+        <v>48.46538287370127</v>
+      </c>
+      <c r="E14">
+        <v>-33.512</v>
+      </c>
+      <c r="F14">
+        <v>5.688000000000001</v>
+      </c>
+      <c r="G14">
+        <v>1.08</v>
+      </c>
+      <c r="H14">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>3.83</v>
+      </c>
+      <c r="K14">
+        <v>2.914</v>
+      </c>
+      <c r="L14">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M14">
+        <v>1.1182608</v>
+      </c>
+      <c r="N14">
+        <v>-0.2022608000000001</v>
+      </c>
+      <c r="O14">
+        <v>-0.04449737600000003</v>
+      </c>
+      <c r="P14">
+        <v>-0.1577634240000001</v>
+      </c>
+      <c r="Q14">
+        <v>2.756236576</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1407888934160503</v>
+      </c>
+      <c r="T14">
+        <v>0.8413744824241859</v>
+      </c>
+      <c r="U14">
+        <v>0.1966</v>
+      </c>
+      <c r="V14">
+        <v>0.1802084093442245</v>
+      </c>
+      <c r="W14">
+        <v>0.1611710267229255</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>0.8191291333828387</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1472083399933655</v>
+      </c>
+      <c r="C15">
+        <v>41.6069366253907</v>
+      </c>
+      <c r="D15">
+        <v>46.6889366253907</v>
+      </c>
+      <c r="E15">
+        <v>-33.038</v>
+      </c>
+      <c r="F15">
+        <v>6.162000000000001</v>
+      </c>
+      <c r="G15">
+        <v>1.08</v>
+      </c>
+      <c r="H15">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>3.83</v>
+      </c>
+      <c r="K15">
+        <v>2.914</v>
+      </c>
+      <c r="L15">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M15">
+        <v>1.3174356</v>
+      </c>
+      <c r="N15">
+        <v>-0.4014356000000001</v>
+      </c>
+      <c r="O15">
+        <v>-0.08831583200000001</v>
+      </c>
+      <c r="P15">
+        <v>-0.3131197680000001</v>
+      </c>
+      <c r="Q15">
+        <v>2.600880232</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1421446169961085</v>
+      </c>
+      <c r="T15">
+        <v>0.8525587514879607</v>
+      </c>
+      <c r="U15">
+        <v>0.2138</v>
+      </c>
+      <c r="V15">
+        <v>0.152963833678094</v>
+      </c>
+      <c r="W15">
+        <v>0.1810963323596235</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>0.6952901530822455</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1489583399933654</v>
+      </c>
+      <c r="C16">
+        <v>40.39122574721885</v>
+      </c>
+      <c r="D16">
+        <v>45.94722574721885</v>
+      </c>
+      <c r="E16">
+        <v>-32.564</v>
+      </c>
+      <c r="F16">
+        <v>6.636000000000001</v>
+      </c>
+      <c r="G16">
+        <v>1.08</v>
+      </c>
+      <c r="H16">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>3.83</v>
+      </c>
+      <c r="K16">
+        <v>2.914</v>
+      </c>
+      <c r="L16">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M16">
+        <v>1.4187768</v>
+      </c>
+      <c r="N16">
+        <v>-0.5027768000000001</v>
+      </c>
+      <c r="O16">
+        <v>-0.110610896</v>
+      </c>
+      <c r="P16">
+        <v>-0.3921659040000001</v>
+      </c>
+      <c r="Q16">
+        <v>2.521834096</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1433462985890865</v>
+      </c>
+      <c r="T16">
+        <v>0.8624722253424717</v>
+      </c>
+      <c r="U16">
+        <v>0.2138</v>
+      </c>
+      <c r="V16">
+        <v>0.1420378455582301</v>
+      </c>
+      <c r="W16">
+        <v>0.1834323086196504</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>0.6456265707192279</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1507083399933655</v>
+      </c>
+      <c r="C17">
+        <v>39.19871231861826</v>
+      </c>
+      <c r="D17">
+        <v>45.22871231861826</v>
+      </c>
+      <c r="E17">
+        <v>-32.09</v>
+      </c>
+      <c r="F17">
+        <v>7.11</v>
+      </c>
+      <c r="G17">
+        <v>1.08</v>
+      </c>
+      <c r="H17">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>3.83</v>
+      </c>
+      <c r="K17">
+        <v>2.914</v>
+      </c>
+      <c r="L17">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M17">
+        <v>1.520118</v>
+      </c>
+      <c r="N17">
+        <v>-0.6041180000000002</v>
+      </c>
+      <c r="O17">
+        <v>-0.13290596</v>
+      </c>
+      <c r="P17">
+        <v>-0.4712120400000002</v>
+      </c>
+      <c r="Q17">
+        <v>2.44278796</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1445762550430758</v>
+      </c>
+      <c r="T17">
+        <v>0.8726189574053245</v>
+      </c>
+      <c r="U17">
+        <v>0.2138</v>
+      </c>
+      <c r="V17">
+        <v>0.1325686558543481</v>
+      </c>
+      <c r="W17">
+        <v>0.1854568213783404</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>0.6025847993379461</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1524583399933654</v>
+      </c>
+      <c r="C18">
+        <v>38.02832482464112</v>
+      </c>
+      <c r="D18">
+        <v>44.53232482464112</v>
+      </c>
+      <c r="E18">
+        <v>-31.616</v>
+      </c>
+      <c r="F18">
+        <v>7.584000000000001</v>
+      </c>
+      <c r="G18">
+        <v>1.08</v>
+      </c>
+      <c r="H18">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>3.83</v>
+      </c>
+      <c r="K18">
+        <v>2.914</v>
+      </c>
+      <c r="L18">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M18">
+        <v>1.6214592</v>
+      </c>
+      <c r="N18">
+        <v>-0.7054592000000004</v>
+      </c>
+      <c r="O18">
+        <v>-0.1552010240000001</v>
+      </c>
+      <c r="P18">
+        <v>-0.5502581760000003</v>
+      </c>
+      <c r="Q18">
+        <v>2.363741824</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1458354961745409</v>
+      </c>
+      <c r="T18">
+        <v>0.8830072783268164</v>
+      </c>
+      <c r="U18">
+        <v>0.2138</v>
+      </c>
+      <c r="V18">
+        <v>0.1242831148634514</v>
+      </c>
+      <c r="W18">
+        <v>0.1872282700421941</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>0.5649232493793244</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1542083399933654</v>
+      </c>
+      <c r="C19">
+        <v>36.87905674221656</v>
+      </c>
+      <c r="D19">
+        <v>43.85705674221656</v>
+      </c>
+      <c r="E19">
+        <v>-31.142</v>
+      </c>
+      <c r="F19">
+        <v>8.058000000000002</v>
+      </c>
+      <c r="G19">
+        <v>1.08</v>
+      </c>
+      <c r="H19">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>3.83</v>
+      </c>
+      <c r="K19">
+        <v>2.914</v>
+      </c>
+      <c r="L19">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M19">
+        <v>1.7228004</v>
+      </c>
+      <c r="N19">
+        <v>-0.8068004000000004</v>
+      </c>
+      <c r="O19">
+        <v>-0.1774960880000001</v>
+      </c>
+      <c r="P19">
+        <v>-0.6293043120000004</v>
+      </c>
+      <c r="Q19">
+        <v>2.284695688</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1471250804658005</v>
+      </c>
+      <c r="T19">
+        <v>0.8936459202343684</v>
+      </c>
+      <c r="U19">
+        <v>0.2138</v>
+      </c>
+      <c r="V19">
+        <v>0.1169723434008954</v>
+      </c>
+      <c r="W19">
+        <v>0.1887913129808886</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>0.5316924700040699</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1559583399933655</v>
+      </c>
+      <c r="C20">
+        <v>35.74996168621604</v>
+      </c>
+      <c r="D20">
+        <v>43.20196168621604</v>
+      </c>
+      <c r="E20">
+        <v>-30.668</v>
+      </c>
+      <c r="F20">
+        <v>8.532</v>
+      </c>
+      <c r="G20">
+        <v>1.08</v>
+      </c>
+      <c r="H20">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>3.83</v>
+      </c>
+      <c r="K20">
+        <v>2.914</v>
+      </c>
+      <c r="L20">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M20">
+        <v>1.8241416</v>
+      </c>
+      <c r="N20">
+        <v>-0.9081416</v>
+      </c>
+      <c r="O20">
+        <v>-0.199791152</v>
+      </c>
+      <c r="P20">
+        <v>-0.708350448</v>
+      </c>
+      <c r="Q20">
+        <v>2.205649552</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1484461180324566</v>
+      </c>
+      <c r="T20">
+        <v>0.9045440412128363</v>
+      </c>
+      <c r="U20">
+        <v>0.2138</v>
+      </c>
+      <c r="V20">
+        <v>0.1104738798786234</v>
+      </c>
+      <c r="W20">
+        <v>0.1901806844819503</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>0.5021539994482884</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1626493112505986</v>
+      </c>
+      <c r="C21">
+        <v>32.94197144452901</v>
+      </c>
+      <c r="D21">
+        <v>40.86797144452901</v>
+      </c>
+      <c r="E21">
+        <v>-30.194</v>
+      </c>
+      <c r="F21">
+        <v>9.006000000000002</v>
+      </c>
+      <c r="G21">
+        <v>1.08</v>
+      </c>
+      <c r="H21">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>3.83</v>
+      </c>
+      <c r="K21">
+        <v>2.914</v>
+      </c>
+      <c r="L21">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M21">
+        <v>2.150632800000001</v>
+      </c>
+      <c r="N21">
+        <v>-1.234632800000001</v>
+      </c>
+      <c r="O21">
+        <v>-0.2716192160000002</v>
+      </c>
+      <c r="P21">
+        <v>-0.9630135840000007</v>
+      </c>
+      <c r="Q21">
+        <v>1.950986415999999</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1500355407948735</v>
+      </c>
+      <c r="T21">
+        <v>0.9176562508789065</v>
+      </c>
+      <c r="U21">
+        <v>0.2388</v>
+      </c>
+      <c r="V21">
+        <v>0.09370265347017857</v>
+      </c>
+      <c r="W21">
+        <v>0.2164238063513214</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>0.4259211521371754</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1646493112505986</v>
+      </c>
+      <c r="C22">
+        <v>31.81849675073191</v>
+      </c>
+      <c r="D22">
+        <v>40.21849675073192</v>
+      </c>
+      <c r="E22">
+        <v>-29.72</v>
+      </c>
+      <c r="F22">
+        <v>9.480000000000002</v>
+      </c>
+      <c r="G22">
+        <v>1.08</v>
+      </c>
+      <c r="H22">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>3.83</v>
+      </c>
+      <c r="K22">
+        <v>2.914</v>
+      </c>
+      <c r="L22">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M22">
+        <v>2.263824000000001</v>
+      </c>
+      <c r="N22">
+        <v>-1.347824000000001</v>
+      </c>
+      <c r="O22">
+        <v>-0.2965212800000001</v>
+      </c>
+      <c r="P22">
+        <v>-1.05130272</v>
+      </c>
+      <c r="Q22">
+        <v>1.86269728</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1514259850548094</v>
+      </c>
+      <c r="T22">
+        <v>0.9291269540148926</v>
+      </c>
+      <c r="U22">
+        <v>0.2388</v>
+      </c>
+      <c r="V22">
+        <v>0.08901752079666966</v>
+      </c>
+      <c r="W22">
+        <v>0.2175426160337553</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>0.4046250945303167</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1666493112505986</v>
+      </c>
+      <c r="C23">
+        <v>30.71534206296205</v>
+      </c>
+      <c r="D23">
+        <v>39.58934206296205</v>
+      </c>
+      <c r="E23">
+        <v>-29.246</v>
+      </c>
+      <c r="F23">
+        <v>9.954000000000001</v>
+      </c>
+      <c r="G23">
+        <v>1.08</v>
+      </c>
+      <c r="H23">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>3.83</v>
+      </c>
+      <c r="K23">
+        <v>2.914</v>
+      </c>
+      <c r="L23">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M23">
+        <v>2.3770152</v>
+      </c>
+      <c r="N23">
+        <v>-1.4610152</v>
+      </c>
+      <c r="O23">
+        <v>-0.321423344</v>
+      </c>
+      <c r="P23">
+        <v>-1.139591856</v>
+      </c>
+      <c r="Q23">
+        <v>1.774408144</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.15285163043525</v>
+      </c>
+      <c r="T23">
+        <v>0.9408880546986255</v>
+      </c>
+      <c r="U23">
+        <v>0.2388</v>
+      </c>
+      <c r="V23">
+        <v>0.08477859123492351</v>
+      </c>
+      <c r="W23">
+        <v>0.2185548724131003</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>0.385357232886016</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1686493112505986</v>
+      </c>
+      <c r="C24">
+        <v>29.63156844642652</v>
+      </c>
+      <c r="D24">
+        <v>38.97956844642652</v>
+      </c>
+      <c r="E24">
+        <v>-28.772</v>
+      </c>
+      <c r="F24">
+        <v>10.428</v>
+      </c>
+      <c r="G24">
+        <v>1.08</v>
+      </c>
+      <c r="H24">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>3.83</v>
+      </c>
+      <c r="K24">
+        <v>2.914</v>
+      </c>
+      <c r="L24">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M24">
+        <v>2.4902064</v>
+      </c>
+      <c r="N24">
+        <v>-1.5742064</v>
+      </c>
+      <c r="O24">
+        <v>-0.3463254080000001</v>
+      </c>
+      <c r="P24">
+        <v>-1.227880992</v>
+      </c>
+      <c r="Q24">
+        <v>1.686119008</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1543138308254455</v>
+      </c>
+      <c r="T24">
+        <v>0.9529507220665567</v>
+      </c>
+      <c r="U24">
+        <v>0.2388</v>
+      </c>
+      <c r="V24">
+        <v>0.08092501890606334</v>
+      </c>
+      <c r="W24">
+        <v>0.2194751054852321</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>0.3678409950275607</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1706493112505986</v>
+      </c>
+      <c r="C25">
+        <v>28.56629393650753</v>
+      </c>
+      <c r="D25">
+        <v>38.38829393650754</v>
+      </c>
+      <c r="E25">
+        <v>-28.298</v>
+      </c>
+      <c r="F25">
+        <v>10.902</v>
+      </c>
+      <c r="G25">
+        <v>1.08</v>
+      </c>
+      <c r="H25">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>3.83</v>
+      </c>
+      <c r="K25">
+        <v>2.914</v>
+      </c>
+      <c r="L25">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M25">
+        <v>2.603397600000001</v>
+      </c>
+      <c r="N25">
+        <v>-1.687397600000001</v>
+      </c>
+      <c r="O25">
+        <v>-0.3712274720000001</v>
+      </c>
+      <c r="P25">
+        <v>-1.316170128</v>
+      </c>
+      <c r="Q25">
+        <v>1.597829872</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1558140104465552</v>
+      </c>
+      <c r="T25">
+        <v>0.9653267054700184</v>
+      </c>
+      <c r="U25">
+        <v>0.2388</v>
+      </c>
+      <c r="V25">
+        <v>0.07740653982319103</v>
+      </c>
+      <c r="W25">
+        <v>0.220315318290222</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>0.3518479082872319</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1726493112505986</v>
+      </c>
+      <c r="C26">
+        <v>27.51868928247035</v>
+      </c>
+      <c r="D26">
+        <v>37.81468928247035</v>
+      </c>
+      <c r="E26">
+        <v>-27.824</v>
+      </c>
+      <c r="F26">
+        <v>11.376</v>
+      </c>
+      <c r="G26">
+        <v>1.08</v>
+      </c>
+      <c r="H26">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>3.83</v>
+      </c>
+      <c r="K26">
+        <v>2.914</v>
+      </c>
+      <c r="L26">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M26">
+        <v>2.7165888</v>
+      </c>
+      <c r="N26">
+        <v>-1.8005888</v>
+      </c>
+      <c r="O26">
+        <v>-0.396129536</v>
+      </c>
+      <c r="P26">
+        <v>-1.404459264</v>
+      </c>
+      <c r="Q26">
+        <v>1.509540736</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1573536684787467</v>
+      </c>
+      <c r="T26">
+        <v>0.9780283726472555</v>
+      </c>
+      <c r="U26">
+        <v>0.2388</v>
+      </c>
+      <c r="V26">
+        <v>0.07418126733055806</v>
+      </c>
+      <c r="W26">
+        <v>0.2210855133614627</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>0.337187578775264</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1746493112505986</v>
+      </c>
+      <c r="C27">
+        <v>26.48797406714306</v>
+      </c>
+      <c r="D27">
+        <v>37.25797406714307</v>
+      </c>
+      <c r="E27">
+        <v>-27.35</v>
+      </c>
+      <c r="F27">
+        <v>11.85</v>
+      </c>
+      <c r="G27">
+        <v>1.08</v>
+      </c>
+      <c r="H27">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>3.83</v>
+      </c>
+      <c r="K27">
+        <v>2.914</v>
+      </c>
+      <c r="L27">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M27">
+        <v>2.82978</v>
+      </c>
+      <c r="N27">
+        <v>-1.91378</v>
+      </c>
+      <c r="O27">
+        <v>-0.4210316000000001</v>
+      </c>
+      <c r="P27">
+        <v>-1.4927484</v>
+      </c>
+      <c r="Q27">
+        <v>1.4212516</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1589343840584634</v>
+      </c>
+      <c r="T27">
+        <v>0.9910687509492189</v>
+      </c>
+      <c r="U27">
+        <v>0.2388</v>
+      </c>
+      <c r="V27">
+        <v>0.07121401663733574</v>
+      </c>
+      <c r="W27">
+        <v>0.2217940928270042</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>0.3237000756242534</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1766493112505986</v>
+      </c>
+      <c r="C28">
+        <v>25.47341316438439</v>
+      </c>
+      <c r="D28">
+        <v>36.71741316438439</v>
+      </c>
+      <c r="E28">
+        <v>-26.876</v>
+      </c>
+      <c r="F28">
+        <v>12.324</v>
+      </c>
+      <c r="G28">
+        <v>1.08</v>
+      </c>
+      <c r="H28">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>3.83</v>
+      </c>
+      <c r="K28">
+        <v>2.914</v>
+      </c>
+      <c r="L28">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M28">
+        <v>2.942971200000001</v>
+      </c>
+      <c r="N28">
+        <v>-2.026971200000001</v>
+      </c>
+      <c r="O28">
+        <v>-0.4459336640000001</v>
+      </c>
+      <c r="P28">
+        <v>-1.581037536000001</v>
+      </c>
+      <c r="Q28">
+        <v>1.332962464</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.160557821680875</v>
+      </c>
+      <c r="T28">
+        <v>1.004461571907992</v>
+      </c>
+      <c r="U28">
+        <v>0.2388</v>
+      </c>
+      <c r="V28">
+        <v>0.06847501599743822</v>
+      </c>
+      <c r="W28">
+        <v>0.2224481661798118</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>0.3112500727156282</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1786493112505986</v>
+      </c>
+      <c r="C29">
+        <v>24.47431350052419</v>
+      </c>
+      <c r="D29">
+        <v>36.19231350052419</v>
+      </c>
+      <c r="E29">
+        <v>-26.402</v>
+      </c>
+      <c r="F29">
+        <v>12.798</v>
+      </c>
+      <c r="G29">
+        <v>1.08</v>
+      </c>
+      <c r="H29">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>3.83</v>
+      </c>
+      <c r="K29">
+        <v>2.914</v>
+      </c>
+      <c r="L29">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M29">
+        <v>3.056162400000001</v>
+      </c>
+      <c r="N29">
+        <v>-2.140162400000001</v>
+      </c>
+      <c r="O29">
+        <v>-0.4708357280000001</v>
+      </c>
+      <c r="P29">
+        <v>-1.669326672000001</v>
+      </c>
+      <c r="Q29">
+        <v>1.244673328</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1622257370463664</v>
+      </c>
+      <c r="T29">
+        <v>1.018221319468376</v>
+      </c>
+      <c r="U29">
+        <v>0.2388</v>
+      </c>
+      <c r="V29">
+        <v>0.06593890429382938</v>
+      </c>
+      <c r="W29">
+        <v>0.2230537896546335</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.2997222922446791</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1806493112505986</v>
+      </c>
+      <c r="C30">
+        <v>23.49002108977593</v>
+      </c>
+      <c r="D30">
+        <v>35.68202108977594</v>
+      </c>
+      <c r="E30">
+        <v>-25.928</v>
+      </c>
+      <c r="F30">
+        <v>13.272</v>
+      </c>
+      <c r="G30">
+        <v>1.08</v>
+      </c>
+      <c r="H30">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>3.83</v>
+      </c>
+      <c r="K30">
+        <v>2.914</v>
+      </c>
+      <c r="L30">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M30">
+        <v>3.1693536</v>
+      </c>
+      <c r="N30">
+        <v>-2.253353600000001</v>
+      </c>
+      <c r="O30">
+        <v>-0.4957377920000001</v>
+      </c>
+      <c r="P30">
+        <v>-1.757615808</v>
+      </c>
+      <c r="Q30">
+        <v>1.156384192</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1639399833942327</v>
+      </c>
+      <c r="T30">
+        <v>1.03236328223877</v>
+      </c>
+      <c r="U30">
+        <v>0.2388</v>
+      </c>
+      <c r="V30">
+        <v>0.06358394342619263</v>
+      </c>
+      <c r="W30">
+        <v>0.2236161543098252</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.2890179246645119</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1826493112505986</v>
+      </c>
+      <c r="C31">
+        <v>22.51991831695674</v>
+      </c>
+      <c r="D31">
+        <v>35.18591831695674</v>
+      </c>
+      <c r="E31">
+        <v>-25.454</v>
+      </c>
+      <c r="F31">
+        <v>13.746</v>
+      </c>
+      <c r="G31">
+        <v>1.08</v>
+      </c>
+      <c r="H31">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>3.83</v>
+      </c>
+      <c r="K31">
+        <v>2.914</v>
+      </c>
+      <c r="L31">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M31">
+        <v>3.2825448</v>
+      </c>
+      <c r="N31">
+        <v>-2.3665448</v>
+      </c>
+      <c r="O31">
+        <v>-0.520639856</v>
+      </c>
+      <c r="P31">
+        <v>-1.845904944</v>
+      </c>
+      <c r="Q31">
+        <v>1.068095056</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1657025183716162</v>
+      </c>
+      <c r="T31">
+        <v>1.046903610157626</v>
+      </c>
+      <c r="U31">
+        <v>0.2388</v>
+      </c>
+      <c r="V31">
+        <v>0.06139139365287564</v>
+      </c>
+      <c r="W31">
+        <v>0.2241397351956933</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.279051789331253</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1846493112505986</v>
+      </c>
+      <c r="C32">
+        <v>21.56342144377646</v>
+      </c>
+      <c r="D32">
+        <v>34.70342144377646</v>
+      </c>
+      <c r="E32">
+        <v>-24.98</v>
+      </c>
+      <c r="F32">
+        <v>14.22</v>
+      </c>
+      <c r="G32">
+        <v>1.08</v>
+      </c>
+      <c r="H32">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>3.83</v>
+      </c>
+      <c r="K32">
+        <v>2.914</v>
+      </c>
+      <c r="L32">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M32">
+        <v>3.395736</v>
+      </c>
+      <c r="N32">
+        <v>-2.479736</v>
+      </c>
+      <c r="O32">
+        <v>-0.54554192</v>
+      </c>
+      <c r="P32">
+        <v>-1.93419408</v>
+      </c>
+      <c r="Q32">
+        <v>0.9798059199999998</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1675154114912107</v>
+      </c>
+      <c r="T32">
+        <v>1.06185937601702</v>
+      </c>
+      <c r="U32">
+        <v>0.2388</v>
+      </c>
+      <c r="V32">
+        <v>0.05934501386444646</v>
+      </c>
+      <c r="W32">
+        <v>0.2246284106891702</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.2697500630202112</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1866493112505986</v>
+      </c>
+      <c r="C33">
+        <v>20.61997831752536</v>
+      </c>
+      <c r="D33">
+        <v>34.23397831752536</v>
+      </c>
+      <c r="E33">
+        <v>-24.506</v>
+      </c>
+      <c r="F33">
+        <v>14.694</v>
+      </c>
+      <c r="G33">
+        <v>1.08</v>
+      </c>
+      <c r="H33">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>3.83</v>
+      </c>
+      <c r="K33">
+        <v>2.914</v>
+      </c>
+      <c r="L33">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M33">
+        <v>3.5089272</v>
+      </c>
+      <c r="N33">
+        <v>-2.592927200000001</v>
+      </c>
+      <c r="O33">
+        <v>-0.5704439840000001</v>
+      </c>
+      <c r="P33">
+        <v>-2.022483216</v>
+      </c>
+      <c r="Q33">
+        <v>0.8915167839999998</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1693808522374602</v>
+      </c>
+      <c r="T33">
+        <v>1.077248642336107</v>
+      </c>
+      <c r="U33">
+        <v>0.2388</v>
+      </c>
+      <c r="V33">
+        <v>0.05743065857849657</v>
+      </c>
+      <c r="W33">
+        <v>0.225085558731455</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.2610484480840753</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1886493112505986</v>
+      </c>
+      <c r="C34">
+        <v>19.68906626325138</v>
+      </c>
+      <c r="D34">
+        <v>33.77706626325138</v>
+      </c>
+      <c r="E34">
+        <v>-24.032</v>
+      </c>
+      <c r="F34">
+        <v>15.168</v>
+      </c>
+      <c r="G34">
+        <v>1.08</v>
+      </c>
+      <c r="H34">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>3.83</v>
+      </c>
+      <c r="K34">
+        <v>2.914</v>
+      </c>
+      <c r="L34">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M34">
+        <v>3.622118400000001</v>
+      </c>
+      <c r="N34">
+        <v>-2.706118400000001</v>
+      </c>
+      <c r="O34">
+        <v>-0.5953460480000001</v>
+      </c>
+      <c r="P34">
+        <v>-2.110772352000001</v>
+      </c>
+      <c r="Q34">
+        <v>0.8032276479999991</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1713011588880111</v>
+      </c>
+      <c r="T34">
+        <v>1.093090534135168</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>0.05563595049791854</v>
+      </c>
+      <c r="W34">
+        <v>0.225514135021097</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.2528906840814479</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1906493112505986</v>
+      </c>
+      <c r="C35">
+        <v>18.77019014250943</v>
+      </c>
+      <c r="D35">
+        <v>33.33219014250943</v>
+      </c>
+      <c r="E35">
+        <v>-23.558</v>
+      </c>
+      <c r="F35">
+        <v>15.642</v>
+      </c>
+      <c r="G35">
+        <v>1.08</v>
+      </c>
+      <c r="H35">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>3.83</v>
+      </c>
+      <c r="K35">
+        <v>2.914</v>
+      </c>
+      <c r="L35">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M35">
+        <v>3.735309600000001</v>
+      </c>
+      <c r="N35">
+        <v>-2.819309600000001</v>
+      </c>
+      <c r="O35">
+        <v>-0.6202481120000001</v>
+      </c>
+      <c r="P35">
+        <v>-2.199061488000001</v>
+      </c>
+      <c r="Q35">
+        <v>0.7149385119999994</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1732787881251455</v>
+      </c>
+      <c r="T35">
+        <v>1.109405318226738</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>0.05395001260404222</v>
+      </c>
+      <c r="W35">
+        <v>0.2259167369901547</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.2452273300183738</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1926493112505986</v>
+      </c>
+      <c r="C36">
+        <v>17.86288056352514</v>
+      </c>
+      <c r="D36">
+        <v>32.89888056352515</v>
+      </c>
+      <c r="E36">
+        <v>-23.084</v>
+      </c>
+      <c r="F36">
+        <v>16.116</v>
+      </c>
+      <c r="G36">
+        <v>1.08</v>
+      </c>
+      <c r="H36">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>3.83</v>
+      </c>
+      <c r="K36">
+        <v>2.914</v>
+      </c>
+      <c r="L36">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M36">
+        <v>3.848500800000001</v>
+      </c>
+      <c r="N36">
+        <v>-2.932500800000001</v>
+      </c>
+      <c r="O36">
+        <v>-0.6451501760000001</v>
+      </c>
+      <c r="P36">
+        <v>-2.287350624000001</v>
+      </c>
+      <c r="Q36">
+        <v>0.6266493759999991</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1753163455209811</v>
+      </c>
+      <c r="T36">
+        <v>1.126214489715022</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>0.05236324752745274</v>
+      </c>
+      <c r="W36">
+        <v>0.2262956564904443</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.2380147614884216</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1946493112505986</v>
+      </c>
+      <c r="C37">
+        <v>16.96669222917151</v>
+      </c>
+      <c r="D37">
+        <v>32.47669222917152</v>
+      </c>
+      <c r="E37">
+        <v>-22.61</v>
+      </c>
+      <c r="F37">
+        <v>16.59</v>
+      </c>
+      <c r="G37">
+        <v>1.08</v>
+      </c>
+      <c r="H37">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>3.83</v>
+      </c>
+      <c r="K37">
+        <v>2.914</v>
+      </c>
+      <c r="L37">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M37">
+        <v>3.961692000000001</v>
+      </c>
+      <c r="N37">
+        <v>-3.045692000000001</v>
+      </c>
+      <c r="O37">
+        <v>-0.6700522400000002</v>
+      </c>
+      <c r="P37">
+        <v>-2.375639760000001</v>
+      </c>
+      <c r="Q37">
+        <v>0.5383602399999989</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1774165969905347</v>
+      </c>
+      <c r="T37">
+        <v>1.143540866479868</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>0.05086715474095409</v>
+      </c>
+      <c r="W37">
+        <v>0.2266529234478602</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.2312143397316095</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1966493112505986</v>
+      </c>
+      <c r="C38">
+        <v>16.08120241053542</v>
+      </c>
+      <c r="D38">
+        <v>32.06520241053542</v>
+      </c>
+      <c r="E38">
+        <v>-22.136</v>
+      </c>
+      <c r="F38">
+        <v>17.064</v>
+      </c>
+      <c r="G38">
+        <v>1.08</v>
+      </c>
+      <c r="H38">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>3.83</v>
+      </c>
+      <c r="K38">
+        <v>2.914</v>
+      </c>
+      <c r="L38">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M38">
+        <v>4.0748832</v>
+      </c>
+      <c r="N38">
+        <v>-3.1588832</v>
+      </c>
+      <c r="O38">
+        <v>-0.694954304</v>
+      </c>
+      <c r="P38">
+        <v>-2.463928896000001</v>
+      </c>
+      <c r="Q38">
+        <v>0.4500711039999996</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1795824813185118</v>
+      </c>
+      <c r="T38">
+        <v>1.161408692518616</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>0.04945417822037204</v>
+      </c>
+      <c r="W38">
+        <v>0.2269903422409752</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.2247917191835093</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1986493112505986</v>
+      </c>
+      <c r="C39">
+        <v>15.20600953507453</v>
+      </c>
+      <c r="D39">
+        <v>31.66400953507452</v>
+      </c>
+      <c r="E39">
+        <v>-21.662</v>
+      </c>
+      <c r="F39">
+        <v>17.538</v>
+      </c>
+      <c r="G39">
+        <v>1.08</v>
+      </c>
+      <c r="H39">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>3.83</v>
+      </c>
+      <c r="K39">
+        <v>2.914</v>
+      </c>
+      <c r="L39">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M39">
+        <v>4.188074400000001</v>
+      </c>
+      <c r="N39">
+        <v>-3.272074400000001</v>
+      </c>
+      <c r="O39">
+        <v>-0.7198563680000001</v>
+      </c>
+      <c r="P39">
+        <v>-2.552218032000001</v>
+      </c>
+      <c r="Q39">
+        <v>0.3617819679999994</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.181817123879123</v>
+      </c>
+      <c r="T39">
+        <v>1.179843751130023</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>0.04811757880901064</v>
+      </c>
+      <c r="W39">
+        <v>0.2273095221804083</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.2187162673136848</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.2006493112505986</v>
+      </c>
+      <c r="C40">
+        <v>14.34073187945264</v>
+      </c>
+      <c r="D40">
+        <v>31.27273187945265</v>
+      </c>
+      <c r="E40">
+        <v>-21.188</v>
+      </c>
+      <c r="F40">
+        <v>18.012</v>
+      </c>
+      <c r="G40">
+        <v>1.08</v>
+      </c>
+      <c r="H40">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>3.83</v>
+      </c>
+      <c r="K40">
+        <v>2.914</v>
+      </c>
+      <c r="L40">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M40">
+        <v>4.301265600000002</v>
+      </c>
+      <c r="N40">
+        <v>-3.385265600000002</v>
+      </c>
+      <c r="O40">
+        <v>-0.7447584320000002</v>
+      </c>
+      <c r="P40">
+        <v>-2.640507168000001</v>
+      </c>
+      <c r="Q40">
+        <v>0.2734928319999987</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.184123851683625</v>
+      </c>
+      <c r="T40">
+        <v>1.198873489051475</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>0.04685132673508929</v>
+      </c>
+      <c r="W40">
+        <v>0.2276119031756607</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.2129605760685878</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.2026493112505986</v>
+      </c>
+      <c r="C41">
+        <v>13.48500635810916</v>
+      </c>
+      <c r="D41">
+        <v>30.89100635810917</v>
+      </c>
+      <c r="E41">
+        <v>-20.714</v>
+      </c>
+      <c r="F41">
+        <v>18.486</v>
+      </c>
+      <c r="G41">
+        <v>1.08</v>
+      </c>
+      <c r="H41">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>3.83</v>
+      </c>
+      <c r="K41">
+        <v>2.914</v>
+      </c>
+      <c r="L41">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M41">
+        <v>4.414456800000001</v>
+      </c>
+      <c r="N41">
+        <v>-3.498456800000001</v>
+      </c>
+      <c r="O41">
+        <v>-0.7696604960000001</v>
+      </c>
+      <c r="P41">
+        <v>-2.728796304000001</v>
+      </c>
+      <c r="Q41">
+        <v>0.1852036959999994</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1865062099079468</v>
+      </c>
+      <c r="T41">
+        <v>1.218527152806417</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>0.04565001066495881</v>
+      </c>
+      <c r="W41">
+        <v>0.2278987774532079</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.2075000484770855</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.2046493112505986</v>
+      </c>
+      <c r="C42">
+        <v>12.63848739948132</v>
+      </c>
+      <c r="D42">
+        <v>30.51848739948132</v>
+      </c>
+      <c r="E42">
+        <v>-20.24</v>
+      </c>
+      <c r="F42">
+        <v>18.96</v>
+      </c>
+      <c r="G42">
+        <v>1.08</v>
+      </c>
+      <c r="H42">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>3.83</v>
+      </c>
+      <c r="K42">
+        <v>2.914</v>
+      </c>
+      <c r="L42">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M42">
+        <v>4.527648000000001</v>
+      </c>
+      <c r="N42">
+        <v>-3.611648000000001</v>
+      </c>
+      <c r="O42">
+        <v>-0.7945625600000001</v>
+      </c>
+      <c r="P42">
+        <v>-2.817085440000001</v>
+      </c>
+      <c r="Q42">
+        <v>0.09691455999999921</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1889679800730792</v>
+      </c>
+      <c r="T42">
+        <v>1.238835938686524</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>0.04450876039833483</v>
+      </c>
+      <c r="W42">
+        <v>0.2281713080168777</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.2023125472651583</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.2066493112505986</v>
+      </c>
+      <c r="C43">
+        <v>11.80084590256845</v>
+      </c>
+      <c r="D43">
+        <v>30.15484590256845</v>
+      </c>
+      <c r="E43">
+        <v>-19.766</v>
+      </c>
+      <c r="F43">
+        <v>19.434</v>
+      </c>
+      <c r="G43">
+        <v>1.08</v>
+      </c>
+      <c r="H43">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>3.83</v>
+      </c>
+      <c r="K43">
+        <v>2.914</v>
+      </c>
+      <c r="L43">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M43">
+        <v>4.640839200000001</v>
+      </c>
+      <c r="N43">
+        <v>-3.724839200000001</v>
+      </c>
+      <c r="O43">
+        <v>-0.8194646240000002</v>
+      </c>
+      <c r="P43">
+        <v>-2.905374576000001</v>
+      </c>
+      <c r="Q43">
+        <v>0.008625423999998993</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1915132000743178</v>
+      </c>
+      <c r="T43">
+        <v>1.259833157986295</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>0.04342318087642422</v>
+      </c>
+      <c r="W43">
+        <v>0.2284305444067099</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.1973780948928374</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.2086493112505986</v>
+      </c>
+      <c r="C44">
+        <v>10.97176826721581</v>
+      </c>
+      <c r="D44">
+        <v>29.79976826721581</v>
+      </c>
+      <c r="E44">
+        <v>-19.292</v>
+      </c>
+      <c r="F44">
+        <v>19.908</v>
+      </c>
+      <c r="G44">
+        <v>1.08</v>
+      </c>
+      <c r="H44">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>3.83</v>
+      </c>
+      <c r="K44">
+        <v>2.914</v>
+      </c>
+      <c r="L44">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M44">
+        <v>4.7540304</v>
+      </c>
+      <c r="N44">
+        <v>-3.838030400000001</v>
+      </c>
+      <c r="O44">
+        <v>-0.844366688</v>
+      </c>
+      <c r="P44">
+        <v>-2.993663712</v>
+      </c>
+      <c r="Q44">
+        <v>-0.07966371200000033</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1941461862824957</v>
+      </c>
+      <c r="T44">
+        <v>1.281554419330887</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0.04238929561746176</v>
+      </c>
+      <c r="W44">
+        <v>0.2286774362065501</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.192678616443008</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.2106493112505986</v>
+      </c>
+      <c r="C45">
+        <v>10.15095549211238</v>
+      </c>
+      <c r="D45">
+        <v>29.45295549211238</v>
+      </c>
+      <c r="E45">
+        <v>-18.818</v>
+      </c>
+      <c r="F45">
+        <v>20.382</v>
+      </c>
+      <c r="G45">
+        <v>1.08</v>
+      </c>
+      <c r="H45">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>3.83</v>
+      </c>
+      <c r="K45">
+        <v>2.914</v>
+      </c>
+      <c r="L45">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M45">
+        <v>4.867221600000001</v>
+      </c>
+      <c r="N45">
+        <v>-3.951221600000001</v>
+      </c>
+      <c r="O45">
+        <v>-0.8692687520000001</v>
+      </c>
+      <c r="P45">
+        <v>-3.081952848000001</v>
+      </c>
+      <c r="Q45">
+        <v>-0.1679528480000005</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1968715579716623</v>
+      </c>
+      <c r="T45">
+        <v>1.304037830196341</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0.04140349804496264</v>
+      </c>
+      <c r="W45">
+        <v>0.2289128446668629</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.1881977183861938</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.2126493112505986</v>
+      </c>
+      <c r="C46">
+        <v>9.33812233504964</v>
+      </c>
+      <c r="D46">
+        <v>29.11412233504964</v>
+      </c>
+      <c r="E46">
+        <v>-18.344</v>
+      </c>
+      <c r="F46">
+        <v>20.856</v>
+      </c>
+      <c r="G46">
+        <v>1.08</v>
+      </c>
+      <c r="H46">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>3.83</v>
+      </c>
+      <c r="K46">
+        <v>2.914</v>
+      </c>
+      <c r="L46">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M46">
+        <v>4.980412800000001</v>
+      </c>
+      <c r="N46">
+        <v>-4.064412800000001</v>
+      </c>
+      <c r="O46">
+        <v>-0.8941708160000001</v>
+      </c>
+      <c r="P46">
+        <v>-3.170241984000001</v>
+      </c>
+      <c r="Q46">
+        <v>-0.2562419840000012</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1996942643640134</v>
+      </c>
+      <c r="T46">
+        <v>1.327324220021275</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0.04046250945303167</v>
+      </c>
+      <c r="W46">
+        <v>0.229137552742616</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.1839204975137803</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.2146493112505986</v>
+      </c>
+      <c r="C47">
+        <v>8.532996530484393</v>
+      </c>
+      <c r="D47">
+        <v>28.78299653048439</v>
+      </c>
+      <c r="E47">
+        <v>-17.87</v>
+      </c>
+      <c r="F47">
+        <v>21.33</v>
+      </c>
+      <c r="G47">
+        <v>1.08</v>
+      </c>
+      <c r="H47">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>3.83</v>
+      </c>
+      <c r="K47">
+        <v>2.914</v>
+      </c>
+      <c r="L47">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M47">
+        <v>5.093604000000001</v>
+      </c>
+      <c r="N47">
+        <v>-4.177604000000001</v>
+      </c>
+      <c r="O47">
+        <v>-0.91907288</v>
+      </c>
+      <c r="P47">
+        <v>-3.258531120000001</v>
+      </c>
+      <c r="Q47">
+        <v>-0.3445311200000005</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.2026196146251773</v>
+      </c>
+      <c r="T47">
+        <v>1.351457387658026</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0.03956334257629763</v>
+      </c>
+      <c r="W47">
+        <v>0.2293522737927801</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.1798333753468075</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.2166493112505986</v>
+      </c>
+      <c r="C48">
+        <v>7.735318059895</v>
+      </c>
+      <c r="D48">
+        <v>28.459318059895</v>
+      </c>
+      <c r="E48">
+        <v>-17.396</v>
+      </c>
+      <c r="F48">
+        <v>21.804</v>
+      </c>
+      <c r="G48">
+        <v>1.08</v>
+      </c>
+      <c r="H48">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>3.83</v>
+      </c>
+      <c r="K48">
+        <v>2.914</v>
+      </c>
+      <c r="L48">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M48">
+        <v>5.206795200000001</v>
+      </c>
+      <c r="N48">
+        <v>-4.290795200000002</v>
+      </c>
+      <c r="O48">
+        <v>-0.9439749440000003</v>
+      </c>
+      <c r="P48">
+        <v>-3.346820256000001</v>
+      </c>
+      <c r="Q48">
+        <v>-0.4328202560000012</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.2056533111923102</v>
+      </c>
+      <c r="T48">
+        <v>1.37648437631836</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.03870326991159551</v>
+      </c>
+      <c r="W48">
+        <v>0.229557659145111</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.1759239541436158</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.2186493112505986</v>
+      </c>
+      <c r="C49">
+        <v>6.944838470821232</v>
+      </c>
+      <c r="D49">
+        <v>28.14283847082124</v>
+      </c>
+      <c r="E49">
+        <v>-16.922</v>
+      </c>
+      <c r="F49">
+        <v>22.27800000000001</v>
+      </c>
+      <c r="G49">
+        <v>1.08</v>
+      </c>
+      <c r="H49">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>3.83</v>
+      </c>
+      <c r="K49">
+        <v>2.914</v>
+      </c>
+      <c r="L49">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M49">
+        <v>5.319986400000001</v>
+      </c>
+      <c r="N49">
+        <v>-4.403986400000001</v>
+      </c>
+      <c r="O49">
+        <v>-0.9688770080000001</v>
+      </c>
+      <c r="P49">
+        <v>-3.435109392000001</v>
+      </c>
+      <c r="Q49">
+        <v>-0.5211093920000005</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.208801486875184</v>
+      </c>
+      <c r="T49">
+        <v>1.402455779645121</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.03787979608368922</v>
+      </c>
+      <c r="W49">
+        <v>0.229754304695215</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.1721808912894965</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.2206493112505986</v>
+      </c>
+      <c r="C50">
+        <v>6.161320240839721</v>
+      </c>
+      <c r="D50">
+        <v>27.83332024083973</v>
+      </c>
+      <c r="E50">
+        <v>-16.448</v>
+      </c>
+      <c r="F50">
+        <v>22.752</v>
+      </c>
+      <c r="G50">
+        <v>1.08</v>
+      </c>
+      <c r="H50">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>3.83</v>
+      </c>
+      <c r="K50">
+        <v>2.914</v>
+      </c>
+      <c r="L50">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M50">
+        <v>5.4331776</v>
+      </c>
+      <c r="N50">
+        <v>-4.5171776</v>
+      </c>
+      <c r="O50">
+        <v>-0.9937790719999999</v>
+      </c>
+      <c r="P50">
+        <v>-3.523398528</v>
+      </c>
+      <c r="Q50">
+        <v>-0.6093985280000003</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.2120707462381683</v>
+      </c>
+      <c r="T50">
+        <v>1.429426083099835</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.03709063366527903</v>
+      </c>
+      <c r="W50">
+        <v>0.2299427566807314</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.168593789387632</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.2226493112505986</v>
+      </c>
+      <c r="C51">
+        <v>5.384536183053388</v>
+      </c>
+      <c r="D51">
+        <v>27.53053618305339</v>
+      </c>
+      <c r="E51">
+        <v>-15.974</v>
+      </c>
+      <c r="F51">
+        <v>23.226</v>
+      </c>
+      <c r="G51">
+        <v>1.08</v>
+      </c>
+      <c r="H51">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>3.83</v>
+      </c>
+      <c r="K51">
+        <v>2.914</v>
+      </c>
+      <c r="L51">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M51">
+        <v>5.546368800000001</v>
+      </c>
+      <c r="N51">
+        <v>-4.630368800000001</v>
+      </c>
+      <c r="O51">
+        <v>-1.018681136</v>
+      </c>
+      <c r="P51">
+        <v>-3.611687664000001</v>
+      </c>
+      <c r="Q51">
+        <v>-0.6976876640000009</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.2154682118506814</v>
+      </c>
+      <c r="T51">
+        <v>1.457454045513557</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.03633368195782436</v>
+      </c>
+      <c r="W51">
+        <v>0.2301235167484716</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.1651530998082925</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.2246493112505986</v>
+      </c>
+      <c r="C52">
+        <v>4.61426888996742</v>
+      </c>
+      <c r="D52">
+        <v>27.23426888996742</v>
+      </c>
+      <c r="E52">
+        <v>-15.5</v>
+      </c>
+      <c r="F52">
+        <v>23.7</v>
+      </c>
+      <c r="G52">
+        <v>1.08</v>
+      </c>
+      <c r="H52">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>3.83</v>
+      </c>
+      <c r="K52">
+        <v>2.914</v>
+      </c>
+      <c r="L52">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M52">
+        <v>5.659560000000001</v>
+      </c>
+      <c r="N52">
+        <v>-4.74356</v>
+      </c>
+      <c r="O52">
+        <v>-1.0435832</v>
+      </c>
+      <c r="P52">
+        <v>-3.6999768</v>
+      </c>
+      <c r="Q52">
+        <v>-0.7859768000000003</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.219001576087695</v>
+      </c>
+      <c r="T52">
+        <v>1.486603126423828</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.03560700831866787</v>
+      </c>
+      <c r="W52">
+        <v>0.2302970464135021</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.1618500378121268</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.2266493112505986</v>
+      </c>
+      <c r="C53">
+        <v>3.850310212891028</v>
+      </c>
+      <c r="D53">
+        <v>26.94431021289103</v>
+      </c>
+      <c r="E53">
+        <v>-15.026</v>
+      </c>
+      <c r="F53">
+        <v>24.174</v>
+      </c>
+      <c r="G53">
+        <v>1.08</v>
+      </c>
+      <c r="H53">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>3.83</v>
+      </c>
+      <c r="K53">
+        <v>2.914</v>
+      </c>
+      <c r="L53">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M53">
+        <v>5.772751200000001</v>
+      </c>
+      <c r="N53">
+        <v>-4.856751200000001</v>
+      </c>
+      <c r="O53">
+        <v>-1.068485264</v>
+      </c>
+      <c r="P53">
+        <v>-3.788265936000001</v>
+      </c>
+      <c r="Q53">
+        <v>-0.8742659360000009</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.2226791592731582</v>
+      </c>
+      <c r="T53">
+        <v>1.5169419657386</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.0349088316849685</v>
+      </c>
+      <c r="W53">
+        <v>0.2304637709936295</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.1586765076589477</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.2286493112505986</v>
+      </c>
+      <c r="C54">
+        <v>3.09246077424519</v>
+      </c>
+      <c r="D54">
+        <v>26.66046077424519</v>
+      </c>
+      <c r="E54">
+        <v>-14.552</v>
+      </c>
+      <c r="F54">
+        <v>24.648</v>
+      </c>
+      <c r="G54">
+        <v>1.08</v>
+      </c>
+      <c r="H54">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>3.83</v>
+      </c>
+      <c r="K54">
+        <v>2.914</v>
+      </c>
+      <c r="L54">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M54">
+        <v>5.885942400000001</v>
+      </c>
+      <c r="N54">
+        <v>-4.969942400000001</v>
+      </c>
+      <c r="O54">
+        <v>-1.093387328</v>
+      </c>
+      <c r="P54">
+        <v>-3.876555072000001</v>
+      </c>
+      <c r="Q54">
+        <v>-0.9625550720000007</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.226509975091349</v>
+      </c>
+      <c r="T54">
+        <v>1.548544923358155</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.03423750799871911</v>
+      </c>
+      <c r="W54">
+        <v>0.2306240830899059</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.1556250363578142</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2306493112505986</v>
+      </c>
+      <c r="C55">
+        <v>2.34052951037506</v>
+      </c>
+      <c r="D55">
+        <v>26.38252951037506</v>
+      </c>
+      <c r="E55">
+        <v>-14.078</v>
+      </c>
+      <c r="F55">
+        <v>25.122</v>
+      </c>
+      <c r="G55">
+        <v>1.08</v>
+      </c>
+      <c r="H55">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>3.83</v>
+      </c>
+      <c r="K55">
+        <v>2.914</v>
+      </c>
+      <c r="L55">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M55">
+        <v>5.999133600000001</v>
+      </c>
+      <c r="N55">
+        <v>-5.083133600000002</v>
+      </c>
+      <c r="O55">
+        <v>-1.118289392</v>
+      </c>
+      <c r="P55">
+        <v>-3.964844208000001</v>
+      </c>
+      <c r="Q55">
+        <v>-1.050844208000001</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.2305038043486118</v>
+      </c>
+      <c r="T55">
+        <v>1.581492687684924</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.03359151728176214</v>
+      </c>
+      <c r="W55">
+        <v>0.2307783456731152</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.1526887149171006</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2326493112505986</v>
+      </c>
+      <c r="C56">
+        <v>1.594333242664121</v>
+      </c>
+      <c r="D56">
+        <v>26.11033324266413</v>
+      </c>
+      <c r="E56">
+        <v>-13.604</v>
+      </c>
+      <c r="F56">
+        <v>25.596</v>
+      </c>
+      <c r="G56">
+        <v>1.08</v>
+      </c>
+      <c r="H56">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>3.83</v>
+      </c>
+      <c r="K56">
+        <v>2.914</v>
+      </c>
+      <c r="L56">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M56">
+        <v>6.112324800000001</v>
+      </c>
+      <c r="N56">
+        <v>-5.196324800000001</v>
+      </c>
+      <c r="O56">
+        <v>-1.143191456</v>
+      </c>
+      <c r="P56">
+        <v>-4.053133344000001</v>
+      </c>
+      <c r="Q56">
+        <v>-1.139133344000001</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.2346712783561903</v>
+      </c>
+      <c r="T56">
+        <v>1.615872963504161</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.03296945214691469</v>
+      </c>
+      <c r="W56">
+        <v>0.2309268948273168</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.1498611461223396</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2346493112505986</v>
+      </c>
+      <c r="C57">
+        <v>0.8536962749266657</v>
+      </c>
+      <c r="D57">
+        <v>25.84369627492667</v>
+      </c>
+      <c r="E57">
+        <v>-13.13</v>
+      </c>
+      <c r="F57">
+        <v>26.07</v>
+      </c>
+      <c r="G57">
+        <v>1.08</v>
+      </c>
+      <c r="H57">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>3.83</v>
+      </c>
+      <c r="K57">
+        <v>2.914</v>
+      </c>
+      <c r="L57">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M57">
+        <v>6.225516000000002</v>
+      </c>
+      <c r="N57">
+        <v>-5.309516000000002</v>
+      </c>
+      <c r="O57">
+        <v>-1.16809352</v>
+      </c>
+      <c r="P57">
+        <v>-4.141422480000002</v>
+      </c>
+      <c r="Q57">
+        <v>-1.227422480000002</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.2390239734307723</v>
+      </c>
+      <c r="T57">
+        <v>1.651781251582032</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.03237000756242533</v>
+      </c>
+      <c r="W57">
+        <v>0.2310700421940928</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.1471363980110242</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2366493112505986</v>
+      </c>
+      <c r="C58">
+        <v>0.1184500152195298</v>
+      </c>
+      <c r="D58">
+        <v>25.58245001521953</v>
+      </c>
+      <c r="E58">
+        <v>-12.656</v>
+      </c>
+      <c r="F58">
+        <v>26.544</v>
+      </c>
+      <c r="G58">
+        <v>1.08</v>
+      </c>
+      <c r="H58">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>3.83</v>
+      </c>
+      <c r="K58">
+        <v>2.914</v>
+      </c>
+      <c r="L58">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M58">
+        <v>6.338707200000001</v>
+      </c>
+      <c r="N58">
+        <v>-5.422707200000001</v>
+      </c>
+      <c r="O58">
+        <v>-1.192995584</v>
+      </c>
+      <c r="P58">
+        <v>-4.229711616000001</v>
+      </c>
+      <c r="Q58">
+        <v>-1.315711616000001</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.2435745182814716</v>
+      </c>
+      <c r="T58">
+        <v>1.689321734572532</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.03179197171309631</v>
+      </c>
+      <c r="W58">
+        <v>0.2312080771549126</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.144508962332256</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2386493112505986</v>
+      </c>
+      <c r="C59">
+        <v>-0.6115673796379539</v>
+      </c>
+      <c r="D59">
+        <v>25.32643262036206</v>
+      </c>
+      <c r="E59">
+        <v>-12.182</v>
+      </c>
+      <c r="F59">
+        <v>27.01800000000001</v>
+      </c>
+      <c r="G59">
+        <v>1.08</v>
+      </c>
+      <c r="H59">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>3.83</v>
+      </c>
+      <c r="K59">
+        <v>2.914</v>
+      </c>
+      <c r="L59">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M59">
+        <v>6.451898400000002</v>
+      </c>
+      <c r="N59">
+        <v>-5.535898400000002</v>
+      </c>
+      <c r="O59">
+        <v>-1.217897648</v>
+      </c>
+      <c r="P59">
+        <v>-4.318000752000002</v>
+      </c>
+      <c r="Q59">
+        <v>-1.404000752000002</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.2483367163810408</v>
+      </c>
+      <c r="T59">
+        <v>1.728608286539336</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.03123421782339286</v>
+      </c>
+      <c r="W59">
+        <v>0.2313412687837738</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.1419737173790584</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2406493112505986</v>
+      </c>
+      <c r="C60">
+        <v>-1.336511338410435</v>
+      </c>
+      <c r="D60">
+        <v>25.07548866158957</v>
+      </c>
+      <c r="E60">
+        <v>-11.708</v>
+      </c>
+      <c r="F60">
+        <v>27.492</v>
+      </c>
+      <c r="G60">
+        <v>1.08</v>
+      </c>
+      <c r="H60">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>3.83</v>
+      </c>
+      <c r="K60">
+        <v>2.914</v>
+      </c>
+      <c r="L60">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M60">
+        <v>6.5650896</v>
+      </c>
+      <c r="N60">
+        <v>-5.6490896</v>
+      </c>
+      <c r="O60">
+        <v>-1.242799712</v>
+      </c>
+      <c r="P60">
+        <v>-4.406289888</v>
+      </c>
+      <c r="Q60">
+        <v>-1.492289888</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.2533256858186846</v>
+      </c>
+      <c r="T60">
+        <v>1.769765626695034</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.03069569682643782</v>
+      </c>
+      <c r="W60">
+        <v>0.2314698675978467</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.1395258946656266</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2426493112505986</v>
+      </c>
+      <c r="C61">
+        <v>-2.056531190111215</v>
+      </c>
+      <c r="D61">
+        <v>24.82946880988879</v>
+      </c>
+      <c r="E61">
+        <v>-11.234</v>
+      </c>
+      <c r="F61">
+        <v>27.966</v>
+      </c>
+      <c r="G61">
+        <v>1.08</v>
+      </c>
+      <c r="H61">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>3.83</v>
+      </c>
+      <c r="K61">
+        <v>2.914</v>
+      </c>
+      <c r="L61">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M61">
+        <v>6.6782808</v>
+      </c>
+      <c r="N61">
+        <v>-5.762280800000001</v>
+      </c>
+      <c r="O61">
+        <v>-1.267701776</v>
+      </c>
+      <c r="P61">
+        <v>-4.494579024000001</v>
+      </c>
+      <c r="Q61">
+        <v>-1.580579024000001</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.2585580196191403</v>
+      </c>
+      <c r="T61">
+        <v>1.812930641980278</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.0301754307785321</v>
+      </c>
+      <c r="W61">
+        <v>0.2315941071300865</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.1371610489933277</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2446493112505986</v>
+      </c>
+      <c r="C62">
+        <v>-2.771770460323406</v>
+      </c>
+      <c r="D62">
+        <v>24.58822953967659</v>
+      </c>
+      <c r="E62">
+        <v>-10.76</v>
+      </c>
+      <c r="F62">
+        <v>28.44</v>
+      </c>
+      <c r="G62">
+        <v>1.08</v>
+      </c>
+      <c r="H62">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>3.83</v>
+      </c>
+      <c r="K62">
+        <v>2.914</v>
+      </c>
+      <c r="L62">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M62">
+        <v>6.791472000000001</v>
+      </c>
+      <c r="N62">
+        <v>-5.875472</v>
+      </c>
+      <c r="O62">
+        <v>-1.29260384</v>
+      </c>
+      <c r="P62">
+        <v>-4.58286816</v>
+      </c>
+      <c r="Q62">
+        <v>-1.66886816</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2640519701096188</v>
+      </c>
+      <c r="T62">
+        <v>1.858253908029785</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.02967250693222323</v>
+      </c>
+      <c r="W62">
+        <v>0.2317142053445851</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.1348750315101056</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2466493112505986</v>
+      </c>
+      <c r="C63">
+        <v>-3.482367150413296</v>
+      </c>
+      <c r="D63">
+        <v>24.35163284958671</v>
+      </c>
+      <c r="E63">
+        <v>-10.286</v>
+      </c>
+      <c r="F63">
+        <v>28.914</v>
+      </c>
+      <c r="G63">
+        <v>1.08</v>
+      </c>
+      <c r="H63">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>3.83</v>
+      </c>
+      <c r="K63">
+        <v>2.914</v>
+      </c>
+      <c r="L63">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M63">
+        <v>6.904663200000001</v>
+      </c>
+      <c r="N63">
+        <v>-5.988663200000001</v>
+      </c>
+      <c r="O63">
+        <v>-1.317505904</v>
+      </c>
+      <c r="P63">
+        <v>-4.671157296000001</v>
+      </c>
+      <c r="Q63">
+        <v>-1.757157296000001</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.269827661650891</v>
+      </c>
+      <c r="T63">
+        <v>1.905901444133113</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.02918607239235071</v>
+      </c>
+      <c r="W63">
+        <v>0.2318303659127067</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.1326639654197759</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2486493112505986</v>
+      </c>
+      <c r="C64">
+        <v>-4.188454000777131</v>
+      </c>
+      <c r="D64">
+        <v>24.11954599922287</v>
+      </c>
+      <c r="E64">
+        <v>-9.812000000000001</v>
+      </c>
+      <c r="F64">
+        <v>29.388</v>
+      </c>
+      <c r="G64">
+        <v>1.08</v>
+      </c>
+      <c r="H64">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>3.83</v>
+      </c>
+      <c r="K64">
+        <v>2.914</v>
+      </c>
+      <c r="L64">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M64">
+        <v>7.017854400000001</v>
+      </c>
+      <c r="N64">
+        <v>-6.101854400000001</v>
+      </c>
+      <c r="O64">
+        <v>-1.342407968</v>
+      </c>
+      <c r="P64">
+        <v>-4.759446432000001</v>
+      </c>
+      <c r="Q64">
+        <v>-1.845446432000001</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2759073369574935</v>
+      </c>
+      <c r="T64">
+        <v>1.956056745294511</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.02871532928924829</v>
+      </c>
+      <c r="W64">
+        <v>0.2319427793657275</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.1305242240420377</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2506493112505986</v>
+      </c>
+      <c r="C65">
+        <v>-4.890158739176709</v>
+      </c>
+      <c r="D65">
+        <v>23.8918412608233</v>
+      </c>
+      <c r="E65">
+        <v>-9.337999999999997</v>
+      </c>
+      <c r="F65">
+        <v>29.86200000000001</v>
+      </c>
+      <c r="G65">
+        <v>1.08</v>
+      </c>
+      <c r="H65">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>3.83</v>
+      </c>
+      <c r="K65">
+        <v>2.914</v>
+      </c>
+      <c r="L65">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M65">
+        <v>7.131045600000002</v>
+      </c>
+      <c r="N65">
+        <v>-6.215045600000002</v>
+      </c>
+      <c r="O65">
+        <v>-1.367310032</v>
+      </c>
+      <c r="P65">
+        <v>-4.847735568000001</v>
+      </c>
+      <c r="Q65">
+        <v>-1.933735568000001</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2823156433617501</v>
+      </c>
+      <c r="T65">
+        <v>2.008923143815984</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.02825953041164116</v>
+      </c>
+      <c r="W65">
+        <v>0.2320516241377001</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.1284524109620053</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2526493112505986</v>
+      </c>
+      <c r="C66">
+        <v>-5.587604315139551</v>
+      </c>
+      <c r="D66">
+        <v>23.66839568486045</v>
+      </c>
+      <c r="E66">
+        <v>-8.863999999999997</v>
+      </c>
+      <c r="F66">
+        <v>30.33600000000001</v>
+      </c>
+      <c r="G66">
+        <v>1.08</v>
+      </c>
+      <c r="H66">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>3.83</v>
+      </c>
+      <c r="K66">
+        <v>2.914</v>
+      </c>
+      <c r="L66">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M66">
+        <v>7.244236800000002</v>
+      </c>
+      <c r="N66">
+        <v>-6.328236800000003</v>
+      </c>
+      <c r="O66">
+        <v>-1.392212096</v>
+      </c>
+      <c r="P66">
+        <v>-4.936024704000002</v>
+      </c>
+      <c r="Q66">
+        <v>-2.022024704000002</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2890799667884654</v>
+      </c>
+      <c r="T66">
+        <v>2.06472656447754</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.02781797524895927</v>
+      </c>
+      <c r="W66">
+        <v>0.2321570675105485</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.1264453420407239</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2546493112505986</v>
+      </c>
+      <c r="C67">
+        <v>-6.280909121327984</v>
+      </c>
+      <c r="D67">
+        <v>23.44909087867202</v>
+      </c>
+      <c r="E67">
+        <v>-8.389999999999997</v>
+      </c>
+      <c r="F67">
+        <v>30.81000000000001</v>
+      </c>
+      <c r="G67">
+        <v>1.08</v>
+      </c>
+      <c r="H67">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>3.83</v>
+      </c>
+      <c r="K67">
+        <v>2.914</v>
+      </c>
+      <c r="L67">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M67">
+        <v>7.357428000000001</v>
+      </c>
+      <c r="N67">
+        <v>-6.441428000000002</v>
+      </c>
+      <c r="O67">
+        <v>-1.41711416</v>
+      </c>
+      <c r="P67">
+        <v>-5.024313840000001</v>
+      </c>
+      <c r="Q67">
+        <v>-2.110313840000001</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2962308229824215</v>
+      </c>
+      <c r="T67">
+        <v>2.123718752034041</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.02739000639897528</v>
+      </c>
+      <c r="W67">
+        <v>0.2322592664719247</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.1245000290862512</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2566493112505986</v>
+      </c>
+      <c r="C68">
+        <v>-6.970187202714243</v>
+      </c>
+      <c r="D68">
+        <v>23.23381279728576</v>
+      </c>
+      <c r="E68">
+        <v>-7.915999999999997</v>
+      </c>
+      <c r="F68">
+        <v>31.28400000000001</v>
+      </c>
+      <c r="G68">
+        <v>1.08</v>
+      </c>
+      <c r="H68">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>3.83</v>
+      </c>
+      <c r="K68">
+        <v>2.914</v>
+      </c>
+      <c r="L68">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M68">
+        <v>7.470619200000002</v>
+      </c>
+      <c r="N68">
+        <v>-6.554619200000001</v>
+      </c>
+      <c r="O68">
+        <v>-1.442016224</v>
+      </c>
+      <c r="P68">
+        <v>-5.112602976000002</v>
+      </c>
+      <c r="Q68">
+        <v>-2.198602976000001</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.3038023177760222</v>
+      </c>
+      <c r="T68">
+        <v>2.186181068270336</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.02697500630202111</v>
+      </c>
+      <c r="W68">
+        <v>0.2323583684950774</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.1226136650091869</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2586493112505986</v>
+      </c>
+      <c r="C69">
+        <v>-7.655548454338099</v>
+      </c>
+      <c r="D69">
+        <v>23.02245154566191</v>
+      </c>
+      <c r="E69">
+        <v>-7.441999999999997</v>
+      </c>
+      <c r="F69">
+        <v>31.75800000000001</v>
+      </c>
+      <c r="G69">
+        <v>1.08</v>
+      </c>
+      <c r="H69">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>3.83</v>
+      </c>
+      <c r="K69">
+        <v>2.914</v>
+      </c>
+      <c r="L69">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M69">
+        <v>7.583810400000002</v>
+      </c>
+      <c r="N69">
+        <v>-6.667810400000002</v>
+      </c>
+      <c r="O69">
+        <v>-1.466918288</v>
+      </c>
+      <c r="P69">
+        <v>-5.200892112000002</v>
+      </c>
+      <c r="Q69">
+        <v>-2.286892112000002</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.3118326910419622</v>
+      </c>
+      <c r="T69">
+        <v>2.252428979430043</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.02657239426766259</v>
+      </c>
+      <c r="W69">
+        <v>0.2324545122488822</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.1207836103075571</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2606493112505986</v>
+      </c>
+      <c r="C70">
+        <v>-8.337098808367877</v>
+      </c>
+      <c r="D70">
+        <v>22.81490119163213</v>
+      </c>
+      <c r="E70">
+        <v>-6.967999999999996</v>
+      </c>
+      <c r="F70">
+        <v>32.23200000000001</v>
+      </c>
+      <c r="G70">
+        <v>1.08</v>
+      </c>
+      <c r="H70">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>3.83</v>
+      </c>
+      <c r="K70">
+        <v>2.914</v>
+      </c>
+      <c r="L70">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M70">
+        <v>7.697001600000002</v>
+      </c>
+      <c r="N70">
+        <v>-6.781001600000002</v>
+      </c>
+      <c r="O70">
+        <v>-1.491820352</v>
+      </c>
+      <c r="P70">
+        <v>-5.289181248000001</v>
+      </c>
+      <c r="Q70">
+        <v>-2.375181248000001</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.3203649626370235</v>
+      </c>
+      <c r="T70">
+        <v>2.322817385037232</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.02618162376372637</v>
+      </c>
+      <c r="W70">
+        <v>0.2325478282452222</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.1190073807442108</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2626493112505986</v>
+      </c>
+      <c r="C71">
+        <v>-9.014940411133331</v>
+      </c>
+      <c r="D71">
+        <v>22.61105958886668</v>
+      </c>
+      <c r="E71">
+        <v>-6.493999999999993</v>
+      </c>
+      <c r="F71">
+        <v>32.70600000000001</v>
+      </c>
+      <c r="G71">
+        <v>1.08</v>
+      </c>
+      <c r="H71">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>3.83</v>
+      </c>
+      <c r="K71">
+        <v>2.914</v>
+      </c>
+      <c r="L71">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M71">
+        <v>7.810192800000003</v>
+      </c>
+      <c r="N71">
+        <v>-6.894192800000003</v>
+      </c>
+      <c r="O71">
+        <v>-1.516722416</v>
+      </c>
+      <c r="P71">
+        <v>-5.377470384000002</v>
+      </c>
+      <c r="Q71">
+        <v>-2.463470384000002</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.3294477033672501</v>
+      </c>
+      <c r="T71">
+        <v>2.397746978102949</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.02580217994106367</v>
+      </c>
+      <c r="W71">
+        <v>0.232638439430074</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.117282636095744</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2646493112505986</v>
+      </c>
+      <c r="C72">
+        <v>-9.68917179075244</v>
+      </c>
+      <c r="D72">
+        <v>22.41082820924757</v>
+      </c>
+      <c r="E72">
+        <v>-6.019999999999996</v>
+      </c>
+      <c r="F72">
+        <v>33.18000000000001</v>
+      </c>
+      <c r="G72">
+        <v>1.08</v>
+      </c>
+      <c r="H72">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>3.83</v>
+      </c>
+      <c r="K72">
+        <v>2.914</v>
+      </c>
+      <c r="L72">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M72">
+        <v>7.923384000000002</v>
+      </c>
+      <c r="N72">
+        <v>-7.007384000000002</v>
+      </c>
+      <c r="O72">
+        <v>-1.54162448</v>
+      </c>
+      <c r="P72">
+        <v>-5.465759520000002</v>
+      </c>
+      <c r="Q72">
+        <v>-2.551759520000001</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.3391359601461585</v>
+      </c>
+      <c r="T72">
+        <v>2.477671877373048</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.02543357737047705</v>
+      </c>
+      <c r="W72">
+        <v>0.2327264617239301</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.1156071698658049</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2666493112505986</v>
+      </c>
+      <c r="C73">
+        <v>-10.35988801592987</v>
+      </c>
+      <c r="D73">
+        <v>22.21411198407014</v>
+      </c>
+      <c r="E73">
+        <v>-5.545999999999999</v>
+      </c>
+      <c r="F73">
+        <v>33.654</v>
+      </c>
+      <c r="G73">
+        <v>1.08</v>
+      </c>
+      <c r="H73">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>3.83</v>
+      </c>
+      <c r="K73">
+        <v>2.914</v>
+      </c>
+      <c r="L73">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M73">
+        <v>8.036575200000001</v>
+      </c>
+      <c r="N73">
+        <v>-7.120575200000001</v>
+      </c>
+      <c r="O73">
+        <v>-1.566526544</v>
+      </c>
+      <c r="P73">
+        <v>-5.554048656000001</v>
+      </c>
+      <c r="Q73">
+        <v>-2.640048656000001</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.3494923725649914</v>
+      </c>
+      <c r="T73">
+        <v>2.563108838661773</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.02507535797089287</v>
+      </c>
+      <c r="W73">
+        <v>0.2328120045165508</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.1139788998676949</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2686493112505985</v>
+      </c>
+      <c r="C74">
+        <v>-11.02718084646482</v>
+      </c>
+      <c r="D74">
+        <v>22.02081915353518</v>
+      </c>
+      <c r="E74">
+        <v>-5.072000000000003</v>
+      </c>
+      <c r="F74">
+        <v>34.128</v>
+      </c>
+      <c r="G74">
+        <v>1.08</v>
+      </c>
+      <c r="H74">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>3.83</v>
+      </c>
+      <c r="K74">
+        <v>2.914</v>
+      </c>
+      <c r="L74">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M74">
+        <v>8.149766400000001</v>
+      </c>
+      <c r="N74">
+        <v>-7.2337664</v>
+      </c>
+      <c r="O74">
+        <v>-1.591428608</v>
+      </c>
+      <c r="P74">
+        <v>-5.642337792</v>
+      </c>
+      <c r="Q74">
+        <v>-2.728337792</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.3605885287280268</v>
+      </c>
+      <c r="T74">
+        <v>2.65464844004255</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.02472708911018602</v>
+      </c>
+      <c r="W74">
+        <v>0.2328951711204876</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.1123958595917547</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2706493112505986</v>
+      </c>
+      <c r="C75">
+        <v>-11.69113887596904</v>
+      </c>
+      <c r="D75">
+        <v>21.83086112403097</v>
+      </c>
+      <c r="E75">
+        <v>-4.597999999999999</v>
+      </c>
+      <c r="F75">
+        <v>34.602</v>
+      </c>
+      <c r="G75">
+        <v>1.08</v>
+      </c>
+      <c r="H75">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>3.83</v>
+      </c>
+      <c r="K75">
+        <v>2.914</v>
+      </c>
+      <c r="L75">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M75">
+        <v>8.262957600000002</v>
+      </c>
+      <c r="N75">
+        <v>-7.346957600000001</v>
+      </c>
+      <c r="O75">
+        <v>-1.616330672</v>
+      </c>
+      <c r="P75">
+        <v>-5.730626928000001</v>
+      </c>
+      <c r="Q75">
+        <v>-2.816626928000001</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.3725066223846205</v>
+      </c>
+      <c r="T75">
+        <v>2.752968752636719</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.02438836186210128</v>
+      </c>
+      <c r="W75">
+        <v>0.2329760591873302</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.1108561902822786</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2726493112505985</v>
+      </c>
+      <c r="C76">
+        <v>-12.35184766726101</v>
+      </c>
+      <c r="D76">
+        <v>21.64415233273899</v>
+      </c>
+      <c r="E76">
+        <v>-4.124000000000002</v>
+      </c>
+      <c r="F76">
+        <v>35.076</v>
+      </c>
+      <c r="G76">
+        <v>1.08</v>
+      </c>
+      <c r="H76">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>3.83</v>
+      </c>
+      <c r="K76">
+        <v>2.914</v>
+      </c>
+      <c r="L76">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M76">
+        <v>8.376148800000001</v>
+      </c>
+      <c r="N76">
+        <v>-7.460148800000001</v>
+      </c>
+      <c r="O76">
+        <v>-1.641232736</v>
+      </c>
+      <c r="P76">
+        <v>-5.818916064000001</v>
+      </c>
+      <c r="Q76">
+        <v>-2.904916064</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.3853414924763366</v>
+      </c>
+      <c r="T76">
+        <v>2.85885216619967</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.02405878940450532</v>
+      </c>
+      <c r="W76">
+        <v>0.2330547610902041</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.1093581336568424</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2746493112505986</v>
+      </c>
+      <c r="C77">
+        <v>-13.00938988087165</v>
+      </c>
+      <c r="D77">
+        <v>21.46061011912835</v>
+      </c>
+      <c r="E77">
+        <v>-3.649999999999999</v>
+      </c>
+      <c r="F77">
+        <v>35.55</v>
+      </c>
+      <c r="G77">
+        <v>1.08</v>
+      </c>
+      <c r="H77">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>3.83</v>
+      </c>
+      <c r="K77">
+        <v>2.914</v>
+      </c>
+      <c r="L77">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M77">
+        <v>8.489340000000002</v>
+      </c>
+      <c r="N77">
+        <v>-7.573340000000002</v>
+      </c>
+      <c r="O77">
+        <v>-1.6661348</v>
+      </c>
+      <c r="P77">
+        <v>-5.907205200000002</v>
+      </c>
+      <c r="Q77">
+        <v>-2.993205200000002</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.3992031521753901</v>
+      </c>
+      <c r="T77">
+        <v>2.973206252847657</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.02373800554577858</v>
+      </c>
+      <c r="W77">
+        <v>0.2331313642756681</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.1079000252080845</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2766493112505986</v>
+      </c>
+      <c r="C78">
+        <v>-13.66384539706625</v>
+      </c>
+      <c r="D78">
+        <v>21.28015460293375</v>
+      </c>
+      <c r="E78">
+        <v>-3.175999999999995</v>
+      </c>
+      <c r="F78">
+        <v>36.02400000000001</v>
+      </c>
+      <c r="G78">
+        <v>1.08</v>
+      </c>
+      <c r="H78">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>3.83</v>
+      </c>
+      <c r="K78">
+        <v>2.914</v>
+      </c>
+      <c r="L78">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M78">
+        <v>8.602531200000003</v>
+      </c>
+      <c r="N78">
+        <v>-7.686531200000003</v>
+      </c>
+      <c r="O78">
+        <v>-1.691036864</v>
+      </c>
+      <c r="P78">
+        <v>-5.995494336000002</v>
+      </c>
+      <c r="Q78">
+        <v>-3.081494336000002</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.414219950182698</v>
+      </c>
+      <c r="T78">
+        <v>3.097089846716309</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.02342566336754464</v>
+      </c>
+      <c r="W78">
+        <v>0.2332059515878304</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.1064802880342939</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2786493112505986</v>
+      </c>
+      <c r="C79">
+        <v>-14.31529143176176</v>
+      </c>
+      <c r="D79">
+        <v>21.10270856823825</v>
+      </c>
+      <c r="E79">
+        <v>-2.701999999999998</v>
+      </c>
+      <c r="F79">
+        <v>36.498</v>
+      </c>
+      <c r="G79">
+        <v>1.08</v>
+      </c>
+      <c r="H79">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>3.83</v>
+      </c>
+      <c r="K79">
+        <v>2.914</v>
+      </c>
+      <c r="L79">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M79">
+        <v>8.715722400000002</v>
+      </c>
+      <c r="N79">
+        <v>-7.799722400000002</v>
+      </c>
+      <c r="O79">
+        <v>-1.715938928</v>
+      </c>
+      <c r="P79">
+        <v>-6.083783472000002</v>
+      </c>
+      <c r="Q79">
+        <v>-3.169783472000002</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.4305425567123805</v>
+      </c>
+      <c r="T79">
+        <v>3.231745927008323</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.02312143397316095</v>
+      </c>
+      <c r="W79">
+        <v>0.2332786015672092</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.1050974271507317</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2806493112505986</v>
+      </c>
+      <c r="C80">
+        <v>-14.96380264669239</v>
+      </c>
+      <c r="D80">
+        <v>20.92819735330762</v>
+      </c>
+      <c r="E80">
+        <v>-2.227999999999994</v>
+      </c>
+      <c r="F80">
+        <v>36.97200000000001</v>
+      </c>
+      <c r="G80">
+        <v>1.08</v>
+      </c>
+      <c r="H80">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>3.83</v>
+      </c>
+      <c r="K80">
+        <v>2.914</v>
+      </c>
+      <c r="L80">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M80">
+        <v>8.828913600000002</v>
+      </c>
+      <c r="N80">
+        <v>-7.912913600000001</v>
+      </c>
+      <c r="O80">
+        <v>-1.740840992</v>
+      </c>
+      <c r="P80">
+        <v>-6.172072608000001</v>
+      </c>
+      <c r="Q80">
+        <v>-3.258072608000001</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.4483490365629433</v>
+      </c>
+      <c r="T80">
+        <v>3.378643469145064</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.0228250053324794</v>
+      </c>
+      <c r="W80">
+        <v>0.2333493887266039</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.1037500242385428</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2826493112505986</v>
+      </c>
+      <c r="C81">
+        <v>-15.6094512541539</v>
+      </c>
+      <c r="D81">
+        <v>20.75654874584611</v>
+      </c>
+      <c r="E81">
+        <v>-1.753999999999998</v>
+      </c>
+      <c r="F81">
+        <v>37.44600000000001</v>
+      </c>
+      <c r="G81">
+        <v>1.08</v>
+      </c>
+      <c r="H81">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>3.83</v>
+      </c>
+      <c r="K81">
+        <v>2.914</v>
+      </c>
+      <c r="L81">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M81">
+        <v>8.942104800000001</v>
+      </c>
+      <c r="N81">
+        <v>-8.026104800000001</v>
+      </c>
+      <c r="O81">
+        <v>-1.765743056</v>
+      </c>
+      <c r="P81">
+        <v>-6.260361744000001</v>
+      </c>
+      <c r="Q81">
+        <v>-3.346361744000001</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.4678513716373692</v>
+      </c>
+      <c r="T81">
+        <v>3.539531253390068</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.02253608121434676</v>
+      </c>
+      <c r="W81">
+        <v>0.233418383806014</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.1024367327924853</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2846493112505986</v>
+      </c>
+      <c r="C82">
+        <v>-16.25230711663536</v>
+      </c>
+      <c r="D82">
+        <v>20.58769288336465</v>
+      </c>
+      <c r="E82">
+        <v>-1.279999999999994</v>
+      </c>
+      <c r="F82">
+        <v>37.92000000000001</v>
+      </c>
+      <c r="G82">
+        <v>1.08</v>
+      </c>
+      <c r="H82">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>3.83</v>
+      </c>
+      <c r="K82">
+        <v>2.914</v>
+      </c>
+      <c r="L82">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M82">
+        <v>9.055296000000002</v>
+      </c>
+      <c r="N82">
+        <v>-8.139296000000002</v>
+      </c>
+      <c r="O82">
+        <v>-1.79064512</v>
+      </c>
+      <c r="P82">
+        <v>-6.348650880000001</v>
+      </c>
+      <c r="Q82">
+        <v>-3.434650880000001</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.4893039402192377</v>
+      </c>
+      <c r="T82">
+        <v>3.716507816059572</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.02225438019916742</v>
+      </c>
+      <c r="W82">
+        <v>0.2334856540084388</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.1011562736325792</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2866493112505986</v>
+      </c>
+      <c r="C83">
+        <v>-16.89243784162695</v>
+      </c>
+      <c r="D83">
+        <v>20.42156215837306</v>
+      </c>
+      <c r="E83">
+        <v>-0.8059999999999974</v>
+      </c>
+      <c r="F83">
+        <v>38.39400000000001</v>
+      </c>
+      <c r="G83">
+        <v>1.08</v>
+      </c>
+      <c r="H83">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>3.83</v>
+      </c>
+      <c r="K83">
+        <v>2.914</v>
+      </c>
+      <c r="L83">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M83">
+        <v>9.168487200000001</v>
+      </c>
+      <c r="N83">
+        <v>-8.252487200000001</v>
+      </c>
+      <c r="O83">
+        <v>-1.815547184</v>
+      </c>
+      <c r="P83">
+        <v>-6.436940016000001</v>
+      </c>
+      <c r="Q83">
+        <v>-3.522940016000001</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.513014673914987</v>
+      </c>
+      <c r="T83">
+        <v>3.912113490589023</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.0219796347646098</v>
+      </c>
+      <c r="W83">
+        <v>0.2335512632182112</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.09990743074822639</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2886493112505986</v>
+      </c>
+      <c r="C84">
+        <v>-17.52990887187438</v>
+      </c>
+      <c r="D84">
+        <v>20.25809112812562</v>
+      </c>
+      <c r="E84">
+        <v>-0.3319999999999936</v>
+      </c>
+      <c r="F84">
+        <v>38.86800000000001</v>
+      </c>
+      <c r="G84">
+        <v>1.08</v>
+      </c>
+      <c r="H84">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>3.83</v>
+      </c>
+      <c r="K84">
+        <v>2.914</v>
+      </c>
+      <c r="L84">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M84">
+        <v>9.281678400000002</v>
+      </c>
+      <c r="N84">
+        <v>-8.365678400000002</v>
+      </c>
+      <c r="O84">
+        <v>-1.840449248</v>
+      </c>
+      <c r="P84">
+        <v>-6.525229152000001</v>
+      </c>
+      <c r="Q84">
+        <v>-3.611229152000001</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.5393599335769308</v>
+      </c>
+      <c r="T84">
+        <v>4.12945312895508</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.02171159043821211</v>
+      </c>
+      <c r="W84">
+        <v>0.233615272203355</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.09868904744641871</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2906493112505986</v>
+      </c>
+      <c r="C85">
+        <v>-18.1647835713328</v>
+      </c>
+      <c r="D85">
+        <v>20.0972164286672</v>
+      </c>
+      <c r="E85">
+        <v>0.142000000000003</v>
+      </c>
+      <c r="F85">
+        <v>39.34200000000001</v>
+      </c>
+      <c r="G85">
+        <v>1.08</v>
+      </c>
+      <c r="H85">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>3.83</v>
+      </c>
+      <c r="K85">
+        <v>2.914</v>
+      </c>
+      <c r="L85">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M85">
+        <v>9.394869600000002</v>
+      </c>
+      <c r="N85">
+        <v>-8.478869600000001</v>
+      </c>
+      <c r="O85">
+        <v>-1.865351312</v>
+      </c>
+      <c r="P85">
+        <v>-6.613518288000002</v>
+      </c>
+      <c r="Q85">
+        <v>-3.699518288000001</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.5688046355520444</v>
+      </c>
+      <c r="T85">
+        <v>4.372362136540673</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.0214500050112457</v>
+      </c>
+      <c r="W85">
+        <v>0.2336777388033145</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.09750002277838965</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2926493112505986</v>
+      </c>
+      <c r="C86">
+        <v>-18.79712330705757</v>
+      </c>
+      <c r="D86">
+        <v>19.93887669294243</v>
+      </c>
+      <c r="E86">
+        <v>0.6159999999999997</v>
+      </c>
+      <c r="F86">
+        <v>39.816</v>
+      </c>
+      <c r="G86">
+        <v>1.08</v>
+      </c>
+      <c r="H86">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>3.83</v>
+      </c>
+      <c r="K86">
+        <v>2.914</v>
+      </c>
+      <c r="L86">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M86">
+        <v>9.508060800000001</v>
+      </c>
+      <c r="N86">
+        <v>-8.5920608</v>
+      </c>
+      <c r="O86">
+        <v>-1.890253376</v>
+      </c>
+      <c r="P86">
+        <v>-6.701807424</v>
+      </c>
+      <c r="Q86">
+        <v>-3.787807424</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.6019299252740469</v>
+      </c>
+      <c r="T86">
+        <v>4.645634770074463</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.02119464780873088</v>
+      </c>
+      <c r="W86">
+        <v>0.2337387181032751</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.09633930822150405</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2946493112505986</v>
+      </c>
+      <c r="C87">
+        <v>-19.42698752725407</v>
+      </c>
+      <c r="D87">
+        <v>19.78301247274593</v>
+      </c>
+      <c r="E87">
+        <v>1.090000000000003</v>
+      </c>
+      <c r="F87">
+        <v>40.29000000000001</v>
+      </c>
+      <c r="G87">
+        <v>1.08</v>
+      </c>
+      <c r="H87">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>3.83</v>
+      </c>
+      <c r="K87">
+        <v>2.914</v>
+      </c>
+      <c r="L87">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M87">
+        <v>9.621252000000002</v>
+      </c>
+      <c r="N87">
+        <v>-8.705252000000002</v>
+      </c>
+      <c r="O87">
+        <v>-1.91515544</v>
+      </c>
+      <c r="P87">
+        <v>-6.790096560000001</v>
+      </c>
+      <c r="Q87">
+        <v>-3.876096560000001</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.6394719202923167</v>
+      </c>
+      <c r="T87">
+        <v>4.955343754746094</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.0209452990109811</v>
+      </c>
+      <c r="W87">
+        <v>0.2337982625961777</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.09520590459536871</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2966493112505986</v>
+      </c>
+      <c r="C88">
+        <v>-20.05443383569519</v>
+      </c>
+      <c r="D88">
+        <v>19.62956616430481</v>
+      </c>
+      <c r="E88">
+        <v>1.564</v>
+      </c>
+      <c r="F88">
+        <v>40.764</v>
+      </c>
+      <c r="G88">
+        <v>1.08</v>
+      </c>
+      <c r="H88">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>3.83</v>
+      </c>
+      <c r="K88">
+        <v>2.914</v>
+      </c>
+      <c r="L88">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M88">
+        <v>9.734443200000001</v>
+      </c>
+      <c r="N88">
+        <v>-8.818443200000001</v>
+      </c>
+      <c r="O88">
+        <v>-1.940057504</v>
+      </c>
+      <c r="P88">
+        <v>-6.878385696</v>
+      </c>
+      <c r="Q88">
+        <v>-3.964385696</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.6823770574560537</v>
+      </c>
+      <c r="T88">
+        <v>5.309296880085101</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.02070174902248132</v>
+      </c>
+      <c r="W88">
+        <v>0.2338564223334315</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.09409885919309702</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2986493112505986</v>
+      </c>
+      <c r="C89">
+        <v>-20.67951806270224</v>
+      </c>
+      <c r="D89">
+        <v>19.47848193729776</v>
+      </c>
+      <c r="E89">
+        <v>2.038000000000004</v>
+      </c>
+      <c r="F89">
+        <v>41.23800000000001</v>
+      </c>
+      <c r="G89">
+        <v>1.08</v>
+      </c>
+      <c r="H89">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>3.83</v>
+      </c>
+      <c r="K89">
+        <v>2.914</v>
+      </c>
+      <c r="L89">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M89">
+        <v>9.847634400000002</v>
+      </c>
+      <c r="N89">
+        <v>-8.931634400000002</v>
+      </c>
+      <c r="O89">
+        <v>-1.964959568</v>
+      </c>
+      <c r="P89">
+        <v>-6.966674832000002</v>
+      </c>
+      <c r="Q89">
+        <v>-4.052674832000001</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.7318829849526731</v>
+      </c>
+      <c r="T89">
+        <v>5.71770433239934</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.02046379788429188</v>
+      </c>
+      <c r="W89">
+        <v>0.2339132450652311</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.09301726311041769</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.3006493112505986</v>
+      </c>
+      <c r="C90">
+        <v>-21.3022943328728</v>
+      </c>
+      <c r="D90">
+        <v>19.3297056671272</v>
+      </c>
+      <c r="E90">
+        <v>2.512</v>
+      </c>
+      <c r="F90">
+        <v>41.712</v>
+      </c>
+      <c r="G90">
+        <v>1.08</v>
+      </c>
+      <c r="H90">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>3.83</v>
+      </c>
+      <c r="K90">
+        <v>2.914</v>
+      </c>
+      <c r="L90">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M90">
+        <v>9.960825600000002</v>
+      </c>
+      <c r="N90">
+        <v>-9.044825600000001</v>
+      </c>
+      <c r="O90">
+        <v>-1.989861632</v>
+      </c>
+      <c r="P90">
+        <v>-7.054963968000001</v>
+      </c>
+      <c r="Q90">
+        <v>-4.140963968000001</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.789639900365396</v>
+      </c>
+      <c r="T90">
+        <v>6.194179693432619</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.02023125472651583</v>
+      </c>
+      <c r="W90">
+        <v>0.233968776371308</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.09196024875689024</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.3026493112505986</v>
+      </c>
+      <c r="C91">
+        <v>-21.92281512972847</v>
+      </c>
+      <c r="D91">
+        <v>19.18318487027154</v>
+      </c>
+      <c r="E91">
+        <v>2.986000000000004</v>
+      </c>
+      <c r="F91">
+        <v>42.18600000000001</v>
+      </c>
+      <c r="G91">
+        <v>1.08</v>
+      </c>
+      <c r="H91">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>3.83</v>
+      </c>
+      <c r="K91">
+        <v>2.914</v>
+      </c>
+      <c r="L91">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M91">
+        <v>10.0740168</v>
+      </c>
+      <c r="N91">
+        <v>-9.158016800000002</v>
+      </c>
+      <c r="O91">
+        <v>-2.014763696</v>
+      </c>
+      <c r="P91">
+        <v>-7.143253104000002</v>
+      </c>
+      <c r="Q91">
+        <v>-4.229253104000001</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.8578980731258865</v>
+      </c>
+      <c r="T91">
+        <v>6.757286938290129</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.02000393725767858</v>
+      </c>
+      <c r="W91">
+        <v>0.2340230597828664</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.09092698753490269</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.3046493112505986</v>
+      </c>
+      <c r="C92">
+        <v>-22.54113135744431</v>
+      </c>
+      <c r="D92">
+        <v>19.03886864255569</v>
+      </c>
+      <c r="E92">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="F92">
+        <v>42.66</v>
+      </c>
+      <c r="G92">
+        <v>1.08</v>
+      </c>
+      <c r="H92">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>3.83</v>
+      </c>
+      <c r="K92">
+        <v>2.914</v>
+      </c>
+      <c r="L92">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M92">
+        <v>10.187208</v>
+      </c>
+      <c r="N92">
+        <v>-9.271208000000001</v>
+      </c>
+      <c r="O92">
+        <v>-2.03966576</v>
+      </c>
+      <c r="P92">
+        <v>-7.231542240000001</v>
+      </c>
+      <c r="Q92">
+        <v>-4.317542240000002</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.9398078804384753</v>
+      </c>
+      <c r="T92">
+        <v>7.433015632119143</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.01978167128814881</v>
+      </c>
+      <c r="W92">
+        <v>0.2340761368963901</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.08991668767340377</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.3066493112505986</v>
+      </c>
+      <c r="C93">
+        <v>-23.15729239981297</v>
+      </c>
+      <c r="D93">
+        <v>18.89670760018704</v>
+      </c>
+      <c r="E93">
+        <v>3.934000000000005</v>
+      </c>
+      <c r="F93">
+        <v>43.13400000000001</v>
+      </c>
+      <c r="G93">
+        <v>1.08</v>
+      </c>
+      <c r="H93">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>3.83</v>
+      </c>
+      <c r="K93">
+        <v>2.914</v>
+      </c>
+      <c r="L93">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M93">
+        <v>10.3003992</v>
+      </c>
+      <c r="N93">
+        <v>-9.384399200000002</v>
+      </c>
+      <c r="O93">
+        <v>-2.064567824</v>
+      </c>
+      <c r="P93">
+        <v>-7.319831376000002</v>
+      </c>
+      <c r="Q93">
+        <v>-4.405831376000002</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>1.039919867153862</v>
+      </c>
+      <c r="T93">
+        <v>8.25890625791016</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.01956429028498234</v>
+      </c>
+      <c r="W93">
+        <v>0.2341280474799462</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.08892859220446525</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.3086493112505986</v>
+      </c>
+      <c r="C94">
+        <v>-23.77134617658647</v>
+      </c>
+      <c r="D94">
+        <v>18.75665382341354</v>
+      </c>
+      <c r="E94">
+        <v>4.408000000000001</v>
+      </c>
+      <c r="F94">
+        <v>43.608</v>
+      </c>
+      <c r="G94">
+        <v>1.08</v>
+      </c>
+      <c r="H94">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>3.83</v>
+      </c>
+      <c r="K94">
+        <v>2.914</v>
+      </c>
+      <c r="L94">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M94">
+        <v>10.4135904</v>
+      </c>
+      <c r="N94">
+        <v>-9.497590400000002</v>
+      </c>
+      <c r="O94">
+        <v>-2.089469888</v>
+      </c>
+      <c r="P94">
+        <v>-7.408120512000002</v>
+      </c>
+      <c r="Q94">
+        <v>-4.494120512000002</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>1.165059850548094</v>
+      </c>
+      <c r="T94">
+        <v>9.291269540148932</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.01935163495579776</v>
+      </c>
+      <c r="W94">
+        <v>0.2341788295725555</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.08796197707180797</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.3106493112505986</v>
+      </c>
+      <c r="C95">
+        <v>-24.38333919733114</v>
+      </c>
+      <c r="D95">
+        <v>18.61866080266887</v>
+      </c>
+      <c r="E95">
+        <v>4.882000000000005</v>
+      </c>
+      <c r="F95">
+        <v>44.08200000000001</v>
+      </c>
+      <c r="G95">
+        <v>1.08</v>
+      </c>
+      <c r="H95">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>3.83</v>
+      </c>
+      <c r="K95">
+        <v>2.914</v>
+      </c>
+      <c r="L95">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M95">
+        <v>10.5267816</v>
+      </c>
+      <c r="N95">
+        <v>-9.610781600000003</v>
+      </c>
+      <c r="O95">
+        <v>-2.114371952</v>
+      </c>
+      <c r="P95">
+        <v>-7.496409648000002</v>
+      </c>
+      <c r="Q95">
+        <v>-4.582409648000002</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.325954114912108</v>
+      </c>
+      <c r="T95">
+        <v>10.61859376017021</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.01914355285949885</v>
+      </c>
+      <c r="W95">
+        <v>0.2342285195771517</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.08701614936135849</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.3126493112505986</v>
+      </c>
+      <c r="C96">
+        <v>-24.99331661292253</v>
+      </c>
+      <c r="D96">
+        <v>18.48268338707748</v>
+      </c>
+      <c r="E96">
+        <v>5.356000000000009</v>
+      </c>
+      <c r="F96">
+        <v>44.55600000000001</v>
+      </c>
+      <c r="G96">
+        <v>1.08</v>
+      </c>
+      <c r="H96">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>3.83</v>
+      </c>
+      <c r="K96">
+        <v>2.914</v>
+      </c>
+      <c r="L96">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M96">
+        <v>10.6399728</v>
+      </c>
+      <c r="N96">
+        <v>-9.723972800000002</v>
+      </c>
+      <c r="O96">
+        <v>-2.139274016</v>
+      </c>
+      <c r="P96">
+        <v>-7.584698784000002</v>
+      </c>
+      <c r="Q96">
+        <v>-4.670698784000002</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.540479800730793</v>
+      </c>
+      <c r="T96">
+        <v>12.38835938686525</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.01893989804184461</v>
+      </c>
+      <c r="W96">
+        <v>0.2342771523476075</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.08609044564474833</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.3146493112505986</v>
+      </c>
+      <c r="C97">
+        <v>-25.60132226480025</v>
+      </c>
+      <c r="D97">
+        <v>18.34867773519976</v>
+      </c>
+      <c r="E97">
+        <v>5.830000000000005</v>
+      </c>
+      <c r="F97">
+        <v>45.03000000000001</v>
+      </c>
+      <c r="G97">
+        <v>1.08</v>
+      </c>
+      <c r="H97">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>3.83</v>
+      </c>
+      <c r="K97">
+        <v>2.914</v>
+      </c>
+      <c r="L97">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M97">
+        <v>10.753164</v>
+      </c>
+      <c r="N97">
+        <v>-9.837164000000001</v>
+      </c>
+      <c r="O97">
+        <v>-2.16417608</v>
+      </c>
+      <c r="P97">
+        <v>-7.672987920000002</v>
+      </c>
+      <c r="Q97">
+        <v>-4.758987920000001</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.840815760876953</v>
+      </c>
+      <c r="T97">
+        <v>14.8660312642383</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.01874053069403572</v>
+      </c>
+      <c r="W97">
+        <v>0.2343247612702643</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.08518423042743517</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.3166493112505986</v>
+      </c>
+      <c r="C98">
+        <v>-26.2073987320955</v>
+      </c>
+      <c r="D98">
+        <v>18.21660126790451</v>
+      </c>
+      <c r="E98">
+        <v>6.304000000000002</v>
+      </c>
+      <c r="F98">
+        <v>45.504</v>
+      </c>
+      <c r="G98">
+        <v>1.08</v>
+      </c>
+      <c r="H98">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>3.83</v>
+      </c>
+      <c r="K98">
+        <v>2.914</v>
+      </c>
+      <c r="L98">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M98">
+        <v>10.8663552</v>
+      </c>
+      <c r="N98">
+        <v>-9.950355200000001</v>
+      </c>
+      <c r="O98">
+        <v>-2.189078144</v>
+      </c>
+      <c r="P98">
+        <v>-7.761277056000001</v>
+      </c>
+      <c r="Q98">
+        <v>-4.847277056000001</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>2.291319701096187</v>
+      </c>
+      <c r="T98">
+        <v>18.58253908029784</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.01854531683263952</v>
+      </c>
+      <c r="W98">
+        <v>0.2343713783403657</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.08429689469381607</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.3186493112505986</v>
+      </c>
+      <c r="C99">
+        <v>-26.81158737673783</v>
+      </c>
+      <c r="D99">
+        <v>18.08641262326217</v>
+      </c>
+      <c r="E99">
+        <v>6.777999999999999</v>
+      </c>
+      <c r="F99">
+        <v>45.978</v>
+      </c>
+      <c r="G99">
+        <v>1.08</v>
+      </c>
+      <c r="H99">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>3.83</v>
+      </c>
+      <c r="K99">
+        <v>2.914</v>
+      </c>
+      <c r="L99">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M99">
+        <v>10.9795464</v>
+      </c>
+      <c r="N99">
+        <v>-10.0635464</v>
+      </c>
+      <c r="O99">
+        <v>-2.213980208</v>
+      </c>
+      <c r="P99">
+        <v>-7.849566192</v>
+      </c>
+      <c r="Q99">
+        <v>-4.935566192</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>3.042159601461582</v>
+      </c>
+      <c r="T99">
+        <v>24.77671877373045</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.01835412799931333</v>
+      </c>
+      <c r="W99">
+        <v>0.234417034233764</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.08342785454233337</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.3206493112505986</v>
+      </c>
+      <c r="C100">
+        <v>-27.4139283866414</v>
+      </c>
+      <c r="D100">
+        <v>17.95807161335861</v>
+      </c>
+      <c r="E100">
+        <v>7.252000000000002</v>
+      </c>
+      <c r="F100">
+        <v>46.45200000000001</v>
+      </c>
+      <c r="G100">
+        <v>1.08</v>
+      </c>
+      <c r="H100">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>3.83</v>
+      </c>
+      <c r="K100">
+        <v>2.914</v>
+      </c>
+      <c r="L100">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M100">
+        <v>11.0927376</v>
+      </c>
+      <c r="N100">
+        <v>-10.1767376</v>
+      </c>
+      <c r="O100">
+        <v>-2.238882272</v>
+      </c>
+      <c r="P100">
+        <v>-7.937855328000001</v>
+      </c>
+      <c r="Q100">
+        <v>-5.023855328000002</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>4.543839402192372</v>
+      </c>
+      <c r="T100">
+        <v>37.16507816059568</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.01816684097891218</v>
+      </c>
+      <c r="W100">
+        <v>0.2344617583742358</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.08257654990414631</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.3226493112505986</v>
+      </c>
+      <c r="C101">
+        <v>-28.0144608170654</v>
+      </c>
+      <c r="D101">
+        <v>17.8315391829346</v>
+      </c>
+      <c r="E101">
+        <v>7.725999999999999</v>
+      </c>
+      <c r="F101">
+        <v>46.926</v>
+      </c>
+      <c r="G101">
+        <v>1.08</v>
+      </c>
+      <c r="H101">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>3.83</v>
+      </c>
+      <c r="K101">
+        <v>2.914</v>
+      </c>
+      <c r="L101">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="M101">
+        <v>11.2059288</v>
+      </c>
+      <c r="N101">
+        <v>-10.2899288</v>
+      </c>
+      <c r="O101">
+        <v>-2.263784336</v>
+      </c>
+      <c r="P101">
+        <v>-8.026144464000001</v>
+      </c>
+      <c r="Q101">
+        <v>-5.112144464000002</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>9.048878804384746</v>
+      </c>
+      <c r="T101">
+        <v>74.33015632119137</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.01798333753468074</v>
+      </c>
+      <c r="W101">
+        <v>0.2345055789967183</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.08174244333945802</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/greece/greece_paper_forest_products.xlsx
+++ b/research/traditional_assets/database/data/greece/greece_paper_forest_products.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09684382525883664</v>
+        <v>0.09666586884326721</v>
       </c>
       <c r="C2">
-        <v>32.22515369659642</v>
+        <v>32.04112567724414</v>
       </c>
       <c r="D2">
-        <v>31.60515369659642</v>
+        <v>31.71572567724414</v>
       </c>
       <c r="E2">
-        <v>-19.5</v>
+        <v>-19.2054</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.2946</v>
       </c>
       <c r="G2">
         <v>0.62</v>
@@ -1439,28 +1439,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.01481838</v>
       </c>
       <c r="N2">
-        <v>3.249333333333333</v>
+        <v>3.234514953333333</v>
       </c>
       <c r="O2">
-        <v>0.7148533333333333</v>
+        <v>0.7115932897333334</v>
       </c>
       <c r="P2">
-        <v>2.53448</v>
+        <v>2.5229216636</v>
       </c>
       <c r="Q2">
-        <v>5.418480000000001</v>
+        <v>5.4069216636</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09684382525883664</v>
+        <v>0.09724598873057293</v>
       </c>
       <c r="T2">
-        <v>0.6652721574126822</v>
+        <v>0.6705136956226002</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>219.2772309343756</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09666586884326721</v>
+        <v>0.09648791242769775</v>
       </c>
       <c r="C3">
-        <v>32.04112567724414</v>
+        <v>31.8578740557507</v>
       </c>
       <c r="D3">
-        <v>31.71572567724414</v>
+        <v>31.82707405575071</v>
       </c>
       <c r="E3">
-        <v>-19.2054</v>
+        <v>-18.9108</v>
       </c>
       <c r="F3">
-        <v>0.2946</v>
+        <v>0.5892000000000001</v>
       </c>
       <c r="G3">
         <v>0.62</v>
@@ -1521,28 +1521,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M3">
-        <v>0.01481838</v>
+        <v>0.02963676</v>
       </c>
       <c r="N3">
-        <v>3.234514953333333</v>
+        <v>3.219696573333334</v>
       </c>
       <c r="O3">
-        <v>0.7115932897333334</v>
+        <v>0.7083332461333334</v>
       </c>
       <c r="P3">
-        <v>2.5229216636</v>
+        <v>2.5113633272</v>
       </c>
       <c r="Q3">
-        <v>5.4069216636</v>
+        <v>5.3953633272</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09724598873057293</v>
+        <v>0.09765635962009975</v>
       </c>
       <c r="T3">
-        <v>0.6705136956226002</v>
+        <v>0.6758622040000677</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>219.2772309343756</v>
+        <v>109.6386154671878</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09648791242769775</v>
+        <v>0.09630995601212833</v>
       </c>
       <c r="C4">
-        <v>31.8578740557507</v>
+        <v>31.67540703831882</v>
       </c>
       <c r="D4">
-        <v>31.82707405575071</v>
+        <v>31.93920703831882</v>
       </c>
       <c r="E4">
-        <v>-18.9108</v>
+        <v>-18.6162</v>
       </c>
       <c r="F4">
-        <v>0.5892000000000001</v>
+        <v>0.8838</v>
       </c>
       <c r="G4">
         <v>0.62</v>
@@ -1603,28 +1603,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M4">
-        <v>0.02963676</v>
+        <v>0.04445514</v>
       </c>
       <c r="N4">
-        <v>3.219696573333334</v>
+        <v>3.204878193333333</v>
       </c>
       <c r="O4">
-        <v>0.7083332461333334</v>
+        <v>0.7050732025333333</v>
       </c>
       <c r="P4">
-        <v>2.5113633272</v>
+        <v>2.4998049908</v>
       </c>
       <c r="Q4">
-        <v>5.3953633272</v>
+        <v>5.3838049908</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09765635962009975</v>
+        <v>0.09807519176508075</v>
       </c>
       <c r="T4">
-        <v>0.6758622040000677</v>
+        <v>0.6813209909007819</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>109.6386154671878</v>
+        <v>73.09241031145855</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09630995601212833</v>
+        <v>0.09613199959655888</v>
       </c>
       <c r="C5">
-        <v>31.67540703831882</v>
+        <v>31.49373294720836</v>
       </c>
       <c r="D5">
-        <v>31.93920703831882</v>
+        <v>32.05213294720836</v>
       </c>
       <c r="E5">
-        <v>-18.6162</v>
+        <v>-18.3216</v>
       </c>
       <c r="F5">
-        <v>0.8838</v>
+        <v>1.1784</v>
       </c>
       <c r="G5">
         <v>0.62</v>
@@ -1685,28 +1685,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M5">
-        <v>0.04445514</v>
+        <v>0.05927352</v>
       </c>
       <c r="N5">
-        <v>3.204878193333333</v>
+        <v>3.190059813333333</v>
       </c>
       <c r="O5">
-        <v>0.7050732025333333</v>
+        <v>0.7018131589333333</v>
       </c>
       <c r="P5">
-        <v>2.4998049908</v>
+        <v>2.4882466544</v>
       </c>
       <c r="Q5">
-        <v>5.3838049908</v>
+        <v>5.3722466544</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09807519176508075</v>
+        <v>0.09850274957974883</v>
       </c>
       <c r="T5">
-        <v>0.6813209909007819</v>
+        <v>0.6868935025285944</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>73.09241031145855</v>
+        <v>54.81930773359391</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09613199959655888</v>
+        <v>0.09595404318098943</v>
       </c>
       <c r="C6">
-        <v>31.49373294720836</v>
+        <v>31.31286022279524</v>
       </c>
       <c r="D6">
-        <v>32.05213294720836</v>
+        <v>32.16586022279524</v>
       </c>
       <c r="E6">
-        <v>-18.3216</v>
+        <v>-18.027</v>
       </c>
       <c r="F6">
-        <v>1.1784</v>
+        <v>1.473</v>
       </c>
       <c r="G6">
         <v>0.62</v>
@@ -1767,28 +1767,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M6">
-        <v>0.05927352</v>
+        <v>0.0740919</v>
       </c>
       <c r="N6">
-        <v>3.190059813333333</v>
+        <v>3.175241433333333</v>
       </c>
       <c r="O6">
-        <v>0.7018131589333333</v>
+        <v>0.6985531153333333</v>
       </c>
       <c r="P6">
-        <v>2.4882466544</v>
+        <v>2.476688318</v>
       </c>
       <c r="Q6">
-        <v>5.3722466544</v>
+        <v>5.360688318</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09850274957974883</v>
+        <v>0.09893930861156783</v>
       </c>
       <c r="T6">
-        <v>0.6868935025285944</v>
+        <v>0.6925833301906765</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>54.81930773359391</v>
+        <v>43.85544618687513</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09595404318098943</v>
+        <v>0.09577608676541999</v>
       </c>
       <c r="C7">
-        <v>31.31286022279524</v>
+        <v>31.13279742567437</v>
       </c>
       <c r="D7">
-        <v>32.16586022279524</v>
+        <v>32.28039742567437</v>
       </c>
       <c r="E7">
-        <v>-18.027</v>
+        <v>-17.7324</v>
       </c>
       <c r="F7">
-        <v>1.473</v>
+        <v>1.7676</v>
       </c>
       <c r="G7">
         <v>0.62</v>
@@ -1849,28 +1849,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M7">
-        <v>0.0740919</v>
+        <v>0.08891028000000001</v>
       </c>
       <c r="N7">
-        <v>3.175241433333333</v>
+        <v>3.160423053333334</v>
       </c>
       <c r="O7">
-        <v>0.6985531153333333</v>
+        <v>0.6952930717333333</v>
       </c>
       <c r="P7">
-        <v>2.476688318</v>
+        <v>2.4651299816</v>
       </c>
       <c r="Q7">
-        <v>5.360688318</v>
+        <v>5.349129981600001</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09893930861156783</v>
+        <v>0.09938515613342552</v>
       </c>
       <c r="T7">
-        <v>0.6925833301906765</v>
+        <v>0.6983942180157816</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>43.85544618687513</v>
+        <v>36.54620515572928</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09577608676541999</v>
+        <v>0.09559813034985057</v>
       </c>
       <c r="C8">
-        <v>31.13279742567437</v>
+        <v>30.95355323880775</v>
       </c>
       <c r="D8">
-        <v>32.28039742567437</v>
+        <v>32.39575323880776</v>
       </c>
       <c r="E8">
-        <v>-17.7324</v>
+        <v>-17.4378</v>
       </c>
       <c r="F8">
-        <v>1.7676</v>
+        <v>2.0622</v>
       </c>
       <c r="G8">
         <v>0.62</v>
@@ -1931,28 +1931,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M8">
-        <v>0.08891027999999999</v>
+        <v>0.10372866</v>
       </c>
       <c r="N8">
-        <v>3.160423053333334</v>
+        <v>3.145604673333334</v>
       </c>
       <c r="O8">
-        <v>0.6952930717333333</v>
+        <v>0.6920330281333334</v>
       </c>
       <c r="P8">
-        <v>2.4651299816</v>
+        <v>2.4535716452</v>
       </c>
       <c r="Q8">
-        <v>5.349129981600001</v>
+        <v>5.337571645200001</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09938515613342552</v>
+        <v>0.09984059177403286</v>
       </c>
       <c r="T8">
-        <v>0.6983942180157816</v>
+        <v>0.704330071170459</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>36.54620515572928</v>
+        <v>31.32531870491081</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09559813034985057</v>
+        <v>0.09542017393428114</v>
       </c>
       <c r="C9">
-        <v>30.95355323880775</v>
+        <v>30.77513646971875</v>
       </c>
       <c r="D9">
-        <v>32.39575323880776</v>
+        <v>32.51193646971875</v>
       </c>
       <c r="E9">
-        <v>-17.4378</v>
+        <v>-17.1432</v>
       </c>
       <c r="F9">
-        <v>2.0622</v>
+        <v>2.3568</v>
       </c>
       <c r="G9">
         <v>0.62</v>
@@ -2013,28 +2013,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M9">
-        <v>0.10372866</v>
+        <v>0.11854704</v>
       </c>
       <c r="N9">
-        <v>3.145604673333334</v>
+        <v>3.130786293333333</v>
       </c>
       <c r="O9">
-        <v>0.6920330281333334</v>
+        <v>0.6887729845333334</v>
       </c>
       <c r="P9">
-        <v>2.4535716452</v>
+        <v>2.4420133088</v>
       </c>
       <c r="Q9">
-        <v>5.337571645200001</v>
+        <v>5.3260133088</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09984059177403287</v>
+        <v>0.100305928189436</v>
       </c>
       <c r="T9">
-        <v>0.7043300711704591</v>
+        <v>0.7103949646111076</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>31.3253187049108</v>
+        <v>27.40965386679695</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09542017393428114</v>
+        <v>0.09524221751871169</v>
       </c>
       <c r="C10">
-        <v>30.77513646971875</v>
+        <v>30.59755605273367</v>
       </c>
       <c r="D10">
-        <v>32.51193646971875</v>
+        <v>32.62895605273367</v>
       </c>
       <c r="E10">
-        <v>-17.1432</v>
+        <v>-16.8486</v>
       </c>
       <c r="F10">
-        <v>2.3568</v>
+        <v>2.6514</v>
       </c>
       <c r="G10">
         <v>0.62</v>
@@ -2095,28 +2095,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M10">
-        <v>0.11854704</v>
+        <v>0.13336542</v>
       </c>
       <c r="N10">
-        <v>3.130786293333333</v>
+        <v>3.115967913333333</v>
       </c>
       <c r="O10">
-        <v>0.6887729845333334</v>
+        <v>0.6855129409333334</v>
       </c>
       <c r="P10">
-        <v>2.4420133088</v>
+        <v>2.4304549724</v>
       </c>
       <c r="Q10">
-        <v>5.3260133088</v>
+        <v>5.3144549724</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.100305928189436</v>
+        <v>0.100781491778804</v>
       </c>
       <c r="T10">
-        <v>0.7103949646111076</v>
+        <v>0.7165931524130892</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>27.40965386679695</v>
+        <v>24.36413677048618</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09524221751871169</v>
+        <v>0.09506426110314224</v>
       </c>
       <c r="C11">
-        <v>30.59755605273367</v>
+        <v>30.42082105127209</v>
       </c>
       <c r="D11">
-        <v>32.62895605273367</v>
+        <v>32.74682105127209</v>
       </c>
       <c r="E11">
-        <v>-16.8486</v>
+        <v>-16.554</v>
       </c>
       <c r="F11">
-        <v>2.6514</v>
+        <v>2.946</v>
       </c>
       <c r="G11">
         <v>0.62</v>
@@ -2177,28 +2177,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M11">
-        <v>0.13336542</v>
+        <v>0.1481838</v>
       </c>
       <c r="N11">
-        <v>3.115967913333333</v>
+        <v>3.101149533333333</v>
       </c>
       <c r="O11">
-        <v>0.6855129409333334</v>
+        <v>0.6822528973333334</v>
       </c>
       <c r="P11">
-        <v>2.4304549724</v>
+        <v>2.418896636</v>
       </c>
       <c r="Q11">
-        <v>5.3144549724</v>
+        <v>5.302896636</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.100781491778804</v>
+        <v>0.1012676234479358</v>
       </c>
       <c r="T11">
-        <v>0.7165931524130892</v>
+        <v>0.7229290777217813</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>24.36413677048618</v>
+        <v>21.92772309343757</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09506426110314224</v>
+        <v>0.09488630468757281</v>
       </c>
       <c r="C12">
-        <v>30.42082105127208</v>
+        <v>30.24494066018681</v>
       </c>
       <c r="D12">
-        <v>32.74682105127209</v>
+        <v>32.86554066018682</v>
       </c>
       <c r="E12">
-        <v>-16.554</v>
+        <v>-16.2594</v>
       </c>
       <c r="F12">
-        <v>2.946</v>
+        <v>3.2406</v>
       </c>
       <c r="G12">
         <v>0.62</v>
@@ -2259,28 +2259,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M12">
-        <v>0.1481838</v>
+        <v>0.16300218</v>
       </c>
       <c r="N12">
-        <v>3.101149533333333</v>
+        <v>3.086331153333334</v>
       </c>
       <c r="O12">
-        <v>0.6822528973333334</v>
+        <v>0.6789928537333334</v>
       </c>
       <c r="P12">
-        <v>2.418896636</v>
+        <v>2.4073382996</v>
       </c>
       <c r="Q12">
-        <v>5.302896636</v>
+        <v>5.2913382996</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1012676234479358</v>
+        <v>0.1017646794242391</v>
       </c>
       <c r="T12">
-        <v>0.7229290777217813</v>
+        <v>0.7294073833744892</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>21.92772309343756</v>
+        <v>19.93429372130688</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09488630468757281</v>
+        <v>0.09470834827200336</v>
       </c>
       <c r="C13">
-        <v>30.24494066018681</v>
+        <v>30.06992420815518</v>
       </c>
       <c r="D13">
-        <v>32.86554066018682</v>
+        <v>32.98512420815518</v>
       </c>
       <c r="E13">
-        <v>-16.2594</v>
+        <v>-15.9648</v>
       </c>
       <c r="F13">
-        <v>3.2406</v>
+        <v>3.5352</v>
       </c>
       <c r="G13">
         <v>0.62</v>
@@ -2341,28 +2341,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M13">
-        <v>0.16300218</v>
+        <v>0.17782056</v>
       </c>
       <c r="N13">
-        <v>3.086331153333334</v>
+        <v>3.071512773333334</v>
       </c>
       <c r="O13">
-        <v>0.6789928537333334</v>
+        <v>0.6757328101333334</v>
       </c>
       <c r="P13">
-        <v>2.4073382996</v>
+        <v>2.3957799632</v>
       </c>
       <c r="Q13">
-        <v>5.2913382996</v>
+        <v>5.279779963200001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1017646794242391</v>
+        <v>0.1022730321272766</v>
       </c>
       <c r="T13">
-        <v>0.7294073833744892</v>
+        <v>0.7360329232465767</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>19.93429372130688</v>
+        <v>18.27310257786464</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09470834827200336</v>
+        <v>0.09453039185643392</v>
       </c>
       <c r="C14">
-        <v>30.06992420815518</v>
+        <v>29.89578116012244</v>
       </c>
       <c r="D14">
-        <v>32.98512420815518</v>
+        <v>33.10558116012244</v>
       </c>
       <c r="E14">
-        <v>-15.9648</v>
+        <v>-15.6702</v>
       </c>
       <c r="F14">
-        <v>3.5352</v>
+        <v>3.8298</v>
       </c>
       <c r="G14">
         <v>0.62</v>
@@ -2423,28 +2423,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M14">
-        <v>0.17782056</v>
+        <v>0.19263894</v>
       </c>
       <c r="N14">
-        <v>3.071512773333334</v>
+        <v>3.056694393333333</v>
       </c>
       <c r="O14">
-        <v>0.6757328101333334</v>
+        <v>0.6724727665333333</v>
       </c>
       <c r="P14">
-        <v>2.3957799632</v>
+        <v>2.3842216268</v>
       </c>
       <c r="Q14">
-        <v>5.279779963200001</v>
+        <v>5.268221626800001</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1022730321272766</v>
+        <v>0.1027930710993493</v>
       </c>
       <c r="T14">
-        <v>0.7360329232465767</v>
+        <v>0.7428107743800914</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>18.27310257786464</v>
+        <v>16.86747930264428</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09453039185643392</v>
+        <v>0.09435243544086448</v>
       </c>
       <c r="C15">
-        <v>29.89578116012244</v>
+        <v>29.7225211197991</v>
       </c>
       <c r="D15">
-        <v>33.10558116012244</v>
+        <v>33.22692111979911</v>
       </c>
       <c r="E15">
-        <v>-15.6702</v>
+        <v>-15.3756</v>
       </c>
       <c r="F15">
-        <v>3.8298</v>
+        <v>4.124400000000001</v>
       </c>
       <c r="G15">
         <v>0.62</v>
@@ -2505,28 +2505,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M15">
-        <v>0.19263894</v>
+        <v>0.20745732</v>
       </c>
       <c r="N15">
-        <v>3.056694393333333</v>
+        <v>3.041876013333333</v>
       </c>
       <c r="O15">
-        <v>0.6724727665333333</v>
+        <v>0.6692127229333333</v>
       </c>
       <c r="P15">
-        <v>2.3842216268</v>
+        <v>2.3726632904</v>
       </c>
       <c r="Q15">
-        <v>5.268221626800001</v>
+        <v>5.256663290400001</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1027930710993493</v>
+        <v>0.1033252040010052</v>
       </c>
       <c r="T15">
-        <v>0.7428107743800914</v>
+        <v>0.7497462499585716</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>16.86747930264428</v>
+        <v>15.6626593524554</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09435243544086448</v>
+        <v>0.09417447902529505</v>
       </c>
       <c r="C16">
-        <v>29.7225211197991</v>
+        <v>29.55015383221335</v>
       </c>
       <c r="D16">
-        <v>33.22692111979911</v>
+        <v>33.34915383221335</v>
       </c>
       <c r="E16">
-        <v>-15.3756</v>
+        <v>-15.081</v>
       </c>
       <c r="F16">
-        <v>4.124400000000001</v>
+        <v>4.419</v>
       </c>
       <c r="G16">
         <v>0.62</v>
@@ -2587,28 +2587,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M16">
-        <v>0.20745732</v>
+        <v>0.2222757</v>
       </c>
       <c r="N16">
-        <v>3.041876013333333</v>
+        <v>3.027057633333333</v>
       </c>
       <c r="O16">
-        <v>0.6692127229333333</v>
+        <v>0.6659526793333334</v>
       </c>
       <c r="P16">
-        <v>2.3726632904</v>
+        <v>2.361104954</v>
       </c>
       <c r="Q16">
-        <v>5.256663290400001</v>
+        <v>5.245104954</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1033252040010052</v>
+        <v>0.1038698576768177</v>
       </c>
       <c r="T16">
-        <v>0.7497462499585716</v>
+        <v>0.756844913197722</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>15.6626593524554</v>
+        <v>14.61848206229171</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09417447902529505</v>
+        <v>0.09399652260972559</v>
       </c>
       <c r="C17">
-        <v>29.55015383221335</v>
+        <v>29.37868918631995</v>
       </c>
       <c r="D17">
-        <v>33.34915383221335</v>
+        <v>33.47228918631995</v>
       </c>
       <c r="E17">
-        <v>-15.081</v>
+        <v>-14.7864</v>
       </c>
       <c r="F17">
-        <v>4.419</v>
+        <v>4.7136</v>
       </c>
       <c r="G17">
         <v>0.62</v>
@@ -2669,28 +2669,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M17">
-        <v>0.2222757</v>
+        <v>0.23709408</v>
       </c>
       <c r="N17">
-        <v>3.027057633333333</v>
+        <v>3.012239253333334</v>
       </c>
       <c r="O17">
-        <v>0.6659526793333334</v>
+        <v>0.6626926357333334</v>
       </c>
       <c r="P17">
-        <v>2.361104954</v>
+        <v>2.3495466176</v>
       </c>
       <c r="Q17">
-        <v>5.245104954</v>
+        <v>5.2335466176</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1038698576768177</v>
+        <v>0.1044274792972924</v>
       </c>
       <c r="T17">
-        <v>0.756844913197722</v>
+        <v>0.7641125922282807</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>14.61848206229171</v>
+        <v>13.70482693339848</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09399652260972559</v>
+        <v>0.09381856619415616</v>
       </c>
       <c r="C18">
-        <v>29.37868918631995</v>
+        <v>29.20813721766716</v>
       </c>
       <c r="D18">
-        <v>33.47228918631995</v>
+        <v>33.59633721766716</v>
       </c>
       <c r="E18">
-        <v>-14.7864</v>
+        <v>-14.4918</v>
       </c>
       <c r="F18">
-        <v>4.7136</v>
+        <v>5.0082</v>
       </c>
       <c r="G18">
         <v>0.62</v>
@@ -2751,28 +2751,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M18">
-        <v>0.23709408</v>
+        <v>0.25191246</v>
       </c>
       <c r="N18">
-        <v>3.012239253333334</v>
+        <v>2.997420873333334</v>
       </c>
       <c r="O18">
-        <v>0.6626926357333334</v>
+        <v>0.6594325921333334</v>
       </c>
       <c r="P18">
-        <v>2.3495466176</v>
+        <v>2.3379882812</v>
       </c>
       <c r="Q18">
-        <v>5.2335466176</v>
+        <v>5.221988281200001</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1044274792972924</v>
+        <v>0.1049985375833207</v>
       </c>
       <c r="T18">
-        <v>0.7641125922282807</v>
+        <v>0.7715553960547565</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>13.70482693339848</v>
+        <v>12.89866064319857</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09381856619415616</v>
+        <v>0.09385120977858671</v>
       </c>
       <c r="C19">
-        <v>29.20813721766716</v>
+        <v>28.89071354942705</v>
       </c>
       <c r="D19">
-        <v>33.59633721766716</v>
+        <v>33.57351354942706</v>
       </c>
       <c r="E19">
-        <v>-14.4918</v>
+        <v>-14.1972</v>
       </c>
       <c r="F19">
-        <v>5.0082</v>
+        <v>5.3028</v>
       </c>
       <c r="G19">
         <v>0.62</v>
@@ -2833,45 +2833,45 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M19">
-        <v>0.25191246</v>
+        <v>0.27468504</v>
       </c>
       <c r="N19">
-        <v>2.997420873333334</v>
+        <v>2.974648293333333</v>
       </c>
       <c r="O19">
-        <v>0.6594325921333334</v>
+        <v>0.6544226245333333</v>
       </c>
       <c r="P19">
-        <v>2.3379882812</v>
+        <v>2.3202256688</v>
       </c>
       <c r="Q19">
-        <v>5.221988281200001</v>
+        <v>5.2042256688</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1049985375833207</v>
+        <v>0.1055835241202277</v>
       </c>
       <c r="T19">
-        <v>0.7715553960547565</v>
+        <v>0.7791797316818782</v>
       </c>
       <c r="U19">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V19">
         <v>0.22</v>
       </c>
       <c r="W19">
-        <v>0.039234</v>
+        <v>0.040404</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y19">
-        <v>12.89866064319857</v>
+        <v>11.82930578721482</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09385120977858671</v>
+        <v>0.09368495336301728</v>
       </c>
       <c r="C20">
-        <v>28.89071354942705</v>
+        <v>28.71268068855494</v>
       </c>
       <c r="D20">
-        <v>33.57351354942706</v>
+        <v>33.69008068855494</v>
       </c>
       <c r="E20">
-        <v>-14.1972</v>
+        <v>-13.9026</v>
       </c>
       <c r="F20">
-        <v>5.3028</v>
+        <v>5.5974</v>
       </c>
       <c r="G20">
         <v>0.62</v>
@@ -2915,28 +2915,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M20">
-        <v>0.27468504</v>
+        <v>0.28994532</v>
       </c>
       <c r="N20">
-        <v>2.974648293333333</v>
+        <v>2.959388013333333</v>
       </c>
       <c r="O20">
-        <v>0.6544226245333333</v>
+        <v>0.6510653629333333</v>
       </c>
       <c r="P20">
-        <v>2.3202256688</v>
+        <v>2.3083226504</v>
       </c>
       <c r="Q20">
-        <v>5.2042256688</v>
+        <v>5.1923226504</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1055835241202277</v>
+        <v>0.1061829547691571</v>
       </c>
       <c r="T20">
-        <v>0.7791797316818779</v>
+        <v>0.7869923225096692</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>11.82930578721482</v>
+        <v>11.20671074578246</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09368495336301728</v>
+        <v>0.09351869694744784</v>
       </c>
       <c r="C21">
-        <v>28.71268068855494</v>
+        <v>28.53546008937331</v>
       </c>
       <c r="D21">
-        <v>33.69008068855494</v>
+        <v>33.80746008937331</v>
       </c>
       <c r="E21">
-        <v>-13.9026</v>
+        <v>-13.608</v>
       </c>
       <c r="F21">
-        <v>5.5974</v>
+        <v>5.892</v>
       </c>
       <c r="G21">
         <v>0.62</v>
@@ -2997,28 +2997,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M21">
-        <v>0.28994532</v>
+        <v>0.3052056</v>
       </c>
       <c r="N21">
-        <v>2.959388013333333</v>
+        <v>2.944127733333334</v>
       </c>
       <c r="O21">
-        <v>0.6510653629333333</v>
+        <v>0.6477081013333333</v>
       </c>
       <c r="P21">
-        <v>2.3083226504</v>
+        <v>2.296419632</v>
       </c>
       <c r="Q21">
-        <v>5.1923226504</v>
+        <v>5.180419632</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1061829547691571</v>
+        <v>0.1067973711843098</v>
       </c>
       <c r="T21">
-        <v>0.7869923225096692</v>
+        <v>0.7950002281081553</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.20671074578246</v>
+        <v>10.64637520849334</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09351869694744784</v>
+        <v>0.0933524405318784</v>
       </c>
       <c r="C22">
-        <v>28.53546008937331</v>
+        <v>28.35906027155319</v>
       </c>
       <c r="D22">
-        <v>33.80746008937331</v>
+        <v>33.92566027155319</v>
       </c>
       <c r="E22">
-        <v>-13.608</v>
+        <v>-13.3134</v>
       </c>
       <c r="F22">
-        <v>5.892</v>
+        <v>6.186600000000001</v>
       </c>
       <c r="G22">
         <v>0.62</v>
@@ -3079,28 +3079,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M22">
-        <v>0.3052056</v>
+        <v>0.32046588</v>
       </c>
       <c r="N22">
-        <v>2.944127733333334</v>
+        <v>2.928867453333333</v>
       </c>
       <c r="O22">
-        <v>0.6477081013333333</v>
+        <v>0.6443508397333334</v>
       </c>
       <c r="P22">
-        <v>2.296419632</v>
+        <v>2.2845166136</v>
       </c>
       <c r="Q22">
-        <v>5.180419632</v>
+        <v>5.1685166136</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1067973711843098</v>
+        <v>0.1074273424454157</v>
       </c>
       <c r="T22">
-        <v>0.7950002281081553</v>
+        <v>0.8032108654939447</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>10.64637520849334</v>
+        <v>10.13940496046984</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09335244053187838</v>
+        <v>0.09347790411630895</v>
       </c>
       <c r="C23">
-        <v>28.3590602715532</v>
+        <v>27.97518548020626</v>
       </c>
       <c r="D23">
-        <v>33.9256602715532</v>
+        <v>33.83638548020627</v>
       </c>
       <c r="E23">
-        <v>-13.3134</v>
+        <v>-13.0188</v>
       </c>
       <c r="F23">
-        <v>6.1866</v>
+        <v>6.4812</v>
       </c>
       <c r="G23">
         <v>0.62</v>
@@ -3161,45 +3161,45 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M23">
-        <v>0.32046588</v>
+        <v>0.3467442</v>
       </c>
       <c r="N23">
-        <v>2.928867453333333</v>
+        <v>2.902589133333334</v>
       </c>
       <c r="O23">
-        <v>0.6443508397333334</v>
+        <v>0.6385696093333334</v>
       </c>
       <c r="P23">
-        <v>2.2845166136</v>
+        <v>2.264019524</v>
       </c>
       <c r="Q23">
-        <v>5.1685166136</v>
+        <v>5.148019524</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1074273424454157</v>
+        <v>0.1080734668157807</v>
       </c>
       <c r="T23">
-        <v>0.8032108654939446</v>
+        <v>0.8116320320434722</v>
       </c>
       <c r="U23">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V23">
         <v>0.22</v>
       </c>
       <c r="W23">
-        <v>0.040404</v>
+        <v>0.04173</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y23">
-        <v>10.13940496046984</v>
+        <v>9.370981067119027</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09347790411630895</v>
+        <v>0.09332490770073953</v>
       </c>
       <c r="C24">
-        <v>27.97518548020626</v>
+        <v>27.78951458590585</v>
       </c>
       <c r="D24">
-        <v>33.83638548020627</v>
+        <v>33.94531458590585</v>
       </c>
       <c r="E24">
-        <v>-13.0188</v>
+        <v>-12.7242</v>
       </c>
       <c r="F24">
-        <v>6.4812</v>
+        <v>6.7758</v>
       </c>
       <c r="G24">
         <v>0.62</v>
@@ -3243,28 +3243,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M24">
-        <v>0.3467442</v>
+        <v>0.3625053</v>
       </c>
       <c r="N24">
-        <v>2.902589133333334</v>
+        <v>2.886828033333333</v>
       </c>
       <c r="O24">
-        <v>0.6385696093333334</v>
+        <v>0.6351021673333334</v>
       </c>
       <c r="P24">
-        <v>2.264019524</v>
+        <v>2.251725866</v>
       </c>
       <c r="Q24">
-        <v>5.148019524</v>
+        <v>5.135725866</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1080734668157807</v>
+        <v>0.1087363736373241</v>
       </c>
       <c r="T24">
-        <v>0.8116320320434722</v>
+        <v>0.820271930191689</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>9.370981067119027</v>
+        <v>8.963547107679069</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09332490770073953</v>
+        <v>0.09317191128517008</v>
       </c>
       <c r="C25">
-        <v>27.78951458590585</v>
+        <v>27.60454730529851</v>
       </c>
       <c r="D25">
-        <v>33.94531458590585</v>
+        <v>34.05494730529851</v>
       </c>
       <c r="E25">
-        <v>-12.7242</v>
+        <v>-12.4296</v>
       </c>
       <c r="F25">
-        <v>6.7758</v>
+        <v>7.070400000000001</v>
       </c>
       <c r="G25">
         <v>0.62</v>
@@ -3325,28 +3325,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M25">
-        <v>0.3625053</v>
+        <v>0.3782664000000001</v>
       </c>
       <c r="N25">
-        <v>2.886828033333333</v>
+        <v>2.871066933333333</v>
       </c>
       <c r="O25">
-        <v>0.6351021673333334</v>
+        <v>0.6316347253333333</v>
       </c>
       <c r="P25">
-        <v>2.251725866</v>
+        <v>2.239432208</v>
       </c>
       <c r="Q25">
-        <v>5.135725866</v>
+        <v>5.123432208000001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1087363736373241</v>
+        <v>0.1094167253752238</v>
       </c>
       <c r="T25">
-        <v>0.820271930191689</v>
+        <v>0.8291391940806482</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.963547107679069</v>
+        <v>8.59006597819244</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09317191128517008</v>
+        <v>0.09301891486960064</v>
       </c>
       <c r="C26">
-        <v>27.60454730529851</v>
+        <v>27.4202904778281</v>
       </c>
       <c r="D26">
-        <v>34.05494730529851</v>
+        <v>34.16529047782811</v>
       </c>
       <c r="E26">
-        <v>-12.4296</v>
+        <v>-12.135</v>
       </c>
       <c r="F26">
-        <v>7.0704</v>
+        <v>7.365</v>
       </c>
       <c r="G26">
         <v>0.62</v>
@@ -3407,28 +3407,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M26">
-        <v>0.3782664</v>
+        <v>0.3940275</v>
       </c>
       <c r="N26">
-        <v>2.871066933333333</v>
+        <v>2.855305833333333</v>
       </c>
       <c r="O26">
-        <v>0.6316347253333333</v>
+        <v>0.6281672833333334</v>
       </c>
       <c r="P26">
-        <v>2.239432208</v>
+        <v>2.22713855</v>
       </c>
       <c r="Q26">
-        <v>5.123432208000001</v>
+        <v>5.111138550000001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1094167253752238</v>
+        <v>0.1101152198261342</v>
       </c>
       <c r="T26">
-        <v>0.8291391940806482</v>
+        <v>0.8382429183399795</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.590065978192442</v>
+        <v>8.246463339064743</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09301891486960064</v>
+        <v>0.09286591845403119</v>
       </c>
       <c r="C27">
-        <v>27.4202904778281</v>
+        <v>27.23675103187002</v>
       </c>
       <c r="D27">
-        <v>34.16529047782811</v>
+        <v>34.27635103187003</v>
       </c>
       <c r="E27">
-        <v>-12.135</v>
+        <v>-11.8404</v>
       </c>
       <c r="F27">
-        <v>7.365</v>
+        <v>7.6596</v>
       </c>
       <c r="G27">
         <v>0.62</v>
@@ -3489,28 +3489,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M27">
-        <v>0.3940275</v>
+        <v>0.4097886</v>
       </c>
       <c r="N27">
-        <v>2.855305833333333</v>
+        <v>2.839544733333333</v>
       </c>
       <c r="O27">
-        <v>0.6281672833333334</v>
+        <v>0.6246998413333333</v>
       </c>
       <c r="P27">
-        <v>2.22713855</v>
+        <v>2.214844892</v>
       </c>
       <c r="Q27">
-        <v>5.111138550000001</v>
+        <v>5.098844892000001</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1101152198261342</v>
+        <v>0.1108325925054476</v>
       </c>
       <c r="T27">
-        <v>0.8382429183399795</v>
+        <v>0.8475926892009146</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.246463339064743</v>
+        <v>7.929291672177638</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09286591845403119</v>
+        <v>0.09271292203846175</v>
       </c>
       <c r="C28">
-        <v>27.23675103187002</v>
+        <v>27.05393598618127</v>
       </c>
       <c r="D28">
-        <v>34.27635103187003</v>
+        <v>34.38813598618127</v>
       </c>
       <c r="E28">
-        <v>-11.8404</v>
+        <v>-11.5458</v>
       </c>
       <c r="F28">
-        <v>7.6596</v>
+        <v>7.954200000000001</v>
       </c>
       <c r="G28">
         <v>0.62</v>
@@ -3571,28 +3571,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M28">
-        <v>0.4097886</v>
+        <v>0.4255497</v>
       </c>
       <c r="N28">
-        <v>2.839544733333333</v>
+        <v>2.823783633333333</v>
       </c>
       <c r="O28">
-        <v>0.6246998413333333</v>
+        <v>0.6212323993333334</v>
       </c>
       <c r="P28">
-        <v>2.214844892</v>
+        <v>2.202551234</v>
       </c>
       <c r="Q28">
-        <v>5.098844892000001</v>
+        <v>5.086551234</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1108325925054476</v>
+        <v>0.1115696192307695</v>
       </c>
       <c r="T28">
-        <v>0.8475926892009146</v>
+        <v>0.8571986181676287</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.929291672177638</v>
+        <v>7.635614202837726</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09271292203846175</v>
+        <v>0.09273464562289233</v>
       </c>
       <c r="C29">
-        <v>27.05393598618127</v>
+        <v>26.74341952264794</v>
       </c>
       <c r="D29">
-        <v>34.38813598618127</v>
+        <v>34.37221952264795</v>
       </c>
       <c r="E29">
-        <v>-11.5458</v>
+        <v>-11.2512</v>
       </c>
       <c r="F29">
-        <v>7.954200000000001</v>
+        <v>8.248800000000001</v>
       </c>
       <c r="G29">
         <v>0.62</v>
@@ -3653,45 +3653,45 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M29">
-        <v>0.4255497</v>
+        <v>0.4479098400000001</v>
       </c>
       <c r="N29">
-        <v>2.823783633333333</v>
+        <v>2.801423493333334</v>
       </c>
       <c r="O29">
-        <v>0.6212323993333334</v>
+        <v>0.6163131685333334</v>
       </c>
       <c r="P29">
-        <v>2.202551234</v>
+        <v>2.1851103248</v>
       </c>
       <c r="Q29">
-        <v>5.086551234</v>
+        <v>5.0691103248</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1115696192307695</v>
+        <v>0.1123271189206838</v>
       </c>
       <c r="T29">
-        <v>0.8571986181676287</v>
+        <v>0.8670713784945292</v>
       </c>
       <c r="U29">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V29">
         <v>0.22</v>
       </c>
       <c r="W29">
-        <v>0.04173</v>
+        <v>0.042354</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y29">
-        <v>7.635614202837726</v>
+        <v>7.254436145750522</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09273464562289233</v>
+        <v>0.09258788920732286</v>
       </c>
       <c r="C30">
-        <v>26.74341952264794</v>
+        <v>26.55663254473061</v>
       </c>
       <c r="D30">
-        <v>34.37221952264795</v>
+        <v>34.48003254473062</v>
       </c>
       <c r="E30">
-        <v>-11.2512</v>
+        <v>-10.9566</v>
       </c>
       <c r="F30">
-        <v>8.248800000000001</v>
+        <v>8.543400000000002</v>
       </c>
       <c r="G30">
         <v>0.62</v>
@@ -3735,28 +3735,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M30">
-        <v>0.4479098400000001</v>
+        <v>0.4639066200000001</v>
       </c>
       <c r="N30">
-        <v>2.801423493333334</v>
+        <v>2.785426713333333</v>
       </c>
       <c r="O30">
-        <v>0.6163131685333334</v>
+        <v>0.6127938769333333</v>
       </c>
       <c r="P30">
-        <v>2.1851103248</v>
+        <v>2.1726328364</v>
       </c>
       <c r="Q30">
-        <v>5.0691103248</v>
+        <v>5.0566328364</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1123271189206838</v>
+        <v>0.1131059566300322</v>
       </c>
       <c r="T30">
-        <v>0.8670713784945292</v>
+        <v>0.8772222447461311</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>7.254436145750522</v>
+        <v>7.004283175207401</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09258788920732286</v>
+        <v>0.09244113279175342</v>
       </c>
       <c r="C31">
-        <v>26.55663254473062</v>
+        <v>26.37052403458304</v>
       </c>
       <c r="D31">
-        <v>34.48003254473062</v>
+        <v>34.58852403458305</v>
       </c>
       <c r="E31">
-        <v>-10.9566</v>
+        <v>-10.662</v>
       </c>
       <c r="F31">
-        <v>8.5434</v>
+        <v>8.837999999999999</v>
       </c>
       <c r="G31">
         <v>0.62</v>
@@ -3817,28 +3817,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M31">
-        <v>0.46390662</v>
+        <v>0.4799034</v>
       </c>
       <c r="N31">
-        <v>2.785426713333333</v>
+        <v>2.769429933333333</v>
       </c>
       <c r="O31">
-        <v>0.6127938769333333</v>
+        <v>0.6092745853333333</v>
       </c>
       <c r="P31">
-        <v>2.1726328364</v>
+        <v>2.160155348</v>
       </c>
       <c r="Q31">
-        <v>5.0566328364</v>
+        <v>5.044155348</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1131059566300322</v>
+        <v>0.113907046845362</v>
       </c>
       <c r="T31">
-        <v>0.8772222447461311</v>
+        <v>0.8876631357477788</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.004283175207402</v>
+        <v>6.770807069367155</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09244113279175342</v>
+        <v>0.09229437637618398</v>
       </c>
       <c r="C32">
-        <v>26.37052403458304</v>
+        <v>26.18510041682081</v>
       </c>
       <c r="D32">
-        <v>34.58852403458305</v>
+        <v>34.69770041682082</v>
       </c>
       <c r="E32">
-        <v>-10.662</v>
+        <v>-10.3674</v>
       </c>
       <c r="F32">
-        <v>8.837999999999999</v>
+        <v>9.1326</v>
       </c>
       <c r="G32">
         <v>0.62</v>
@@ -3899,28 +3899,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M32">
-        <v>0.4799034</v>
+        <v>0.49590018</v>
       </c>
       <c r="N32">
-        <v>2.769429933333333</v>
+        <v>2.753433153333333</v>
       </c>
       <c r="O32">
-        <v>0.6092745853333333</v>
+        <v>0.6057552937333334</v>
       </c>
       <c r="P32">
-        <v>2.160155348</v>
+        <v>2.1476778596</v>
       </c>
       <c r="Q32">
-        <v>5.044155348</v>
+        <v>5.0316778596</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.113907046845362</v>
+        <v>0.1147313570669333</v>
       </c>
       <c r="T32">
-        <v>0.8876631357477788</v>
+        <v>0.8984066612712135</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.770807069367155</v>
+        <v>6.552393938097246</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09229437637618398</v>
+        <v>0.09214761996061455</v>
       </c>
       <c r="C33">
-        <v>26.18510041682081</v>
+        <v>26.00036819743181</v>
       </c>
       <c r="D33">
-        <v>34.69770041682082</v>
+        <v>34.80756819743181</v>
       </c>
       <c r="E33">
-        <v>-10.3674</v>
+        <v>-10.0728</v>
       </c>
       <c r="F33">
-        <v>9.1326</v>
+        <v>9.427200000000001</v>
       </c>
       <c r="G33">
         <v>0.62</v>
@@ -3981,28 +3981,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M33">
-        <v>0.49590018</v>
+        <v>0.5118969600000001</v>
       </c>
       <c r="N33">
-        <v>2.753433153333333</v>
+        <v>2.737436373333333</v>
       </c>
       <c r="O33">
-        <v>0.6057552937333334</v>
+        <v>0.6022360021333334</v>
       </c>
       <c r="P33">
-        <v>2.1476778596</v>
+        <v>2.1352003712</v>
       </c>
       <c r="Q33">
-        <v>5.0316778596</v>
+        <v>5.0192003712</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1147313570669333</v>
+        <v>0.1155799117067861</v>
       </c>
       <c r="T33">
-        <v>0.8984066612712135</v>
+        <v>0.9094661728394551</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.552393938097246</v>
+        <v>6.347631627531706</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09214761996061455</v>
+        <v>0.09200086354504511</v>
       </c>
       <c r="C34">
-        <v>26.00036819743181</v>
+        <v>25.81633396506867</v>
       </c>
       <c r="D34">
-        <v>34.80756819743181</v>
+        <v>34.91813396506868</v>
       </c>
       <c r="E34">
-        <v>-10.0728</v>
+        <v>-9.7782</v>
       </c>
       <c r="F34">
-        <v>9.427200000000001</v>
+        <v>9.7218</v>
       </c>
       <c r="G34">
         <v>0.62</v>
@@ -4063,28 +4063,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M34">
-        <v>0.5118969600000001</v>
+        <v>0.52789374</v>
       </c>
       <c r="N34">
-        <v>2.737436373333333</v>
+        <v>2.721439593333333</v>
       </c>
       <c r="O34">
-        <v>0.6022360021333334</v>
+        <v>0.5987167105333333</v>
       </c>
       <c r="P34">
-        <v>2.1352003712</v>
+        <v>2.1227228828</v>
       </c>
       <c r="Q34">
-        <v>5.0192003712</v>
+        <v>5.0067228828</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1155799117067861</v>
+        <v>0.1164537963358882</v>
       </c>
       <c r="T34">
-        <v>0.9094661728394551</v>
+        <v>0.9208558190813754</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.347631627531706</v>
+        <v>6.155279153970141</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09200086354504511</v>
+        <v>0.09211930712947566</v>
       </c>
       <c r="C35">
-        <v>25.81633396506867</v>
+        <v>25.43244443971183</v>
       </c>
       <c r="D35">
-        <v>34.91813396506868</v>
+        <v>34.82884443971183</v>
       </c>
       <c r="E35">
-        <v>-9.7782</v>
+        <v>-9.483599999999999</v>
       </c>
       <c r="F35">
-        <v>9.7218</v>
+        <v>10.0164</v>
       </c>
       <c r="G35">
         <v>0.62</v>
@@ -4145,45 +4145,45 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M35">
-        <v>0.52789374</v>
+        <v>0.5539069200000001</v>
       </c>
       <c r="N35">
-        <v>2.721439593333333</v>
+        <v>2.695426413333333</v>
       </c>
       <c r="O35">
-        <v>0.5987167105333333</v>
+        <v>0.5929938109333334</v>
       </c>
       <c r="P35">
-        <v>2.1227228828</v>
+        <v>2.1024326024</v>
       </c>
       <c r="Q35">
-        <v>5.0067228828</v>
+        <v>4.986432602400001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1164537963358882</v>
+        <v>0.1173541623173874</v>
       </c>
       <c r="T35">
-        <v>0.9208558190813754</v>
+        <v>0.9325906061185054</v>
       </c>
       <c r="U35">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V35">
         <v>0.22</v>
       </c>
       <c r="W35">
-        <v>0.042354</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y35">
-        <v>6.155279153970141</v>
+        <v>5.866208231038769</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09211930712947566</v>
+        <v>0.09198035071390623</v>
       </c>
       <c r="C36">
-        <v>25.43244443971183</v>
+        <v>25.24264423674563</v>
       </c>
       <c r="D36">
-        <v>34.82884443971183</v>
+        <v>34.93364423674564</v>
       </c>
       <c r="E36">
-        <v>-9.483599999999999</v>
+        <v>-9.188999999999998</v>
       </c>
       <c r="F36">
-        <v>10.0164</v>
+        <v>10.311</v>
       </c>
       <c r="G36">
         <v>0.62</v>
@@ -4227,28 +4227,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M36">
-        <v>0.5539069200000001</v>
+        <v>0.5701983000000002</v>
       </c>
       <c r="N36">
-        <v>2.695426413333333</v>
+        <v>2.679135033333333</v>
       </c>
       <c r="O36">
-        <v>0.5929938109333334</v>
+        <v>0.5894097073333333</v>
       </c>
       <c r="P36">
-        <v>2.1024326024</v>
+        <v>2.089725326</v>
       </c>
       <c r="Q36">
-        <v>4.986432602400001</v>
+        <v>4.973725326</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1173541623173874</v>
+        <v>0.118282231867548</v>
       </c>
       <c r="T36">
-        <v>0.9325906061185054</v>
+        <v>0.9446864635260088</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.866208231038769</v>
+        <v>5.698602281580517</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09198035071390623</v>
+        <v>0.09184139429833678</v>
       </c>
       <c r="C37">
-        <v>25.24264423674563</v>
+        <v>25.05347662123126</v>
       </c>
       <c r="D37">
-        <v>34.93364423674564</v>
+        <v>35.03907662123127</v>
       </c>
       <c r="E37">
-        <v>-9.188999999999998</v>
+        <v>-8.894399999999999</v>
       </c>
       <c r="F37">
-        <v>10.311</v>
+        <v>10.6056</v>
       </c>
       <c r="G37">
         <v>0.62</v>
@@ -4309,28 +4309,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M37">
-        <v>0.5701983000000002</v>
+        <v>0.58648968</v>
       </c>
       <c r="N37">
-        <v>2.679135033333333</v>
+        <v>2.662843653333333</v>
       </c>
       <c r="O37">
-        <v>0.5894097073333333</v>
+        <v>0.5858256037333334</v>
       </c>
       <c r="P37">
-        <v>2.089725326</v>
+        <v>2.0770180496</v>
       </c>
       <c r="Q37">
-        <v>4.973725326</v>
+        <v>4.9610180496</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.118282231867548</v>
+        <v>0.1192393035911512</v>
       </c>
       <c r="T37">
-        <v>0.9446864635260088</v>
+        <v>0.9571603164774967</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.698602281580517</v>
+        <v>5.540307773758838</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09184139429833679</v>
+        <v>0.09170243788276734</v>
       </c>
       <c r="C38">
-        <v>25.05347662123126</v>
+        <v>24.86494733809785</v>
       </c>
       <c r="D38">
-        <v>35.03907662123126</v>
+        <v>35.14514733809785</v>
       </c>
       <c r="E38">
-        <v>-8.894400000000001</v>
+        <v>-8.5998</v>
       </c>
       <c r="F38">
-        <v>10.6056</v>
+        <v>10.9002</v>
       </c>
       <c r="G38">
         <v>0.62</v>
@@ -4391,28 +4391,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M38">
-        <v>0.58648968</v>
+        <v>0.60278106</v>
       </c>
       <c r="N38">
-        <v>2.662843653333333</v>
+        <v>2.646552273333334</v>
       </c>
       <c r="O38">
-        <v>0.5858256037333334</v>
+        <v>0.5822415001333334</v>
       </c>
       <c r="P38">
-        <v>2.0770180496</v>
+        <v>2.0643107732</v>
       </c>
       <c r="Q38">
-        <v>4.9610180496</v>
+        <v>4.9483107732</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1192393035911512</v>
+        <v>0.1202267585440751</v>
       </c>
       <c r="T38">
-        <v>0.9571603164774964</v>
+        <v>0.9700301647607775</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.540307773758838</v>
+        <v>5.39056972581941</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09170243788276734</v>
+        <v>0.09156348146719791</v>
       </c>
       <c r="C39">
-        <v>24.86494733809785</v>
+        <v>24.67706220205029</v>
       </c>
       <c r="D39">
-        <v>35.14514733809785</v>
+        <v>35.25186220205029</v>
       </c>
       <c r="E39">
-        <v>-8.5998</v>
+        <v>-8.305199999999999</v>
       </c>
       <c r="F39">
-        <v>10.9002</v>
+        <v>11.1948</v>
       </c>
       <c r="G39">
         <v>0.62</v>
@@ -4473,28 +4473,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M39">
-        <v>0.60278106</v>
+        <v>0.6190724400000001</v>
       </c>
       <c r="N39">
-        <v>2.646552273333334</v>
+        <v>2.630260893333333</v>
       </c>
       <c r="O39">
-        <v>0.5822415001333334</v>
+        <v>0.5786573965333334</v>
       </c>
       <c r="P39">
-        <v>2.0643107732</v>
+        <v>2.0516034968</v>
       </c>
       <c r="Q39">
-        <v>4.9483107732</v>
+        <v>4.935603496800001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1202267585440751</v>
+        <v>0.1212460668825773</v>
       </c>
       <c r="T39">
-        <v>0.9700301647607775</v>
+        <v>0.9833151694402935</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.39056972581941</v>
+        <v>5.24871262777153</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09156348146719791</v>
+        <v>0.09142452505162846</v>
       </c>
       <c r="C40">
-        <v>24.67706220205029</v>
+        <v>24.48982709863171</v>
       </c>
       <c r="D40">
-        <v>35.25186220205029</v>
+        <v>35.35922709863172</v>
       </c>
       <c r="E40">
-        <v>-8.305199999999999</v>
+        <v>-8.010599999999998</v>
       </c>
       <c r="F40">
-        <v>11.1948</v>
+        <v>11.4894</v>
       </c>
       <c r="G40">
         <v>0.62</v>
@@ -4555,28 +4555,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M40">
-        <v>0.6190724400000001</v>
+        <v>0.6353638200000001</v>
       </c>
       <c r="N40">
-        <v>2.630260893333333</v>
+        <v>2.613969513333333</v>
       </c>
       <c r="O40">
-        <v>0.5786573965333334</v>
+        <v>0.5750732929333333</v>
       </c>
       <c r="P40">
-        <v>2.0516034968</v>
+        <v>2.0388962204</v>
       </c>
       <c r="Q40">
-        <v>4.935603496800001</v>
+        <v>4.9228962204</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1212460668825773</v>
+        <v>0.122298795166604</v>
       </c>
       <c r="T40">
-        <v>0.9833151694402935</v>
+        <v>0.997035748043728</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.24871262777153</v>
+        <v>5.114130252700464</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09142452505162846</v>
+        <v>0.09128556863605904</v>
       </c>
       <c r="C41">
-        <v>24.48982709863171</v>
+        <v>24.30324798530556</v>
       </c>
       <c r="D41">
-        <v>35.35922709863172</v>
+        <v>35.46724798530556</v>
       </c>
       <c r="E41">
-        <v>-8.010599999999998</v>
+        <v>-7.715999999999999</v>
       </c>
       <c r="F41">
-        <v>11.4894</v>
+        <v>11.784</v>
       </c>
       <c r="G41">
         <v>0.62</v>
@@ -4637,28 +4637,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M41">
-        <v>0.6353638200000001</v>
+        <v>0.6516552000000001</v>
       </c>
       <c r="N41">
-        <v>2.613969513333333</v>
+        <v>2.597678133333333</v>
       </c>
       <c r="O41">
-        <v>0.5750732929333333</v>
+        <v>0.5714891893333334</v>
       </c>
       <c r="P41">
-        <v>2.0388962204</v>
+        <v>2.026188944</v>
       </c>
       <c r="Q41">
-        <v>4.9228962204</v>
+        <v>4.910188944000001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.122298795166604</v>
+        <v>0.1233866143934317</v>
       </c>
       <c r="T41">
-        <v>0.997035748043728</v>
+        <v>1.011213679267277</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.114130252700464</v>
+        <v>4.986276996382953</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09128556863605904</v>
+        <v>0.09114661222048959</v>
       </c>
       <c r="C42">
-        <v>24.30324798530556</v>
+        <v>24.11733089255754</v>
       </c>
       <c r="D42">
-        <v>35.46724798530556</v>
+        <v>35.57593089255754</v>
       </c>
       <c r="E42">
-        <v>-7.715999999999999</v>
+        <v>-7.421399999999998</v>
       </c>
       <c r="F42">
-        <v>11.784</v>
+        <v>12.0786</v>
       </c>
       <c r="G42">
         <v>0.62</v>
@@ -4719,28 +4719,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M42">
-        <v>0.6516552000000001</v>
+        <v>0.6679465800000001</v>
       </c>
       <c r="N42">
-        <v>2.597678133333333</v>
+        <v>2.581386753333333</v>
       </c>
       <c r="O42">
-        <v>0.5714891893333334</v>
+        <v>0.5679050857333333</v>
       </c>
       <c r="P42">
-        <v>2.026188944</v>
+        <v>2.0134816676</v>
       </c>
       <c r="Q42">
-        <v>4.910188944000001</v>
+        <v>4.8974816676</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1233866143934317</v>
+        <v>0.1245113088482874</v>
       </c>
       <c r="T42">
-        <v>1.011213679267277</v>
+        <v>1.025872218328912</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.986276996382953</v>
+        <v>4.864660484276053</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09114661222048959</v>
+        <v>0.09100765580492015</v>
       </c>
       <c r="C43">
-        <v>24.11733089255754</v>
+        <v>23.93208192501779</v>
       </c>
       <c r="D43">
-        <v>35.57593089255754</v>
+        <v>35.6852819250178</v>
       </c>
       <c r="E43">
-        <v>-7.421399999999998</v>
+        <v>-7.126799999999998</v>
       </c>
       <c r="F43">
-        <v>12.0786</v>
+        <v>12.3732</v>
       </c>
       <c r="G43">
         <v>0.62</v>
@@ -4801,28 +4801,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M43">
-        <v>0.6679465800000001</v>
+        <v>0.6842379600000001</v>
       </c>
       <c r="N43">
-        <v>2.581386753333333</v>
+        <v>2.565095373333333</v>
       </c>
       <c r="O43">
-        <v>0.5679050857333333</v>
+        <v>0.5643209821333334</v>
       </c>
       <c r="P43">
-        <v>2.0134816676</v>
+        <v>2.0007743912</v>
       </c>
       <c r="Q43">
-        <v>4.8974816676</v>
+        <v>4.884774391200001</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1245113088482874</v>
+        <v>0.125674785870552</v>
       </c>
       <c r="T43">
-        <v>1.025872218328912</v>
+        <v>1.041036224254742</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.864660484276053</v>
+        <v>4.748835234650432</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09100765580492015</v>
+        <v>0.09086869938935072</v>
       </c>
       <c r="C44">
-        <v>23.93208192501779</v>
+        <v>23.74750726260402</v>
       </c>
       <c r="D44">
-        <v>35.6852819250178</v>
+        <v>35.79530726260402</v>
       </c>
       <c r="E44">
-        <v>-7.126799999999999</v>
+        <v>-6.8322</v>
       </c>
       <c r="F44">
-        <v>12.3732</v>
+        <v>12.6678</v>
       </c>
       <c r="G44">
         <v>0.62</v>
@@ -4883,28 +4883,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M44">
-        <v>0.68423796</v>
+        <v>0.70052934</v>
       </c>
       <c r="N44">
-        <v>2.565095373333333</v>
+        <v>2.548803993333333</v>
       </c>
       <c r="O44">
-        <v>0.5643209821333334</v>
+        <v>0.5607368785333333</v>
       </c>
       <c r="P44">
-        <v>2.0007743912</v>
+        <v>1.9880671148</v>
       </c>
       <c r="Q44">
-        <v>4.884774391200001</v>
+        <v>4.8720671148</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.125674785870552</v>
+        <v>0.1268790866479837</v>
       </c>
       <c r="T44">
-        <v>1.041036224254742</v>
+        <v>1.056732300563934</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.748835234650432</v>
+        <v>4.638397205937632</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09086869938935072</v>
+        <v>0.09072974297378128</v>
       </c>
       <c r="C45">
-        <v>23.74750726260402</v>
+        <v>23.56361316168562</v>
       </c>
       <c r="D45">
-        <v>35.79530726260402</v>
+        <v>35.90601316168562</v>
       </c>
       <c r="E45">
-        <v>-6.8322</v>
+        <v>-6.537599999999999</v>
       </c>
       <c r="F45">
-        <v>12.6678</v>
+        <v>12.9624</v>
       </c>
       <c r="G45">
         <v>0.62</v>
@@ -4965,28 +4965,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M45">
-        <v>0.70052934</v>
+        <v>0.7168207200000001</v>
       </c>
       <c r="N45">
-        <v>2.548803993333333</v>
+        <v>2.532512613333333</v>
       </c>
       <c r="O45">
-        <v>0.5607368785333333</v>
+        <v>0.5571527749333333</v>
       </c>
       <c r="P45">
-        <v>1.9880671148</v>
+        <v>1.9753598384</v>
       </c>
       <c r="Q45">
-        <v>4.8720671148</v>
+        <v>4.8593598384</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1268790866479837</v>
+        <v>0.1281263981674665</v>
       </c>
       <c r="T45">
-        <v>1.056732300563934</v>
+        <v>1.072988951027026</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.638397205937632</v>
+        <v>4.532979087620866</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09072974297378128</v>
+        <v>0.09146828655821182</v>
       </c>
       <c r="C46">
-        <v>23.56361316168562</v>
+        <v>22.68834421915282</v>
       </c>
       <c r="D46">
-        <v>35.90601316168562</v>
+        <v>35.32534421915283</v>
       </c>
       <c r="E46">
-        <v>-6.537599999999999</v>
+        <v>-6.242999999999999</v>
       </c>
       <c r="F46">
-        <v>12.9624</v>
+        <v>13.257</v>
       </c>
       <c r="G46">
         <v>0.62</v>
@@ -5047,45 +5047,45 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M46">
-        <v>0.7168207200000001</v>
+        <v>0.7662546000000001</v>
       </c>
       <c r="N46">
-        <v>2.532512613333333</v>
+        <v>2.483078733333334</v>
       </c>
       <c r="O46">
-        <v>0.5571527749333333</v>
+        <v>0.5462773213333334</v>
       </c>
       <c r="P46">
-        <v>1.9753598384</v>
+        <v>1.936801412</v>
       </c>
       <c r="Q46">
-        <v>4.8593598384</v>
+        <v>4.820801412000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1281263981674665</v>
+        <v>0.129419066469476</v>
       </c>
       <c r="T46">
-        <v>1.072988951027026</v>
+        <v>1.089836752416048</v>
       </c>
       <c r="U46">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V46">
         <v>0.22</v>
       </c>
       <c r="W46">
-        <v>0.04313400000000001</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y46">
-        <v>4.532979087620866</v>
+        <v>4.240540067665934</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09146828655821182</v>
+        <v>0.09134883014264238</v>
       </c>
       <c r="C47">
-        <v>22.68834421915282</v>
+        <v>22.48638850850036</v>
       </c>
       <c r="D47">
-        <v>35.32534421915283</v>
+        <v>35.41798850850036</v>
       </c>
       <c r="E47">
-        <v>-6.242999999999999</v>
+        <v>-5.948399999999999</v>
       </c>
       <c r="F47">
-        <v>13.257</v>
+        <v>13.5516</v>
       </c>
       <c r="G47">
         <v>0.62</v>
@@ -5129,28 +5129,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M47">
-        <v>0.7662546000000001</v>
+        <v>0.7832824800000001</v>
       </c>
       <c r="N47">
-        <v>2.483078733333334</v>
+        <v>2.466050853333333</v>
       </c>
       <c r="O47">
-        <v>0.5462773213333334</v>
+        <v>0.5425311877333333</v>
       </c>
       <c r="P47">
-        <v>1.936801412</v>
+        <v>1.9235196656</v>
       </c>
       <c r="Q47">
-        <v>4.820801412000001</v>
+        <v>4.807519665600001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.129419066469476</v>
+        <v>0.1307596113752637</v>
       </c>
       <c r="T47">
-        <v>1.089836752416048</v>
+        <v>1.107308546449109</v>
       </c>
       <c r="U47">
         <v>0.0578</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.240540067665934</v>
+        <v>4.148354414021022</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09134883014264238</v>
+        <v>0.09122937372707293</v>
       </c>
       <c r="C48">
-        <v>22.48638850850036</v>
+        <v>22.28492001366535</v>
       </c>
       <c r="D48">
-        <v>35.41798850850036</v>
+        <v>35.51112001366536</v>
       </c>
       <c r="E48">
-        <v>-5.948399999999999</v>
+        <v>-5.653799999999999</v>
       </c>
       <c r="F48">
-        <v>13.5516</v>
+        <v>13.8462</v>
       </c>
       <c r="G48">
         <v>0.62</v>
@@ -5211,28 +5211,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M48">
-        <v>0.7832824800000001</v>
+        <v>0.8003103600000001</v>
       </c>
       <c r="N48">
-        <v>2.466050853333333</v>
+        <v>2.449022973333333</v>
       </c>
       <c r="O48">
-        <v>0.5425311877333333</v>
+        <v>0.5387850541333333</v>
       </c>
       <c r="P48">
-        <v>1.9235196656</v>
+        <v>1.9102379192</v>
       </c>
       <c r="Q48">
-        <v>4.807519665600001</v>
+        <v>4.7942379192</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1307596113752637</v>
+        <v>0.1321507428812697</v>
       </c>
       <c r="T48">
-        <v>1.107308546449109</v>
+        <v>1.125439653464549</v>
       </c>
       <c r="U48">
         <v>0.0578</v>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.148354414021022</v>
+        <v>4.060091554148235</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09122937372707293</v>
+        <v>0.09242031731150352</v>
       </c>
       <c r="C49">
-        <v>22.28492001366535</v>
+        <v>21.0831674459632</v>
       </c>
       <c r="D49">
-        <v>35.51112001366536</v>
+        <v>34.60396744596321</v>
       </c>
       <c r="E49">
-        <v>-5.653799999999999</v>
+        <v>-5.359199999999998</v>
       </c>
       <c r="F49">
-        <v>13.8462</v>
+        <v>14.1408</v>
       </c>
       <c r="G49">
         <v>0.62</v>
@@ -5293,45 +5293,45 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M49">
-        <v>0.8003103600000001</v>
+        <v>0.8668310400000001</v>
       </c>
       <c r="N49">
-        <v>2.449022973333333</v>
+        <v>2.382502293333333</v>
       </c>
       <c r="O49">
-        <v>0.5387850541333333</v>
+        <v>0.5241505045333333</v>
       </c>
       <c r="P49">
-        <v>1.9102379192</v>
+        <v>1.8583517888</v>
       </c>
       <c r="Q49">
-        <v>4.7942379192</v>
+        <v>4.742351788800001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1321507428812697</v>
+        <v>0.1335953794451991</v>
       </c>
       <c r="T49">
-        <v>1.125439653464549</v>
+        <v>1.144268110749814</v>
       </c>
       <c r="U49">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V49">
         <v>0.22</v>
       </c>
       <c r="W49">
-        <v>0.04508400000000001</v>
+        <v>0.047814</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y49">
-        <v>4.060091554148235</v>
+        <v>3.748519819194907</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09242031731150349</v>
+        <v>0.09232816089593406</v>
       </c>
       <c r="C50">
-        <v>21.08316744596323</v>
+        <v>20.85710610175566</v>
       </c>
       <c r="D50">
-        <v>34.60396744596323</v>
+        <v>34.67250610175567</v>
       </c>
       <c r="E50">
-        <v>-5.3592</v>
+        <v>-5.0646</v>
       </c>
       <c r="F50">
-        <v>14.1408</v>
+        <v>14.4354</v>
       </c>
       <c r="G50">
         <v>0.62</v>
@@ -5375,28 +5375,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M50">
-        <v>0.86683104</v>
+        <v>0.8848900199999999</v>
       </c>
       <c r="N50">
-        <v>2.382502293333333</v>
+        <v>2.364443313333334</v>
       </c>
       <c r="O50">
-        <v>0.5241505045333333</v>
+        <v>0.5201775289333334</v>
       </c>
       <c r="P50">
-        <v>1.8583517888</v>
+        <v>1.8442657844</v>
       </c>
       <c r="Q50">
-        <v>4.742351788800001</v>
+        <v>4.7282657844</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.133595379445199</v>
+        <v>0.1350966684234001</v>
       </c>
       <c r="T50">
-        <v>1.144268110749813</v>
+        <v>1.16383493890901</v>
       </c>
       <c r="U50">
         <v>0.0613</v>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.748519819194907</v>
+        <v>3.672019414721542</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09232816089593406</v>
+        <v>0.09223600448036461</v>
       </c>
       <c r="C51">
-        <v>20.85710610175566</v>
+        <v>20.63131679976692</v>
       </c>
       <c r="D51">
-        <v>34.67250610175567</v>
+        <v>34.74131679976692</v>
       </c>
       <c r="E51">
-        <v>-5.0646</v>
+        <v>-4.77</v>
       </c>
       <c r="F51">
-        <v>14.4354</v>
+        <v>14.73</v>
       </c>
       <c r="G51">
         <v>0.62</v>
@@ -5457,28 +5457,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M51">
-        <v>0.8848900199999999</v>
+        <v>0.902949</v>
       </c>
       <c r="N51">
-        <v>2.364443313333334</v>
+        <v>2.346384333333333</v>
       </c>
       <c r="O51">
-        <v>0.5201775289333334</v>
+        <v>0.5162045533333334</v>
       </c>
       <c r="P51">
-        <v>1.8442657844</v>
+        <v>1.83017978</v>
       </c>
       <c r="Q51">
-        <v>4.7282657844</v>
+        <v>4.71417978</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1350966684234001</v>
+        <v>0.1366580089607292</v>
       </c>
       <c r="T51">
-        <v>1.16383493890901</v>
+        <v>1.184184440194574</v>
       </c>
       <c r="U51">
         <v>0.0613</v>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.672019414721542</v>
+        <v>3.598579026427111</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09223600448036461</v>
+        <v>0.09214384806479517</v>
       </c>
       <c r="C52">
-        <v>20.63131679976692</v>
+        <v>20.4058011628943</v>
       </c>
       <c r="D52">
-        <v>34.74131679976692</v>
+        <v>34.8104011628943</v>
       </c>
       <c r="E52">
-        <v>-4.77</v>
+        <v>-4.475399999999999</v>
       </c>
       <c r="F52">
-        <v>14.73</v>
+        <v>15.0246</v>
       </c>
       <c r="G52">
         <v>0.62</v>
@@ -5539,28 +5539,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M52">
-        <v>0.902949</v>
+        <v>0.9210079800000001</v>
       </c>
       <c r="N52">
-        <v>2.346384333333333</v>
+        <v>2.328325353333333</v>
       </c>
       <c r="O52">
-        <v>0.5162045533333334</v>
+        <v>0.5122315777333333</v>
       </c>
       <c r="P52">
-        <v>1.83017978</v>
+        <v>1.8160937756</v>
       </c>
       <c r="Q52">
-        <v>4.71417978</v>
+        <v>4.7000937756</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1366580089607292</v>
+        <v>0.1382830776832555</v>
       </c>
       <c r="T52">
-        <v>1.184184440194574</v>
+        <v>1.205364533369345</v>
       </c>
       <c r="U52">
         <v>0.0613</v>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.598579026427111</v>
+        <v>3.528018653359912</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09214384806479517</v>
+        <v>0.09318737164922573</v>
       </c>
       <c r="C53">
-        <v>20.4058011628943</v>
+        <v>19.34463671053639</v>
       </c>
       <c r="D53">
-        <v>34.8104011628943</v>
+        <v>34.0438367105364</v>
       </c>
       <c r="E53">
-        <v>-4.475399999999999</v>
+        <v>-4.1808</v>
       </c>
       <c r="F53">
-        <v>15.0246</v>
+        <v>15.3192</v>
       </c>
       <c r="G53">
         <v>0.62</v>
@@ -5621,45 +5621,45 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M53">
-        <v>0.9210079800000001</v>
+        <v>0.9819607200000001</v>
       </c>
       <c r="N53">
-        <v>2.328325353333333</v>
+        <v>2.267372613333333</v>
       </c>
       <c r="O53">
-        <v>0.5122315777333333</v>
+        <v>0.4988219749333334</v>
       </c>
       <c r="P53">
-        <v>1.8160937756</v>
+        <v>1.7685506384</v>
       </c>
       <c r="Q53">
-        <v>4.7000937756</v>
+        <v>4.6525506384</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1382830776832555</v>
+        <v>0.1399758576025536</v>
       </c>
       <c r="T53">
-        <v>1.205364533369345</v>
+        <v>1.227427130426399</v>
       </c>
       <c r="U53">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V53">
         <v>0.22</v>
       </c>
       <c r="W53">
-        <v>0.047814</v>
+        <v>0.04999800000000001</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y53">
-        <v>3.528018653359912</v>
+        <v>3.309025775830762</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09318737164922573</v>
+        <v>0.09311705523365629</v>
       </c>
       <c r="C54">
-        <v>19.34463671053639</v>
+        <v>19.10062820567267</v>
       </c>
       <c r="D54">
-        <v>34.0438367105364</v>
+        <v>34.09442820567267</v>
       </c>
       <c r="E54">
-        <v>-4.1808</v>
+        <v>-3.886199999999999</v>
       </c>
       <c r="F54">
-        <v>15.3192</v>
+        <v>15.6138</v>
       </c>
       <c r="G54">
         <v>0.62</v>
@@ -5703,28 +5703,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M54">
-        <v>0.9819607200000001</v>
+        <v>1.00084458</v>
       </c>
       <c r="N54">
-        <v>2.267372613333333</v>
+        <v>2.248488753333334</v>
       </c>
       <c r="O54">
-        <v>0.4988219749333334</v>
+        <v>0.4946675257333334</v>
       </c>
       <c r="P54">
-        <v>1.7685506384</v>
+        <v>1.7538212276</v>
       </c>
       <c r="Q54">
-        <v>4.6525506384</v>
+        <v>4.6378212276</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1399758576025536</v>
+        <v>0.141740670709907</v>
       </c>
       <c r="T54">
-        <v>1.227427130426399</v>
+        <v>1.250428561400773</v>
       </c>
       <c r="U54">
         <v>0.0641</v>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.309025775830762</v>
+        <v>3.246591327230181</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09311705523365629</v>
+        <v>0.09304673881808687</v>
       </c>
       <c r="C55">
-        <v>19.10062820567267</v>
+        <v>18.85677028951348</v>
       </c>
       <c r="D55">
-        <v>34.09442820567267</v>
+        <v>34.14517028951348</v>
       </c>
       <c r="E55">
-        <v>-3.886199999999999</v>
+        <v>-3.591599999999998</v>
       </c>
       <c r="F55">
-        <v>15.6138</v>
+        <v>15.9084</v>
       </c>
       <c r="G55">
         <v>0.62</v>
@@ -5785,28 +5785,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M55">
-        <v>1.00084458</v>
+        <v>1.01972844</v>
       </c>
       <c r="N55">
-        <v>2.248488753333334</v>
+        <v>2.229604893333333</v>
       </c>
       <c r="O55">
-        <v>0.4946675257333334</v>
+        <v>0.4905130765333333</v>
       </c>
       <c r="P55">
-        <v>1.7538212276</v>
+        <v>1.7390918168</v>
       </c>
       <c r="Q55">
-        <v>4.6378212276</v>
+        <v>4.623091816800001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.141740670709907</v>
+        <v>0.143582214821928</v>
       </c>
       <c r="T55">
-        <v>1.250428561400773</v>
+        <v>1.274430054591425</v>
       </c>
       <c r="U55">
         <v>0.0641</v>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.246591327230181</v>
+        <v>3.186469265614807</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09304673881808687</v>
+        <v>0.09297642240251741</v>
       </c>
       <c r="C56">
-        <v>18.85677028951348</v>
+        <v>18.61306363541583</v>
       </c>
       <c r="D56">
-        <v>34.14517028951348</v>
+        <v>34.19606363541583</v>
       </c>
       <c r="E56">
-        <v>-3.591599999999998</v>
+        <v>-3.296999999999997</v>
       </c>
       <c r="F56">
-        <v>15.9084</v>
+        <v>16.203</v>
       </c>
       <c r="G56">
         <v>0.62</v>
@@ -5867,28 +5867,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M56">
-        <v>1.01972844</v>
+        <v>1.0386123</v>
       </c>
       <c r="N56">
-        <v>2.229604893333333</v>
+        <v>2.210721033333333</v>
       </c>
       <c r="O56">
-        <v>0.4905130765333333</v>
+        <v>0.4863586273333332</v>
       </c>
       <c r="P56">
-        <v>1.7390918168</v>
+        <v>1.724362406</v>
       </c>
       <c r="Q56">
-        <v>4.623091816800001</v>
+        <v>4.608362405999999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.143582214821928</v>
+        <v>0.1455056053389276</v>
       </c>
       <c r="T56">
-        <v>1.274430054591425</v>
+        <v>1.299498280812773</v>
       </c>
       <c r="U56">
         <v>0.0641</v>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.186469265614807</v>
+        <v>3.128533460785446</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09297642240251741</v>
+        <v>0.09290610598694797</v>
       </c>
       <c r="C57">
-        <v>18.61306363541583</v>
+        <v>18.36950892075725</v>
       </c>
       <c r="D57">
-        <v>34.19606363541583</v>
+        <v>34.24710892075726</v>
       </c>
       <c r="E57">
-        <v>-3.296999999999997</v>
+        <v>-3.002399999999998</v>
       </c>
       <c r="F57">
-        <v>16.203</v>
+        <v>16.4976</v>
       </c>
       <c r="G57">
         <v>0.62</v>
@@ -5949,28 +5949,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M57">
-        <v>1.0386123</v>
+        <v>1.05749616</v>
       </c>
       <c r="N57">
-        <v>2.210721033333333</v>
+        <v>2.191837173333333</v>
       </c>
       <c r="O57">
-        <v>0.4863586273333332</v>
+        <v>0.4822041781333333</v>
       </c>
       <c r="P57">
-        <v>1.724362406</v>
+        <v>1.7096329952</v>
       </c>
       <c r="Q57">
-        <v>4.608362405999999</v>
+        <v>4.5936329952</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1455056053389276</v>
+        <v>0.147516422697609</v>
       </c>
       <c r="T57">
-        <v>1.299498280812773</v>
+        <v>1.325705971862363</v>
       </c>
       <c r="U57">
         <v>0.0641</v>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.128533460785446</v>
+        <v>3.072666791842849</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09290610598694797</v>
+        <v>0.09283578957137853</v>
       </c>
       <c r="C58">
-        <v>18.36950892075725</v>
+        <v>18.12610682696587</v>
       </c>
       <c r="D58">
-        <v>34.24710892075726</v>
+        <v>34.29830682696588</v>
       </c>
       <c r="E58">
-        <v>-3.002399999999998</v>
+        <v>-2.707799999999999</v>
       </c>
       <c r="F58">
-        <v>16.4976</v>
+        <v>16.7922</v>
       </c>
       <c r="G58">
         <v>0.62</v>
@@ -6031,28 +6031,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M58">
-        <v>1.05749616</v>
+        <v>1.07638002</v>
       </c>
       <c r="N58">
-        <v>2.191837173333333</v>
+        <v>2.172953313333333</v>
       </c>
       <c r="O58">
-        <v>0.4822041781333333</v>
+        <v>0.4780497289333333</v>
       </c>
       <c r="P58">
-        <v>1.7096329952</v>
+        <v>1.6949035844</v>
       </c>
       <c r="Q58">
-        <v>4.5936329952</v>
+        <v>4.578903584400001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.147516422697609</v>
+        <v>0.1496207664450664</v>
       </c>
       <c r="T58">
-        <v>1.325705971862363</v>
+        <v>1.353132625286353</v>
       </c>
       <c r="U58">
         <v>0.0641</v>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.072666791842849</v>
+        <v>3.018760356898238</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09283578957137853</v>
+        <v>0.0962941931558091</v>
       </c>
       <c r="C59">
-        <v>18.12610682696587</v>
+        <v>15.4823775537391</v>
       </c>
       <c r="D59">
-        <v>34.29830682696588</v>
+        <v>31.9491775537391</v>
       </c>
       <c r="E59">
-        <v>-2.707799999999999</v>
+        <v>-2.413199999999996</v>
       </c>
       <c r="F59">
-        <v>16.7922</v>
+        <v>17.0868</v>
       </c>
       <c r="G59">
         <v>0.62</v>
@@ -6113,45 +6113,45 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M59">
-        <v>1.07638002</v>
+        <v>1.22854092</v>
       </c>
       <c r="N59">
-        <v>2.172953313333333</v>
+        <v>2.020792413333333</v>
       </c>
       <c r="O59">
-        <v>0.4780497289333333</v>
+        <v>0.4445743309333333</v>
       </c>
       <c r="P59">
-        <v>1.6949035844</v>
+        <v>1.5762180824</v>
       </c>
       <c r="Q59">
-        <v>4.578903584400001</v>
+        <v>4.4602180824</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1496207664450664</v>
+        <v>0.1518253170376407</v>
       </c>
       <c r="T59">
-        <v>1.353132625286353</v>
+        <v>1.381865309825771</v>
       </c>
       <c r="U59">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V59">
         <v>0.22</v>
       </c>
       <c r="W59">
-        <v>0.04999800000000001</v>
+        <v>0.05608200000000001</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y59">
-        <v>3.018760356898238</v>
+        <v>2.64487188048513</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09629419315580909</v>
+        <v>0.09628471674023965</v>
       </c>
       <c r="C60">
-        <v>15.48237755373911</v>
+        <v>15.19377468917237</v>
       </c>
       <c r="D60">
-        <v>31.94917755373911</v>
+        <v>31.95517468917237</v>
       </c>
       <c r="E60">
-        <v>-2.4132</v>
+        <v>-2.118600000000001</v>
       </c>
       <c r="F60">
-        <v>17.0868</v>
+        <v>17.3814</v>
       </c>
       <c r="G60">
         <v>0.62</v>
@@ -6195,28 +6195,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M60">
-        <v>1.22854092</v>
+        <v>1.24972266</v>
       </c>
       <c r="N60">
-        <v>2.020792413333333</v>
+        <v>1.999610673333333</v>
       </c>
       <c r="O60">
-        <v>0.4445743309333333</v>
+        <v>0.4399143481333334</v>
       </c>
       <c r="P60">
-        <v>1.5762180824</v>
+        <v>1.5596963252</v>
       </c>
       <c r="Q60">
-        <v>4.4602180824</v>
+        <v>4.4436963252</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1518253170376407</v>
+        <v>0.1541374066835113</v>
       </c>
       <c r="T60">
-        <v>1.381865309825771</v>
+        <v>1.411999588732966</v>
       </c>
       <c r="U60">
         <v>0.07190000000000001</v>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.644871880485131</v>
+        <v>2.600043543527756</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09628471674023965</v>
+        <v>0.09627524032467022</v>
       </c>
       <c r="C61">
-        <v>15.19377468917237</v>
+        <v>14.90517407645612</v>
       </c>
       <c r="D61">
-        <v>31.95517468917237</v>
+        <v>31.96117407645612</v>
       </c>
       <c r="E61">
-        <v>-2.118600000000001</v>
+        <v>-1.824000000000002</v>
       </c>
       <c r="F61">
-        <v>17.3814</v>
+        <v>17.676</v>
       </c>
       <c r="G61">
         <v>0.62</v>
@@ -6277,28 +6277,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M61">
-        <v>1.24972266</v>
+        <v>1.2709044</v>
       </c>
       <c r="N61">
-        <v>1.999610673333333</v>
+        <v>1.978428933333333</v>
       </c>
       <c r="O61">
-        <v>0.4399143481333334</v>
+        <v>0.4352543653333333</v>
       </c>
       <c r="P61">
-        <v>1.5596963252</v>
+        <v>1.543174568</v>
       </c>
       <c r="Q61">
-        <v>4.4436963252</v>
+        <v>4.427174568</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1541374066835113</v>
+        <v>0.1565651008116755</v>
       </c>
       <c r="T61">
-        <v>1.411999588732966</v>
+        <v>1.44364058158552</v>
       </c>
       <c r="U61">
         <v>0.07190000000000001</v>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.600043543527756</v>
+        <v>2.55670948446896</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09627524032467022</v>
+        <v>0.09626576390910077</v>
       </c>
       <c r="C62">
-        <v>14.90517407645612</v>
+        <v>14.61657571685894</v>
       </c>
       <c r="D62">
-        <v>31.96117407645612</v>
+        <v>31.96717571685895</v>
       </c>
       <c r="E62">
-        <v>-1.824000000000002</v>
+        <v>-1.529399999999999</v>
       </c>
       <c r="F62">
-        <v>17.676</v>
+        <v>17.9706</v>
       </c>
       <c r="G62">
         <v>0.62</v>
@@ -6359,28 +6359,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M62">
-        <v>1.2709044</v>
+        <v>1.29208614</v>
       </c>
       <c r="N62">
-        <v>1.978428933333333</v>
+        <v>1.957247193333333</v>
       </c>
       <c r="O62">
-        <v>0.4352543653333333</v>
+        <v>0.4305943825333333</v>
       </c>
       <c r="P62">
-        <v>1.543174568</v>
+        <v>1.5266528108</v>
       </c>
       <c r="Q62">
-        <v>4.427174568</v>
+        <v>4.4106528108</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1565651008116755</v>
+        <v>0.1591172920746173</v>
       </c>
       <c r="T62">
-        <v>1.44364058158552</v>
+        <v>1.476904189456154</v>
       </c>
       <c r="U62">
         <v>0.07190000000000001</v>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.55670948446896</v>
+        <v>2.514796214231764</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09626576390910077</v>
+        <v>0.09814232749353133</v>
       </c>
       <c r="C63">
-        <v>14.61657571685894</v>
+        <v>13.17589680290993</v>
       </c>
       <c r="D63">
-        <v>31.96717571685895</v>
+        <v>30.82109680290992</v>
       </c>
       <c r="E63">
-        <v>-1.529399999999999</v>
+        <v>-1.2348</v>
       </c>
       <c r="F63">
-        <v>17.9706</v>
+        <v>18.2652</v>
       </c>
       <c r="G63">
         <v>0.62</v>
@@ -6441,45 +6441,45 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M63">
-        <v>1.29208614</v>
+        <v>1.38450216</v>
       </c>
       <c r="N63">
-        <v>1.957247193333333</v>
+        <v>1.864831173333333</v>
       </c>
       <c r="O63">
-        <v>0.4305943825333333</v>
+        <v>0.4102628581333334</v>
       </c>
       <c r="P63">
-        <v>1.5266528108</v>
+        <v>1.4545683152</v>
       </c>
       <c r="Q63">
-        <v>4.4106528108</v>
+        <v>4.3385683152</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1591172920746173</v>
+        <v>0.1618038091935035</v>
       </c>
       <c r="T63">
-        <v>1.476904189456154</v>
+        <v>1.511918513530506</v>
       </c>
       <c r="U63">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V63">
         <v>0.22</v>
       </c>
       <c r="W63">
-        <v>0.05608200000000001</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y63">
-        <v>2.514796214231764</v>
+        <v>2.346932657247232</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09814232749353133</v>
+        <v>0.09816327107796188</v>
       </c>
       <c r="C64">
-        <v>13.17589680290993</v>
+        <v>12.86896937893802</v>
       </c>
       <c r="D64">
-        <v>30.82109680290992</v>
+        <v>30.80876937893802</v>
       </c>
       <c r="E64">
-        <v>-1.2348</v>
+        <v>-0.9402000000000008</v>
       </c>
       <c r="F64">
-        <v>18.2652</v>
+        <v>18.5598</v>
       </c>
       <c r="G64">
         <v>0.62</v>
@@ -6523,28 +6523,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M64">
-        <v>1.38450216</v>
+        <v>1.40683284</v>
       </c>
       <c r="N64">
-        <v>1.864831173333333</v>
+        <v>1.842500493333333</v>
       </c>
       <c r="O64">
-        <v>0.4102628581333334</v>
+        <v>0.4053501085333333</v>
       </c>
       <c r="P64">
-        <v>1.4545683152</v>
+        <v>1.4371503848</v>
       </c>
       <c r="Q64">
-        <v>4.3385683152</v>
+        <v>4.3211503848</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1618038091935035</v>
+        <v>0.164635543453951</v>
       </c>
       <c r="T64">
-        <v>1.511918513530506</v>
+        <v>1.548825503771039</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.346932657247232</v>
+        <v>2.309679757925848</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09816327107796188</v>
+        <v>0.09818421466239247</v>
       </c>
       <c r="C65">
-        <v>12.86896937893802</v>
+        <v>12.56205181215099</v>
       </c>
       <c r="D65">
-        <v>30.80876937893802</v>
+        <v>30.79645181215099</v>
       </c>
       <c r="E65">
-        <v>-0.9402000000000008</v>
+        <v>-0.6455999999999982</v>
       </c>
       <c r="F65">
-        <v>18.5598</v>
+        <v>18.8544</v>
       </c>
       <c r="G65">
         <v>0.62</v>
@@ -6605,28 +6605,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M65">
-        <v>1.40683284</v>
+        <v>1.42916352</v>
       </c>
       <c r="N65">
-        <v>1.842500493333333</v>
+        <v>1.820169813333333</v>
       </c>
       <c r="O65">
-        <v>0.4053501085333333</v>
+        <v>0.4004373589333333</v>
       </c>
       <c r="P65">
-        <v>1.4371503848</v>
+        <v>1.4197324544</v>
       </c>
       <c r="Q65">
-        <v>4.3211503848</v>
+        <v>4.3037324544</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.164635543453951</v>
+        <v>0.1676245962844235</v>
       </c>
       <c r="T65">
-        <v>1.548825503771039</v>
+        <v>1.587782882358268</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.309679757925848</v>
+        <v>2.273591011708256</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09818421466239247</v>
+        <v>0.09820515824682302</v>
       </c>
       <c r="C66">
-        <v>12.56205181215099</v>
+        <v>12.25514409073067</v>
       </c>
       <c r="D66">
-        <v>30.79645181215099</v>
+        <v>30.78414409073067</v>
       </c>
       <c r="E66">
-        <v>-0.6455999999999982</v>
+        <v>-0.3509999999999991</v>
       </c>
       <c r="F66">
-        <v>18.8544</v>
+        <v>19.149</v>
       </c>
       <c r="G66">
         <v>0.62</v>
@@ -6687,28 +6687,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M66">
-        <v>1.42916352</v>
+        <v>1.4514942</v>
       </c>
       <c r="N66">
-        <v>1.820169813333333</v>
+        <v>1.797839133333333</v>
       </c>
       <c r="O66">
-        <v>0.4004373589333333</v>
+        <v>0.3955246093333333</v>
       </c>
       <c r="P66">
-        <v>1.4197324544</v>
+        <v>1.402314524</v>
       </c>
       <c r="Q66">
-        <v>4.3037324544</v>
+        <v>4.286314524</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1676245962844235</v>
+        <v>0.17078445213378</v>
       </c>
       <c r="T66">
-        <v>1.587782882358268</v>
+        <v>1.628966396864768</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.273591011708256</v>
+        <v>2.238612688451206</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09820515824682302</v>
+        <v>0.09822610183125358</v>
       </c>
       <c r="C67">
-        <v>12.25514409073067</v>
+        <v>11.94824620287775</v>
       </c>
       <c r="D67">
-        <v>30.78414409073067</v>
+        <v>30.77184620287775</v>
       </c>
       <c r="E67">
-        <v>-0.3509999999999991</v>
+        <v>-0.05640000000000001</v>
       </c>
       <c r="F67">
-        <v>19.149</v>
+        <v>19.4436</v>
       </c>
       <c r="G67">
         <v>0.62</v>
@@ -6769,28 +6769,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M67">
-        <v>1.4514942</v>
+        <v>1.47382488</v>
       </c>
       <c r="N67">
-        <v>1.797839133333333</v>
+        <v>1.775508453333333</v>
       </c>
       <c r="O67">
-        <v>0.3955246093333333</v>
+        <v>0.3906118597333333</v>
       </c>
       <c r="P67">
-        <v>1.402314524</v>
+        <v>1.3848965936</v>
       </c>
       <c r="Q67">
-        <v>4.286314524</v>
+        <v>4.2688965936</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.17078445213378</v>
+        <v>0.1741301818566282</v>
       </c>
       <c r="T67">
-        <v>1.628966396864768</v>
+        <v>1.67257247104812</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.238612688451206</v>
+        <v>2.204694314383764</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09822610183125358</v>
+        <v>0.09824704541568413</v>
       </c>
       <c r="C68">
-        <v>11.94824620287775</v>
+        <v>11.64135813681176</v>
       </c>
       <c r="D68">
-        <v>30.77184620287775</v>
+        <v>30.75955813681176</v>
       </c>
       <c r="E68">
-        <v>-0.05640000000000001</v>
+        <v>0.2382000000000026</v>
       </c>
       <c r="F68">
-        <v>19.4436</v>
+        <v>19.7382</v>
       </c>
       <c r="G68">
         <v>0.62</v>
@@ -6851,28 +6851,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M68">
-        <v>1.47382488</v>
+        <v>1.49615556</v>
       </c>
       <c r="N68">
-        <v>1.775508453333333</v>
+        <v>1.753177773333333</v>
       </c>
       <c r="O68">
-        <v>0.3906118597333333</v>
+        <v>0.3856991101333333</v>
       </c>
       <c r="P68">
-        <v>1.3848965936</v>
+        <v>1.3674786632</v>
       </c>
       <c r="Q68">
-        <v>4.2688965936</v>
+        <v>4.2514786632</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1741301818566282</v>
+        <v>0.1776786830778307</v>
       </c>
       <c r="T68">
-        <v>1.67257247104812</v>
+        <v>1.718821337606221</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.204694314383764</v>
+        <v>2.171788429094454</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09824704541568413</v>
+        <v>0.09826798900011469</v>
       </c>
       <c r="C69">
-        <v>11.64135813681176</v>
+        <v>11.33447988077104</v>
       </c>
       <c r="D69">
-        <v>30.75955813681176</v>
+        <v>30.74727988077104</v>
       </c>
       <c r="E69">
-        <v>0.2382000000000026</v>
+        <v>0.5328000000000017</v>
       </c>
       <c r="F69">
-        <v>19.7382</v>
+        <v>20.0328</v>
       </c>
       <c r="G69">
         <v>0.62</v>
@@ -6933,28 +6933,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M69">
-        <v>1.49615556</v>
+        <v>1.51848624</v>
       </c>
       <c r="N69">
-        <v>1.753177773333333</v>
+        <v>1.730847093333333</v>
       </c>
       <c r="O69">
-        <v>0.3856991101333333</v>
+        <v>0.3807863605333333</v>
       </c>
       <c r="P69">
-        <v>1.3674786632</v>
+        <v>1.3500607328</v>
       </c>
       <c r="Q69">
-        <v>4.2514786632</v>
+        <v>4.2340607328</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1776786830778307</v>
+        <v>0.1814489656253584</v>
       </c>
       <c r="T69">
-        <v>1.718821337606221</v>
+        <v>1.767960758324203</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.171788429094454</v>
+        <v>2.139850363960712</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09826798900011469</v>
+        <v>0.09828893258454525</v>
       </c>
       <c r="C70">
-        <v>11.33447988077104</v>
+        <v>11.02761142301271</v>
       </c>
       <c r="D70">
-        <v>30.74727988077104</v>
+        <v>30.73501142301271</v>
       </c>
       <c r="E70">
-        <v>0.5328000000000017</v>
+        <v>0.8274000000000008</v>
       </c>
       <c r="F70">
-        <v>20.0328</v>
+        <v>20.3274</v>
       </c>
       <c r="G70">
         <v>0.62</v>
@@ -7015,28 +7015,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M70">
-        <v>1.51848624</v>
+        <v>1.54081692</v>
       </c>
       <c r="N70">
-        <v>1.730847093333333</v>
+        <v>1.708516413333333</v>
       </c>
       <c r="O70">
-        <v>0.3807863605333333</v>
+        <v>0.3758736109333333</v>
       </c>
       <c r="P70">
-        <v>1.3500607328</v>
+        <v>1.3326428024</v>
       </c>
       <c r="Q70">
-        <v>4.2340607328</v>
+        <v>4.2166428024</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1814489656253584</v>
+        <v>0.1854624922082105</v>
       </c>
       <c r="T70">
-        <v>1.767960758324203</v>
+        <v>1.820270464249797</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.139850363960712</v>
+        <v>2.108838039845339</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09828893258454525</v>
+        <v>0.0983098761689758</v>
       </c>
       <c r="C71">
-        <v>11.02761142301271</v>
+        <v>10.72075275181265</v>
       </c>
       <c r="D71">
-        <v>30.73501142301271</v>
+        <v>30.72275275181265</v>
       </c>
       <c r="E71">
-        <v>0.8274000000000008</v>
+        <v>1.122000000000003</v>
       </c>
       <c r="F71">
-        <v>20.3274</v>
+        <v>20.622</v>
       </c>
       <c r="G71">
         <v>0.62</v>
@@ -7097,28 +7097,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M71">
-        <v>1.54081692</v>
+        <v>1.5631476</v>
       </c>
       <c r="N71">
-        <v>1.708516413333333</v>
+        <v>1.686185733333333</v>
       </c>
       <c r="O71">
-        <v>0.3758736109333333</v>
+        <v>0.3709608613333333</v>
       </c>
       <c r="P71">
-        <v>1.3326428024</v>
+        <v>1.315224872</v>
       </c>
       <c r="Q71">
-        <v>4.2166428024</v>
+        <v>4.199224872</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1854624922082105</v>
+        <v>0.1897435872299194</v>
       </c>
       <c r="T71">
-        <v>1.820270464249797</v>
+        <v>1.876067483903764</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.108838039845339</v>
+        <v>2.078711782133263</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.0983098761689758</v>
+        <v>0.09833081975340638</v>
       </c>
       <c r="C72">
-        <v>10.72075275181265</v>
+        <v>10.41390385546536</v>
       </c>
       <c r="D72">
-        <v>30.72275275181265</v>
+        <v>30.71050385546537</v>
       </c>
       <c r="E72">
-        <v>1.122000000000003</v>
+        <v>1.416600000000003</v>
       </c>
       <c r="F72">
-        <v>20.622</v>
+        <v>20.9166</v>
       </c>
       <c r="G72">
         <v>0.62</v>
@@ -7179,28 +7179,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M72">
-        <v>1.5631476</v>
+        <v>1.58547828</v>
       </c>
       <c r="N72">
-        <v>1.686185733333333</v>
+        <v>1.663855053333333</v>
       </c>
       <c r="O72">
-        <v>0.3709608613333333</v>
+        <v>0.3660481117333333</v>
       </c>
       <c r="P72">
-        <v>1.315224872</v>
+        <v>1.2978069416</v>
       </c>
       <c r="Q72">
-        <v>4.199224872</v>
+        <v>4.1818069416</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1897435872299194</v>
+        <v>0.1943199301841599</v>
       </c>
       <c r="T72">
-        <v>1.876067483903764</v>
+        <v>1.935712573878695</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.078711782133263</v>
+        <v>2.049434151398992</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09833081975340638</v>
+        <v>0.09835176333783693</v>
       </c>
       <c r="C73">
-        <v>10.41390385546537</v>
+        <v>10.1070647222841</v>
       </c>
       <c r="D73">
-        <v>30.71050385546537</v>
+        <v>30.6982647222841</v>
       </c>
       <c r="E73">
-        <v>1.416599999999999</v>
+        <v>1.711199999999998</v>
       </c>
       <c r="F73">
-        <v>20.9166</v>
+        <v>21.2112</v>
       </c>
       <c r="G73">
         <v>0.62</v>
@@ -7261,28 +7261,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M73">
-        <v>1.58547828</v>
+        <v>1.60780896</v>
       </c>
       <c r="N73">
-        <v>1.663855053333333</v>
+        <v>1.641524373333333</v>
       </c>
       <c r="O73">
-        <v>0.3660481117333333</v>
+        <v>0.3611353621333334</v>
       </c>
       <c r="P73">
-        <v>1.2978069416</v>
+        <v>1.2803890112</v>
       </c>
       <c r="Q73">
-        <v>4.181806941600001</v>
+        <v>4.164389011200001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1943199301841599</v>
+        <v>0.199223154777989</v>
       </c>
       <c r="T73">
-        <v>1.935712573878694</v>
+        <v>1.999618027423262</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.049434151398992</v>
+        <v>2.020969788185117</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09835176333783693</v>
+        <v>0.1064581869222675</v>
       </c>
       <c r="C74">
-        <v>10.1070647222841</v>
+        <v>5.709916496358431</v>
       </c>
       <c r="D74">
-        <v>30.6982647222841</v>
+        <v>26.59571649635843</v>
       </c>
       <c r="E74">
-        <v>1.711199999999998</v>
+        <v>2.005800000000001</v>
       </c>
       <c r="F74">
-        <v>21.2112</v>
+        <v>21.5058</v>
       </c>
       <c r="G74">
         <v>0.62</v>
@@ -7343,45 +7343,45 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M74">
-        <v>1.60780896</v>
+        <v>1.935522</v>
       </c>
       <c r="N74">
-        <v>1.641524373333333</v>
+        <v>1.313811333333333</v>
       </c>
       <c r="O74">
-        <v>0.3611353621333334</v>
+        <v>0.2890384933333334</v>
       </c>
       <c r="P74">
-        <v>1.2803890112</v>
+        <v>1.02477284</v>
       </c>
       <c r="Q74">
-        <v>4.164389011200001</v>
+        <v>3.90877284</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.199223154777989</v>
+        <v>0.2044895811935833</v>
       </c>
       <c r="T74">
-        <v>1.999618027423262</v>
+        <v>2.068257218267427</v>
       </c>
       <c r="U74">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V74">
         <v>0.22</v>
       </c>
       <c r="W74">
-        <v>0.05912400000000001</v>
+        <v>0.0702</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y74">
-        <v>2.020969788185117</v>
+        <v>1.678789150075966</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1064581869222675</v>
+        <v>0.106589890506698</v>
       </c>
       <c r="C75">
-        <v>5.709916496358431</v>
+        <v>5.357695876155422</v>
       </c>
       <c r="D75">
-        <v>26.59571649635843</v>
+        <v>26.53809587615542</v>
       </c>
       <c r="E75">
-        <v>2.005800000000001</v>
+        <v>2.3004</v>
       </c>
       <c r="F75">
-        <v>21.5058</v>
+        <v>21.8004</v>
       </c>
       <c r="G75">
         <v>0.62</v>
@@ -7425,28 +7425,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M75">
-        <v>1.935522</v>
+        <v>1.962036</v>
       </c>
       <c r="N75">
-        <v>1.313811333333333</v>
+        <v>1.287297333333334</v>
       </c>
       <c r="O75">
-        <v>0.2890384933333334</v>
+        <v>0.2832054133333334</v>
       </c>
       <c r="P75">
-        <v>1.02477284</v>
+        <v>1.00409192</v>
       </c>
       <c r="Q75">
-        <v>3.90877284</v>
+        <v>3.88809192</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2044895811935833</v>
+        <v>0.210161117333454</v>
       </c>
       <c r="T75">
-        <v>2.068257218267427</v>
+        <v>2.142176346868836</v>
       </c>
       <c r="U75">
         <v>0.09</v>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.678789150075966</v>
+        <v>1.656102810210074</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.106589890506698</v>
+        <v>0.1067215940911286</v>
       </c>
       <c r="C76">
-        <v>5.357695876155422</v>
+        <v>5.00572439067486</v>
       </c>
       <c r="D76">
-        <v>26.53809587615542</v>
+        <v>26.48072439067486</v>
       </c>
       <c r="E76">
-        <v>2.3004</v>
+        <v>2.594999999999999</v>
       </c>
       <c r="F76">
-        <v>21.8004</v>
+        <v>22.095</v>
       </c>
       <c r="G76">
         <v>0.62</v>
@@ -7507,28 +7507,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M76">
-        <v>1.962036</v>
+        <v>1.98855</v>
       </c>
       <c r="N76">
-        <v>1.287297333333334</v>
+        <v>1.260783333333334</v>
       </c>
       <c r="O76">
-        <v>0.2832054133333334</v>
+        <v>0.2773723333333334</v>
       </c>
       <c r="P76">
-        <v>1.00409192</v>
+        <v>0.9834110000000003</v>
       </c>
       <c r="Q76">
-        <v>3.88809192</v>
+        <v>3.867411000000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.210161117333454</v>
+        <v>0.2162863763645144</v>
       </c>
       <c r="T76">
-        <v>2.142176346868836</v>
+        <v>2.222009005758359</v>
       </c>
       <c r="U76">
         <v>0.09</v>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.656102810210074</v>
+        <v>1.634021439407273</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1067215940911286</v>
+        <v>0.1068532976755592</v>
       </c>
       <c r="C77">
-        <v>5.00572439067486</v>
+        <v>4.654000427623714</v>
       </c>
       <c r="D77">
-        <v>26.48072439067486</v>
+        <v>26.42360042762371</v>
       </c>
       <c r="E77">
-        <v>2.594999999999999</v>
+        <v>2.889600000000002</v>
       </c>
       <c r="F77">
-        <v>22.095</v>
+        <v>22.3896</v>
       </c>
       <c r="G77">
         <v>0.62</v>
@@ -7589,28 +7589,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M77">
-        <v>1.98855</v>
+        <v>2.015064</v>
       </c>
       <c r="N77">
-        <v>1.260783333333334</v>
+        <v>1.234269333333333</v>
       </c>
       <c r="O77">
-        <v>0.2773723333333334</v>
+        <v>0.2715392533333333</v>
       </c>
       <c r="P77">
-        <v>0.9834110000000003</v>
+        <v>0.9627300799999999</v>
       </c>
       <c r="Q77">
-        <v>3.867411000000001</v>
+        <v>3.84673008</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2162863763645144</v>
+        <v>0.2229220736481632</v>
       </c>
       <c r="T77">
-        <v>2.222009005758359</v>
+        <v>2.308494386222007</v>
       </c>
       <c r="U77">
         <v>0.09</v>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.634021439407273</v>
+        <v>1.612521157309809</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1068532976755592</v>
+        <v>0.1069850012599897</v>
       </c>
       <c r="C78">
-        <v>4.654000427623714</v>
+        <v>4.302522388591054</v>
       </c>
       <c r="D78">
-        <v>26.42360042762371</v>
+        <v>26.36672238859105</v>
       </c>
       <c r="E78">
-        <v>2.889600000000002</v>
+        <v>3.184200000000001</v>
       </c>
       <c r="F78">
-        <v>22.3896</v>
+        <v>22.6842</v>
       </c>
       <c r="G78">
         <v>0.62</v>
@@ -7671,28 +7671,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M78">
-        <v>2.015064</v>
+        <v>2.041578</v>
       </c>
       <c r="N78">
-        <v>1.234269333333333</v>
+        <v>1.207755333333334</v>
       </c>
       <c r="O78">
-        <v>0.2715392533333333</v>
+        <v>0.2657061733333334</v>
       </c>
       <c r="P78">
-        <v>0.9627300799999999</v>
+        <v>0.9420491600000002</v>
       </c>
       <c r="Q78">
-        <v>3.84673008</v>
+        <v>3.826049160000001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2229220736481632</v>
+        <v>0.2301347880869118</v>
       </c>
       <c r="T78">
-        <v>2.308494386222007</v>
+        <v>2.40250023455206</v>
       </c>
       <c r="U78">
         <v>0.09</v>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.612521157309809</v>
+        <v>1.591579324097994</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1069850012599897</v>
+        <v>0.1071167048444203</v>
       </c>
       <c r="C79">
-        <v>4.302522388591054</v>
+        <v>3.951288688899034</v>
       </c>
       <c r="D79">
-        <v>26.36672238859105</v>
+        <v>26.31008868889904</v>
       </c>
       <c r="E79">
-        <v>3.184200000000001</v>
+        <v>3.478800000000003</v>
       </c>
       <c r="F79">
-        <v>22.6842</v>
+        <v>22.9788</v>
       </c>
       <c r="G79">
         <v>0.62</v>
@@ -7753,28 +7753,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M79">
-        <v>2.041578</v>
+        <v>2.068092</v>
       </c>
       <c r="N79">
-        <v>1.207755333333334</v>
+        <v>1.181241333333333</v>
       </c>
       <c r="O79">
-        <v>0.2657061733333334</v>
+        <v>0.2598730933333334</v>
       </c>
       <c r="P79">
-        <v>0.9420491600000002</v>
+        <v>0.9213682400000001</v>
       </c>
       <c r="Q79">
-        <v>3.826049160000001</v>
+        <v>3.80536824</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2301347880869118</v>
+        <v>0.238003203838274</v>
       </c>
       <c r="T79">
-        <v>2.40250023455206</v>
+        <v>2.505052069093936</v>
       </c>
       <c r="U79">
         <v>0.09</v>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.591579324097994</v>
+        <v>1.571174460968532</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1071167048444203</v>
+        <v>0.1072484084288508</v>
       </c>
       <c r="C80">
-        <v>3.951288688899034</v>
+        <v>3.600297757455692</v>
       </c>
       <c r="D80">
-        <v>26.31008868889904</v>
+        <v>26.25369775745569</v>
       </c>
       <c r="E80">
-        <v>3.478800000000003</v>
+        <v>3.773400000000002</v>
       </c>
       <c r="F80">
-        <v>22.9788</v>
+        <v>23.2734</v>
       </c>
       <c r="G80">
         <v>0.62</v>
@@ -7835,28 +7835,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M80">
-        <v>2.068092</v>
+        <v>2.094606</v>
       </c>
       <c r="N80">
-        <v>1.181241333333333</v>
+        <v>1.154727333333333</v>
       </c>
       <c r="O80">
-        <v>0.2598730933333334</v>
+        <v>0.2540400133333333</v>
       </c>
       <c r="P80">
-        <v>0.9213682400000001</v>
+        <v>0.9006873199999998</v>
       </c>
       <c r="Q80">
-        <v>3.80536824</v>
+        <v>3.78468732</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.238003203838274</v>
+        <v>0.2466209925183374</v>
       </c>
       <c r="T80">
-        <v>2.505052069093936</v>
+        <v>2.617370745020753</v>
       </c>
       <c r="U80">
         <v>0.09</v>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.571174460968532</v>
+        <v>1.551286176652475</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1072484084288508</v>
+        <v>0.1073801120132814</v>
       </c>
       <c r="C81">
-        <v>3.600297757455692</v>
+        <v>3.249548036609649</v>
       </c>
       <c r="D81">
-        <v>26.25369775745569</v>
+        <v>26.19754803660965</v>
       </c>
       <c r="E81">
-        <v>3.773400000000002</v>
+        <v>4.068000000000001</v>
       </c>
       <c r="F81">
-        <v>23.2734</v>
+        <v>23.568</v>
       </c>
       <c r="G81">
         <v>0.62</v>
@@ -7917,28 +7917,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M81">
-        <v>2.094606</v>
+        <v>2.12112</v>
       </c>
       <c r="N81">
-        <v>1.154727333333333</v>
+        <v>1.128213333333334</v>
       </c>
       <c r="O81">
-        <v>0.2540400133333333</v>
+        <v>0.2482069333333334</v>
       </c>
       <c r="P81">
-        <v>0.9006873199999998</v>
+        <v>0.8800064000000001</v>
       </c>
       <c r="Q81">
-        <v>3.78468732</v>
+        <v>3.7640064</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2466209925183374</v>
+        <v>0.256100560066407</v>
       </c>
       <c r="T81">
-        <v>2.617370745020753</v>
+        <v>2.740921288540251</v>
       </c>
       <c r="U81">
         <v>0.09</v>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.551286176652475</v>
+        <v>1.531895099444319</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1073801120132814</v>
+        <v>0.1075118155977119</v>
       </c>
       <c r="C82">
-        <v>3.249548036609649</v>
+        <v>2.899037982006739</v>
       </c>
       <c r="D82">
-        <v>26.19754803660965</v>
+        <v>26.14163798200674</v>
       </c>
       <c r="E82">
-        <v>4.068000000000001</v>
+        <v>4.362600000000004</v>
       </c>
       <c r="F82">
-        <v>23.568</v>
+        <v>23.8626</v>
       </c>
       <c r="G82">
         <v>0.62</v>
@@ -7999,28 +7999,28 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M82">
-        <v>2.12112</v>
+        <v>2.147634</v>
       </c>
       <c r="N82">
-        <v>1.128213333333334</v>
+        <v>1.101699333333333</v>
       </c>
       <c r="O82">
-        <v>0.2482069333333334</v>
+        <v>0.2423738533333333</v>
       </c>
       <c r="P82">
-        <v>0.8800064000000001</v>
+        <v>0.8593254799999996</v>
       </c>
       <c r="Q82">
-        <v>3.7640064</v>
+        <v>3.74332548</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.256100560066407</v>
+        <v>0.266577976830063</v>
       </c>
       <c r="T82">
-        <v>2.740921288540251</v>
+        <v>2.877477152430223</v>
       </c>
       <c r="U82">
         <v>0.09</v>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.531895099444319</v>
+        <v>1.512982814265993</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1075118155977119</v>
+        <v>0.1469613482554975</v>
       </c>
       <c r="C83">
-        <v>2.899037982006739</v>
+        <v>-7.58992398610927</v>
       </c>
       <c r="D83">
-        <v>26.14163798200674</v>
+        <v>15.94727601389073</v>
       </c>
       <c r="E83">
-        <v>4.362600000000004</v>
+        <v>4.657200000000003</v>
       </c>
       <c r="F83">
-        <v>23.8626</v>
+        <v>24.1572</v>
       </c>
       <c r="G83">
         <v>0.62</v>
@@ -8081,45 +8081,45 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M83">
-        <v>2.147634</v>
+        <v>3.546276960000001</v>
       </c>
       <c r="N83">
-        <v>1.101699333333333</v>
+        <v>-0.2969436266666672</v>
       </c>
       <c r="O83">
-        <v>0.2423738533333333</v>
+        <v>-0.06532759786666678</v>
       </c>
       <c r="P83">
-        <v>0.8593254799999996</v>
+        <v>-0.2316160288000004</v>
       </c>
       <c r="Q83">
-        <v>3.74332548</v>
+        <v>2.6523839712</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.266577976830063</v>
+        <v>0.2825031479483084</v>
       </c>
       <c r="T83">
-        <v>2.877477152430223</v>
+        <v>3.085035518075383</v>
       </c>
       <c r="U83">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.22</v>
+        <v>0.201578540366834</v>
       </c>
       <c r="W83">
-        <v>0.0702</v>
+        <v>0.1172082702741488</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y83">
-        <v>1.512982814265993</v>
+        <v>0.916266092576518</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1469613482554975</v>
+        <v>0.1479713482554975</v>
       </c>
       <c r="C84">
-        <v>-7.58992398610927</v>
+        <v>-8.042168463245382</v>
       </c>
       <c r="D84">
-        <v>15.94727601389073</v>
+        <v>15.78963153675462</v>
       </c>
       <c r="E84">
-        <v>4.657200000000003</v>
+        <v>4.951800000000002</v>
       </c>
       <c r="F84">
-        <v>24.1572</v>
+        <v>24.4518</v>
       </c>
       <c r="G84">
         <v>0.62</v>
@@ -8163,37 +8163,37 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M84">
-        <v>3.546276960000001</v>
+        <v>3.589524240000001</v>
       </c>
       <c r="N84">
-        <v>-0.2969436266666672</v>
+        <v>-0.3401909066666673</v>
       </c>
       <c r="O84">
-        <v>-0.06532759786666678</v>
+        <v>-0.07484199946666681</v>
       </c>
       <c r="P84">
-        <v>-0.2316160288000004</v>
+        <v>-0.2653489072000005</v>
       </c>
       <c r="Q84">
-        <v>2.6523839712</v>
+        <v>2.6186510928</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2825031479483084</v>
+        <v>0.2964268625335031</v>
       </c>
       <c r="T84">
-        <v>3.085035518075383</v>
+        <v>3.26650819560923</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.201578540366834</v>
+        <v>0.1991498832539805</v>
       </c>
       <c r="W84">
-        <v>0.1172082702741488</v>
+        <v>0.1175647971383157</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.916266092576518</v>
+        <v>0.9052267420635479</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1479713482554975</v>
+        <v>0.1489813482554975</v>
       </c>
       <c r="C85">
-        <v>-8.042168463245382</v>
+        <v>-8.491326705812959</v>
       </c>
       <c r="D85">
-        <v>15.78963153675462</v>
+        <v>15.63507329418705</v>
       </c>
       <c r="E85">
-        <v>4.951800000000002</v>
+        <v>5.246400000000005</v>
       </c>
       <c r="F85">
-        <v>24.4518</v>
+        <v>24.7464</v>
       </c>
       <c r="G85">
         <v>0.62</v>
@@ -8245,37 +8245,37 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M85">
-        <v>3.589524240000001</v>
+        <v>3.632771520000001</v>
       </c>
       <c r="N85">
-        <v>-0.3401909066666673</v>
+        <v>-0.3834381866666678</v>
       </c>
       <c r="O85">
-        <v>-0.07484199946666681</v>
+        <v>-0.08435640106666693</v>
       </c>
       <c r="P85">
-        <v>-0.2653489072000005</v>
+        <v>-0.2990817856000009</v>
       </c>
       <c r="Q85">
-        <v>2.6186510928</v>
+        <v>2.5849182144</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2964268625335031</v>
+        <v>0.3120910414418471</v>
       </c>
       <c r="T85">
-        <v>3.26650819560923</v>
+        <v>3.470664957834807</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.1991498832539805</v>
+        <v>0.1967790513104807</v>
       </c>
       <c r="W85">
-        <v>0.1175647971383157</v>
+        <v>0.1179128352676214</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.9052267420635479</v>
+        <v>0.8944502332294579</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1489813482554975</v>
+        <v>0.1499913482554975</v>
       </c>
       <c r="C86">
-        <v>-8.491326705812948</v>
+        <v>-8.937488464937186</v>
       </c>
       <c r="D86">
-        <v>15.63507329418705</v>
+        <v>15.48351153506281</v>
       </c>
       <c r="E86">
-        <v>5.246400000000001</v>
+        <v>5.541</v>
       </c>
       <c r="F86">
-        <v>24.7464</v>
+        <v>25.041</v>
       </c>
       <c r="G86">
         <v>0.62</v>
@@ -8327,37 +8327,37 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M86">
-        <v>3.63277152</v>
+        <v>3.6760188</v>
       </c>
       <c r="N86">
-        <v>-0.383438186666667</v>
+        <v>-0.4266854666666671</v>
       </c>
       <c r="O86">
-        <v>-0.08435640106666673</v>
+        <v>-0.09387080266666675</v>
       </c>
       <c r="P86">
-        <v>-0.2990817856000002</v>
+        <v>-0.3328146640000003</v>
       </c>
       <c r="Q86">
-        <v>2.5849182144</v>
+        <v>2.551185336</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3120910414418469</v>
+        <v>0.3298437775379701</v>
       </c>
       <c r="T86">
-        <v>3.470664957834805</v>
+        <v>3.702042621690459</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.1967790513104808</v>
+        <v>0.1944640036480045</v>
       </c>
       <c r="W86">
-        <v>0.1179128352676214</v>
+        <v>0.1182526842644729</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8944502332294582</v>
+        <v>0.8839272893091116</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1499913482554975</v>
+        <v>0.1510013482554975</v>
       </c>
       <c r="C87">
-        <v>-8.937488464937186</v>
+        <v>-9.380740045071244</v>
       </c>
       <c r="D87">
-        <v>15.48351153506281</v>
+        <v>15.33485995492876</v>
       </c>
       <c r="E87">
-        <v>5.541</v>
+        <v>5.835599999999999</v>
       </c>
       <c r="F87">
-        <v>25.041</v>
+        <v>25.3356</v>
       </c>
       <c r="G87">
         <v>0.62</v>
@@ -8409,37 +8409,37 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M87">
-        <v>3.6760188</v>
+        <v>3.71926608</v>
       </c>
       <c r="N87">
-        <v>-0.4266854666666671</v>
+        <v>-0.4699327466666667</v>
       </c>
       <c r="O87">
-        <v>-0.09387080266666675</v>
+        <v>-0.1033852042666667</v>
       </c>
       <c r="P87">
-        <v>-0.3328146640000003</v>
+        <v>-0.3665475424</v>
       </c>
       <c r="Q87">
-        <v>2.551185336</v>
+        <v>2.5174524576</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3298437775379701</v>
+        <v>0.3501326187906822</v>
       </c>
       <c r="T87">
-        <v>3.702042621690459</v>
+        <v>3.966474237525492</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.1944640036480045</v>
+        <v>0.1922027943032603</v>
       </c>
       <c r="W87">
-        <v>0.1182526842644729</v>
+        <v>0.1185846297962814</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8839272893091116</v>
+        <v>0.8736490650148196</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1510013482554975</v>
+        <v>0.1520113482554975</v>
       </c>
       <c r="C88">
-        <v>-9.380740045071244</v>
+        <v>-9.821164467874171</v>
       </c>
       <c r="D88">
-        <v>15.33485995492876</v>
+        <v>15.18903553212583</v>
       </c>
       <c r="E88">
-        <v>5.835599999999999</v>
+        <v>6.130200000000002</v>
       </c>
       <c r="F88">
-        <v>25.3356</v>
+        <v>25.6302</v>
       </c>
       <c r="G88">
         <v>0.62</v>
@@ -8491,37 +8491,37 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M88">
-        <v>3.71926608</v>
+        <v>3.762513360000001</v>
       </c>
       <c r="N88">
-        <v>-0.4699327466666667</v>
+        <v>-0.5131800266666673</v>
       </c>
       <c r="O88">
-        <v>-0.1033852042666667</v>
+        <v>-0.1128996058666668</v>
       </c>
       <c r="P88">
-        <v>-0.3665475424</v>
+        <v>-0.4002804208000005</v>
       </c>
       <c r="Q88">
-        <v>2.5174524576</v>
+        <v>2.4837195792</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3501326187906822</v>
+        <v>0.3735428202361193</v>
       </c>
       <c r="T88">
-        <v>3.966474237525492</v>
+        <v>4.271587640412068</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.1922027943032603</v>
+        <v>0.1899935667825332</v>
       </c>
       <c r="W88">
-        <v>0.1185846297962814</v>
+        <v>0.1189089443963241</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8736490650148196</v>
+        <v>0.8636071217387871</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1520113482554975</v>
+        <v>0.1530213482554975</v>
       </c>
       <c r="C89">
-        <v>-9.821164467874171</v>
+        <v>-10.25884162682662</v>
       </c>
       <c r="D89">
-        <v>15.18903553212583</v>
+        <v>15.04595837317339</v>
       </c>
       <c r="E89">
-        <v>6.130200000000002</v>
+        <v>6.424800000000001</v>
       </c>
       <c r="F89">
-        <v>25.6302</v>
+        <v>25.9248</v>
       </c>
       <c r="G89">
         <v>0.62</v>
@@ -8573,37 +8573,37 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M89">
-        <v>3.762513360000001</v>
+        <v>3.80576064</v>
       </c>
       <c r="N89">
-        <v>-0.5131800266666673</v>
+        <v>-0.556427306666667</v>
       </c>
       <c r="O89">
-        <v>-0.1128996058666668</v>
+        <v>-0.1224140074666667</v>
       </c>
       <c r="P89">
-        <v>-0.4002804208000005</v>
+        <v>-0.4340132992000002</v>
       </c>
       <c r="Q89">
-        <v>2.4837195792</v>
+        <v>2.4499867008</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3735428202361193</v>
+        <v>0.4008547219224626</v>
       </c>
       <c r="T89">
-        <v>4.271587640412068</v>
+        <v>4.627553277113075</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.1899935667825332</v>
+        <v>0.1878345489781862</v>
       </c>
       <c r="W89">
-        <v>0.1189089443963241</v>
+        <v>0.1192258882100023</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8636071217387871</v>
+        <v>0.8537934044463009</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1530213482554975</v>
+        <v>0.1540313482554975</v>
       </c>
       <c r="C90">
-        <v>-10.25884162682662</v>
+        <v>-10.69384843318951</v>
       </c>
       <c r="D90">
-        <v>15.04595837317339</v>
+        <v>14.90555156681049</v>
       </c>
       <c r="E90">
-        <v>6.424800000000001</v>
+        <v>6.7194</v>
       </c>
       <c r="F90">
-        <v>25.9248</v>
+        <v>26.2194</v>
       </c>
       <c r="G90">
         <v>0.62</v>
@@ -8655,37 +8655,37 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M90">
-        <v>3.80576064</v>
+        <v>3.84900792</v>
       </c>
       <c r="N90">
-        <v>-0.556427306666667</v>
+        <v>-0.5996745866666671</v>
       </c>
       <c r="O90">
-        <v>-0.1224140074666667</v>
+        <v>-0.1319284090666668</v>
       </c>
       <c r="P90">
-        <v>-0.4340132992000002</v>
+        <v>-0.4677461776000003</v>
       </c>
       <c r="Q90">
-        <v>2.4499867008</v>
+        <v>2.4162538224</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4008547219224626</v>
+        <v>0.4331324239154137</v>
       </c>
       <c r="T90">
-        <v>4.627553277113075</v>
+        <v>5.048239938668808</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.1878345489781862</v>
+        <v>0.1857240484278695</v>
       </c>
       <c r="W90">
-        <v>0.1192258882100023</v>
+        <v>0.1195357096907888</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8537934044463009</v>
+        <v>0.8442002201266796</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1540313482554975</v>
+        <v>0.1550413482554975</v>
       </c>
       <c r="C91">
-        <v>-10.69384843318951</v>
+        <v>-11.12625895386588</v>
       </c>
       <c r="D91">
-        <v>14.90555156681049</v>
+        <v>14.76774104613412</v>
       </c>
       <c r="E91">
-        <v>6.7194</v>
+        <v>7.014000000000003</v>
       </c>
       <c r="F91">
-        <v>26.2194</v>
+        <v>26.514</v>
       </c>
       <c r="G91">
         <v>0.62</v>
@@ -8737,37 +8737,37 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M91">
-        <v>3.84900792</v>
+        <v>3.892255200000001</v>
       </c>
       <c r="N91">
-        <v>-0.5996745866666671</v>
+        <v>-0.6429218666666672</v>
       </c>
       <c r="O91">
-        <v>-0.1319284090666668</v>
+        <v>-0.1414428106666668</v>
       </c>
       <c r="P91">
-        <v>-0.4677461776000003</v>
+        <v>-0.5014790560000004</v>
       </c>
       <c r="Q91">
-        <v>2.4162538224</v>
+        <v>2.382520944</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4331324239154137</v>
+        <v>0.4718656663069552</v>
       </c>
       <c r="T91">
-        <v>5.048239938668808</v>
+        <v>5.55306393253569</v>
       </c>
       <c r="U91">
         <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.1857240484278695</v>
+        <v>0.1836604478897821</v>
       </c>
       <c r="W91">
-        <v>0.1195357096907888</v>
+        <v>0.11983864624978</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8442002201266796</v>
+        <v>0.8348202176808275</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1550413482554975</v>
+        <v>0.1560513482554975</v>
       </c>
       <c r="C92">
-        <v>-11.12625895386588</v>
+        <v>-11.556144541685</v>
       </c>
       <c r="D92">
-        <v>14.76774104613412</v>
+        <v>14.632455458315</v>
       </c>
       <c r="E92">
-        <v>7.014000000000003</v>
+        <v>7.308600000000002</v>
       </c>
       <c r="F92">
-        <v>26.514</v>
+        <v>26.8086</v>
       </c>
       <c r="G92">
         <v>0.62</v>
@@ -8819,37 +8819,37 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M92">
-        <v>3.892255200000001</v>
+        <v>3.935502480000001</v>
       </c>
       <c r="N92">
-        <v>-0.6429218666666672</v>
+        <v>-0.6861691466666673</v>
       </c>
       <c r="O92">
-        <v>-0.1414428106666668</v>
+        <v>-0.1509572122666668</v>
       </c>
       <c r="P92">
-        <v>-0.5014790560000004</v>
+        <v>-0.5352119344000005</v>
       </c>
       <c r="Q92">
-        <v>2.382520944</v>
+        <v>2.3487880656</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4718656663069552</v>
+        <v>0.5192062958966169</v>
       </c>
       <c r="T92">
-        <v>5.55306393253569</v>
+        <v>6.170071036150768</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.1836604478897821</v>
+        <v>0.1816422012096746</v>
       </c>
       <c r="W92">
-        <v>0.11983864624978</v>
+        <v>0.1201349248624198</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8348202176808275</v>
+        <v>0.8256463691348843</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1560513482554975</v>
+        <v>0.1570613482554975</v>
       </c>
       <c r="C93">
-        <v>-11.556144541685</v>
+        <v>-11.98357395859051</v>
       </c>
       <c r="D93">
-        <v>14.632455458315</v>
+        <v>14.4996260414095</v>
       </c>
       <c r="E93">
-        <v>7.308600000000002</v>
+        <v>7.603200000000001</v>
       </c>
       <c r="F93">
-        <v>26.8086</v>
+        <v>27.1032</v>
       </c>
       <c r="G93">
         <v>0.62</v>
@@ -8901,37 +8901,37 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M93">
-        <v>3.935502480000001</v>
+        <v>3.97874976</v>
       </c>
       <c r="N93">
-        <v>-0.6861691466666673</v>
+        <v>-0.729416426666667</v>
       </c>
       <c r="O93">
-        <v>-0.1509572122666668</v>
+        <v>-0.1604716138666667</v>
       </c>
       <c r="P93">
-        <v>-0.5352119344000005</v>
+        <v>-0.5689448128000002</v>
       </c>
       <c r="Q93">
-        <v>2.3487880656</v>
+        <v>2.3150551872</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5192062958966169</v>
+        <v>0.5783820828836942</v>
       </c>
       <c r="T93">
-        <v>6.170071036150768</v>
+        <v>6.941329915669615</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.1816422012096746</v>
+        <v>0.1796678294573955</v>
       </c>
       <c r="W93">
-        <v>0.1201349248624198</v>
+        <v>0.1204247626356544</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8256463691348843</v>
+        <v>0.8166719520790705</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1570613482554975</v>
+        <v>0.1580713482554975</v>
       </c>
       <c r="C94">
-        <v>-11.98357395859051</v>
+        <v>-12.40861349217923</v>
       </c>
       <c r="D94">
-        <v>14.4996260414095</v>
+        <v>14.36918650782077</v>
       </c>
       <c r="E94">
-        <v>7.603200000000001</v>
+        <v>7.897800000000004</v>
       </c>
       <c r="F94">
-        <v>27.1032</v>
+        <v>27.3978</v>
       </c>
       <c r="G94">
         <v>0.62</v>
@@ -8983,37 +8983,37 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M94">
-        <v>3.97874976</v>
+        <v>4.021997040000001</v>
       </c>
       <c r="N94">
-        <v>-0.729416426666667</v>
+        <v>-0.7726637066666679</v>
       </c>
       <c r="O94">
-        <v>-0.1604716138666667</v>
+        <v>-0.1699860154666669</v>
       </c>
       <c r="P94">
-        <v>-0.5689448128000002</v>
+        <v>-0.602677691200001</v>
       </c>
       <c r="Q94">
-        <v>2.3150551872</v>
+        <v>2.281322308799999</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5783820828836942</v>
+        <v>0.6544652375813648</v>
       </c>
       <c r="T94">
-        <v>6.941329915669615</v>
+        <v>7.932948475050989</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.1796678294573955</v>
+        <v>0.1777359173126923</v>
       </c>
       <c r="W94">
-        <v>0.1204247626356544</v>
+        <v>0.1207083673384968</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8166719520790705</v>
+        <v>0.8078905332395103</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1580713482554975</v>
+        <v>0.2121103321495195</v>
       </c>
       <c r="C95">
-        <v>-12.40861349217923</v>
+        <v>-17.37217319077585</v>
       </c>
       <c r="D95">
-        <v>14.36918650782077</v>
+        <v>9.700226809224151</v>
       </c>
       <c r="E95">
-        <v>7.897800000000004</v>
+        <v>8.192400000000003</v>
       </c>
       <c r="F95">
-        <v>27.3978</v>
+        <v>27.6924</v>
       </c>
       <c r="G95">
         <v>0.62</v>
@@ -9065,45 +9065,45 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M95">
-        <v>4.021997040000001</v>
+        <v>5.560633920000001</v>
       </c>
       <c r="N95">
-        <v>-0.7726637066666679</v>
+        <v>-2.311300586666667</v>
       </c>
       <c r="O95">
-        <v>-0.1699860154666669</v>
+        <v>-0.5084861290666668</v>
       </c>
       <c r="P95">
-        <v>-0.602677691200001</v>
+        <v>-1.802814457600001</v>
       </c>
       <c r="Q95">
-        <v>2.281322308799999</v>
+        <v>1.0811855424</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6544652375813648</v>
+        <v>0.7937258420786261</v>
       </c>
       <c r="T95">
-        <v>7.932948475050989</v>
+        <v>9.747980995178358</v>
       </c>
       <c r="U95">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.1777359173126923</v>
+        <v>0.1285560861617255</v>
       </c>
       <c r="W95">
-        <v>0.1207083673384968</v>
+        <v>0.1749859378987255</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y95">
-        <v>0.8078905332395103</v>
+        <v>0.5843458461896612</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2121103321495195</v>
+        <v>0.2136603321495195</v>
       </c>
       <c r="C96">
-        <v>-17.37217319077585</v>
+        <v>-17.75634379606278</v>
       </c>
       <c r="D96">
-        <v>9.700226809224151</v>
+        <v>9.610656203937221</v>
       </c>
       <c r="E96">
-        <v>8.192400000000003</v>
+        <v>8.487000000000002</v>
       </c>
       <c r="F96">
-        <v>27.6924</v>
+        <v>27.987</v>
       </c>
       <c r="G96">
         <v>0.62</v>
@@ -9147,37 +9147,37 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M96">
-        <v>5.560633920000001</v>
+        <v>5.619789600000001</v>
       </c>
       <c r="N96">
-        <v>-2.311300586666667</v>
+        <v>-2.370456266666667</v>
       </c>
       <c r="O96">
-        <v>-0.5084861290666668</v>
+        <v>-0.5215003786666668</v>
       </c>
       <c r="P96">
-        <v>-1.802814457600001</v>
+        <v>-1.848955888000001</v>
       </c>
       <c r="Q96">
-        <v>1.0811855424</v>
+        <v>1.035044112</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7937258420786261</v>
+        <v>0.9433110104943518</v>
       </c>
       <c r="T96">
-        <v>9.747980995178358</v>
+        <v>11.69757719421404</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.1285560861617255</v>
+        <v>0.1272028642021284</v>
       </c>
       <c r="W96">
-        <v>0.1749859378987255</v>
+        <v>0.1752576648682126</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5843458461896612</v>
+        <v>0.5781948372824016</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2136603321495195</v>
+        <v>0.2152103321495195</v>
       </c>
       <c r="C97">
-        <v>-17.75634379606278</v>
+        <v>-18.13887536981683</v>
       </c>
       <c r="D97">
-        <v>9.610656203937221</v>
+        <v>9.522724630183179</v>
       </c>
       <c r="E97">
-        <v>8.487000000000002</v>
+        <v>8.781600000000005</v>
       </c>
       <c r="F97">
-        <v>27.987</v>
+        <v>28.2816</v>
       </c>
       <c r="G97">
         <v>0.62</v>
@@ -9229,37 +9229,37 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M97">
-        <v>5.619789600000001</v>
+        <v>5.678945280000001</v>
       </c>
       <c r="N97">
-        <v>-2.370456266666667</v>
+        <v>-2.429611946666667</v>
       </c>
       <c r="O97">
-        <v>-0.5215003786666668</v>
+        <v>-0.5345146282666668</v>
       </c>
       <c r="P97">
-        <v>-1.848955888000001</v>
+        <v>-1.8950973184</v>
       </c>
       <c r="Q97">
-        <v>1.035044112</v>
+        <v>0.9889026815999999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9433110104943518</v>
+        <v>1.16768876311794</v>
       </c>
       <c r="T97">
-        <v>11.69757719421404</v>
+        <v>14.62197149276755</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.1272028642021284</v>
+        <v>0.1258778343666895</v>
       </c>
       <c r="W97">
-        <v>0.1752576648682126</v>
+        <v>0.1755237308591688</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5781948372824016</v>
+        <v>0.5721719743940432</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2152103321495195</v>
+        <v>0.2167603321495196</v>
       </c>
       <c r="C98">
-        <v>-18.13887536981682</v>
+        <v>-18.5198124925353</v>
       </c>
       <c r="D98">
-        <v>9.522724630183177</v>
+        <v>9.436387507464703</v>
       </c>
       <c r="E98">
-        <v>8.781600000000001</v>
+        <v>9.0762</v>
       </c>
       <c r="F98">
-        <v>28.2816</v>
+        <v>28.5762</v>
       </c>
       <c r="G98">
         <v>0.62</v>
@@ -9311,37 +9311,37 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M98">
-        <v>5.678945280000001</v>
+        <v>5.738100960000001</v>
       </c>
       <c r="N98">
-        <v>-2.429611946666667</v>
+        <v>-2.488767626666667</v>
       </c>
       <c r="O98">
-        <v>-0.5345146282666668</v>
+        <v>-0.5475288778666668</v>
       </c>
       <c r="P98">
-        <v>-1.8950973184</v>
+        <v>-1.9412387488</v>
       </c>
       <c r="Q98">
-        <v>0.9889026815999999</v>
+        <v>0.9427612511999999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.167688763117937</v>
+        <v>1.54165168415725</v>
       </c>
       <c r="T98">
-        <v>14.62197149276751</v>
+        <v>19.49596199035668</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.1258778343666895</v>
+        <v>0.1245801247340432</v>
       </c>
       <c r="W98">
-        <v>0.1755237308591688</v>
+        <v>0.1757843109534041</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5721719743940432</v>
+        <v>0.5662732942456511</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2167603321495196</v>
+        <v>0.2183103321495195</v>
       </c>
       <c r="C99">
-        <v>-18.5198124925353</v>
+        <v>-18.89919814249795</v>
       </c>
       <c r="D99">
-        <v>9.436387507464703</v>
+        <v>9.351601857502052</v>
       </c>
       <c r="E99">
-        <v>9.0762</v>
+        <v>9.370799999999999</v>
       </c>
       <c r="F99">
-        <v>28.5762</v>
+        <v>28.8708</v>
       </c>
       <c r="G99">
         <v>0.62</v>
@@ -9393,37 +9393,37 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M99">
-        <v>5.738100960000001</v>
+        <v>5.79725664</v>
       </c>
       <c r="N99">
-        <v>-2.488767626666667</v>
+        <v>-2.547923306666666</v>
       </c>
       <c r="O99">
-        <v>-0.5475288778666668</v>
+        <v>-0.5605431274666666</v>
       </c>
       <c r="P99">
-        <v>-1.9412387488</v>
+        <v>-1.9873801792</v>
       </c>
       <c r="Q99">
-        <v>0.9427612511999999</v>
+        <v>0.8966198208000007</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.54165168415725</v>
+        <v>2.289577526235874</v>
       </c>
       <c r="T99">
-        <v>19.49596199035668</v>
+        <v>29.24394298553502</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.1245801247340432</v>
+        <v>0.123308898971451</v>
       </c>
       <c r="W99">
-        <v>0.1757843109534041</v>
+        <v>0.1760395730865326</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5662732942456511</v>
+        <v>0.5604949953247772</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2183103321495195</v>
+        <v>0.2198603321495195</v>
       </c>
       <c r="C100">
-        <v>-18.89919814249795</v>
+        <v>-19.27707376710538</v>
       </c>
       <c r="D100">
-        <v>9.351601857502052</v>
+        <v>9.268326232894623</v>
       </c>
       <c r="E100">
-        <v>9.370799999999999</v>
+        <v>9.665400000000002</v>
       </c>
       <c r="F100">
-        <v>28.8708</v>
+        <v>29.1654</v>
       </c>
       <c r="G100">
         <v>0.62</v>
@@ -9475,37 +9475,37 @@
         <v>3.249333333333333</v>
       </c>
       <c r="M100">
-        <v>5.79725664</v>
+        <v>5.85641232</v>
       </c>
       <c r="N100">
-        <v>-2.547923306666666</v>
+        <v>-2.607078986666667</v>
       </c>
       <c r="O100">
-        <v>-0.5605431274666666</v>
+        <v>-0.5735573770666668</v>
       </c>
       <c r="P100">
-        <v>-1.9873801792</v>
+        <v>-2.0335216096</v>
       </c>
       <c r="Q100">
-        <v>0.8966198208000007</v>
+        <v>0.8504783904000002</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.289577526235874</v>
+        <v>4.533355052471749</v>
       </c>
       <c r="T100">
-        <v>29.24394298553502</v>
+        <v>58.48788597107004</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.123308898971451</v>
+        <v>0.1220633545373959</v>
       </c>
       <c r="W100">
-        <v>0.1760395730865326</v>
+        <v>0.1762896784088909</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5604949953247772</v>
+        <v>0.5548334297154359</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2198603321495195</v>
-      </c>
-      <c r="C101">
-        <v>-19.27707376710538</v>
-      </c>
-      <c r="D101">
-        <v>9.268326232894623</v>
-      </c>
-      <c r="E101">
-        <v>9.665400000000002</v>
-      </c>
-      <c r="F101">
-        <v>29.1654</v>
-      </c>
-      <c r="G101">
-        <v>0.62</v>
-      </c>
-      <c r="H101">
-        <v>9.960000000000001</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>6.133333333333334</v>
-      </c>
-      <c r="K101">
-        <v>2.884</v>
-      </c>
-      <c r="L101">
-        <v>3.249333333333333</v>
-      </c>
-      <c r="M101">
-        <v>5.85641232</v>
-      </c>
-      <c r="N101">
-        <v>-2.607078986666667</v>
-      </c>
-      <c r="O101">
-        <v>-0.5735573770666668</v>
-      </c>
-      <c r="P101">
-        <v>-2.0335216096</v>
-      </c>
-      <c r="Q101">
-        <v>0.8504783904000002</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.533355052471749</v>
-      </c>
-      <c r="T101">
-        <v>58.48788597107004</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.1220633545373959</v>
-      </c>
-      <c r="W101">
-        <v>0.1762896784088909</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5548334297154359</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
